--- a/outputs/marine_equipment/Отгрузка_Питер.xlsx
+++ b/outputs/marine_equipment/Отгрузка_Питер.xlsx
@@ -13,8 +13,8 @@
     <sheet name="Упаковка и крепление" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Едет'!$A$3:$O$228</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Остается'!$A$3:$O$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Едет'!$A$3:$O$249</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Остается'!$A$3:$O$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -65,7 +65,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -90,6 +90,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FDF2E3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E2F3"/>
       </patternFill>
     </fill>
   </fills>
@@ -119,7 +124,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -152,6 +157,12 @@
     <xf numFmtId="3" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -546,7 +557,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Контейнер едет, значит лимит по весу жесткий. Взято 23 тонн: оценка массы справочная, запас на погрешность обязателен. Первая очередь — клинкеты Ду250 и Ду350 из бронзы и латуни, дальше остальная бронза и латунь, дальше по цене за килограмм.</t>
+          <t>Контейнер едет, значит лимит по весу жесткий. Взято 25 тонн: оценка массы справочная, запас на погрешность обязателен. Первая очередь — клинкеты Ду250 и Ду350 из бронзы и латуни, дальше остальная бронза и латунь, дальше по цене за килограмм.</t>
         </is>
       </c>
     </row>
@@ -565,12 +576,12 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>225 позиций</t>
+          <t>246 позиций</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2610 штук</t>
+          <t>2653 штук</t>
         </is>
       </c>
     </row>
@@ -582,12 +593,12 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>23.0 т</t>
+          <t>25.0 т</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>лимит 23 т</t>
+          <t>лимит 25 т</t>
         </is>
       </c>
     </row>
@@ -599,7 +610,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>25 куб. м</t>
+          <t>28 куб. м</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -615,7 +626,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>39356800</v>
+        <v>40516550</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
@@ -631,12 +642,12 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>46 позиций</t>
+          <t>25 позиций</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>9.8 т, 5.2 млн руб</t>
+          <t>7.8 т, 4.0 млн руб</t>
         </is>
       </c>
     </row>
@@ -716,22 +727,22 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>11.12</v>
+        <v>11.94</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>12.2</v>
+        <v>13.1</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>9596000</v>
+        <v>9911000</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>863</v>
+        <v>830</v>
       </c>
     </row>
     <row r="14">
@@ -741,22 +752,22 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>358</v>
+        <v>387</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>6.05</v>
+        <v>7.15</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>5.8</v>
+        <v>7.1</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>8550000</v>
+        <v>9357250</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>1413</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="15">
@@ -791,22 +802,22 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="E16" s="6" t="n">
         <v>0.8</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>1488000</v>
+        <v>1508000</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>1215</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="17">
@@ -866,13 +877,13 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="E19" s="6" t="n">
         <v>0.1</v>
@@ -881,7 +892,7 @@
         <v>120000</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="20">
@@ -891,22 +902,22 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C20" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
       <c r="E20" s="6" t="n">
         <v>0.1</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>81500</v>
+        <v>99000</v>
       </c>
       <c r="G20" s="7" t="n">
-        <v>906</v>
+        <v>900</v>
       </c>
     </row>
   </sheetData>
@@ -920,7 +931,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O229"/>
+  <dimension ref="A1:O250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1040,7 +1051,7 @@
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>Ярус 1, на пол</t>
+          <t>Ярус 1, на настил</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
@@ -1105,7 +1116,7 @@
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>Ярус 1, на пол</t>
+          <t>Ярус 1, на настил</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -1170,7 +1181,7 @@
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>Ярус 1, на пол</t>
+          <t>Ярус 1, на настил</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
@@ -1235,7 +1246,7 @@
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>Ярус 1, на пол</t>
+          <t>Ярус 1, на настил</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
@@ -1300,7 +1311,7 @@
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
@@ -1365,7 +1376,7 @@
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
@@ -1430,7 +1441,7 @@
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
@@ -1495,7 +1506,7 @@
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
@@ -1625,7 +1636,7 @@
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
@@ -1690,7 +1701,7 @@
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
@@ -1755,7 +1766,7 @@
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
@@ -1885,7 +1896,7 @@
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
@@ -2470,7 +2481,7 @@
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr">
@@ -2531,7 +2542,7 @@
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
@@ -2592,7 +2603,7 @@
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E28" s="8" t="inlineStr">
@@ -2653,7 +2664,7 @@
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
@@ -2714,7 +2725,7 @@
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr">
@@ -2775,7 +2786,7 @@
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
@@ -2836,7 +2847,7 @@
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E32" s="8" t="inlineStr">
@@ -2897,7 +2908,7 @@
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
@@ -2958,7 +2969,7 @@
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E34" s="8" t="inlineStr">
@@ -3019,7 +3030,7 @@
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
@@ -3080,7 +3091,7 @@
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E36" s="8" t="inlineStr">
@@ -3141,7 +3152,7 @@
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
@@ -3202,7 +3213,7 @@
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E38" s="8" t="inlineStr">
@@ -3263,7 +3274,7 @@
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
@@ -3324,7 +3335,7 @@
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E40" s="8" t="inlineStr">
@@ -3385,7 +3396,7 @@
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
@@ -3446,7 +3457,7 @@
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E42" s="8" t="inlineStr">
@@ -3507,7 +3518,7 @@
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
@@ -3568,7 +3579,7 @@
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E44" s="8" t="inlineStr">
@@ -3629,7 +3640,7 @@
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
@@ -3751,7 +3762,7 @@
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
@@ -3812,7 +3823,7 @@
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E48" s="8" t="inlineStr">
@@ -3873,7 +3884,7 @@
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
@@ -3934,7 +3945,7 @@
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E50" s="8" t="inlineStr">
@@ -3995,7 +4006,7 @@
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
@@ -4056,7 +4067,7 @@
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E52" s="8" t="inlineStr">
@@ -4117,7 +4128,7 @@
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
@@ -4178,7 +4189,7 @@
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E54" s="8" t="inlineStr">
@@ -4239,7 +4250,7 @@
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
@@ -4300,7 +4311,7 @@
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E56" s="8" t="inlineStr">
@@ -4361,7 +4372,7 @@
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
@@ -4422,7 +4433,7 @@
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E58" s="8" t="inlineStr">
@@ -4483,7 +4494,7 @@
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
@@ -4544,7 +4555,7 @@
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E60" s="8" t="inlineStr">
@@ -4605,7 +4616,7 @@
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
@@ -4666,7 +4677,7 @@
       </c>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E62" s="8" t="inlineStr">
@@ -4727,7 +4738,7 @@
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
@@ -4788,7 +4799,7 @@
       </c>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E64" s="8" t="inlineStr">
@@ -4849,7 +4860,7 @@
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
@@ -4910,7 +4921,7 @@
       </c>
       <c r="D66" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E66" s="8" t="inlineStr">
@@ -4971,7 +4982,7 @@
       </c>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr">
@@ -5032,7 +5043,7 @@
       </c>
       <c r="D68" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E68" s="8" t="inlineStr">
@@ -5093,7 +5104,7 @@
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr">
@@ -5154,7 +5165,7 @@
       </c>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E70" s="8" t="inlineStr">
@@ -5215,7 +5226,7 @@
       </c>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr">
@@ -5276,7 +5287,7 @@
       </c>
       <c r="D72" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E72" s="8" t="inlineStr">
@@ -5337,7 +5348,7 @@
       </c>
       <c r="D73" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E73" s="8" t="inlineStr">
@@ -5398,7 +5409,7 @@
       </c>
       <c r="D74" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E74" s="8" t="inlineStr">
@@ -5459,7 +5470,7 @@
       </c>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E75" s="8" t="inlineStr">
@@ -5520,7 +5531,7 @@
       </c>
       <c r="D76" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E76" s="8" t="inlineStr">
@@ -5581,7 +5592,7 @@
       </c>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E77" s="8" t="inlineStr">
@@ -5642,7 +5653,7 @@
       </c>
       <c r="D78" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E78" s="8" t="inlineStr">
@@ -5703,7 +5714,7 @@
       </c>
       <c r="D79" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E79" s="8" t="inlineStr">
@@ -5764,7 +5775,7 @@
       </c>
       <c r="D80" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E80" s="8" t="inlineStr">
@@ -5825,7 +5836,7 @@
       </c>
       <c r="D81" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E81" s="8" t="inlineStr">
@@ -5886,7 +5897,7 @@
       </c>
       <c r="D82" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E82" s="8" t="inlineStr">
@@ -5947,7 +5958,7 @@
       </c>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E83" s="8" t="inlineStr">
@@ -6008,7 +6019,7 @@
       </c>
       <c r="D84" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E84" s="8" t="inlineStr">
@@ -6069,7 +6080,7 @@
       </c>
       <c r="D85" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E85" s="8" t="inlineStr">
@@ -6130,7 +6141,7 @@
       </c>
       <c r="D86" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E86" s="8" t="inlineStr">
@@ -6191,7 +6202,7 @@
       </c>
       <c r="D87" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
@@ -6252,7 +6263,7 @@
       </c>
       <c r="D88" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E88" s="8" t="inlineStr">
@@ -6313,7 +6324,7 @@
       </c>
       <c r="D89" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E89" s="8" t="inlineStr">
@@ -6374,7 +6385,7 @@
       </c>
       <c r="D90" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E90" s="8" t="inlineStr">
@@ -6435,7 +6446,7 @@
       </c>
       <c r="D91" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E91" s="8" t="inlineStr">
@@ -6496,7 +6507,7 @@
       </c>
       <c r="D92" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E92" s="8" t="inlineStr">
@@ -6557,7 +6568,7 @@
       </c>
       <c r="D93" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E93" s="8" t="inlineStr">
@@ -6618,7 +6629,7 @@
       </c>
       <c r="D94" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E94" s="8" t="inlineStr">
@@ -6679,7 +6690,7 @@
       </c>
       <c r="D95" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E95" s="8" t="inlineStr">
@@ -6740,7 +6751,7 @@
       </c>
       <c r="D96" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E96" s="8" t="inlineStr">
@@ -6801,7 +6812,7 @@
       </c>
       <c r="D97" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr">
@@ -6862,7 +6873,7 @@
       </c>
       <c r="D98" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E98" s="8" t="inlineStr">
@@ -6923,7 +6934,7 @@
       </c>
       <c r="D99" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E99" s="8" t="inlineStr">
@@ -6984,7 +6995,7 @@
       </c>
       <c r="D100" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E100" s="8" t="inlineStr">
@@ -7045,7 +7056,7 @@
       </c>
       <c r="D101" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E101" s="8" t="inlineStr">
@@ -7106,7 +7117,7 @@
       </c>
       <c r="D102" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E102" s="8" t="inlineStr">
@@ -7167,7 +7178,7 @@
       </c>
       <c r="D103" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E103" s="8" t="inlineStr">
@@ -7228,7 +7239,7 @@
       </c>
       <c r="D104" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E104" s="8" t="inlineStr">
@@ -7289,7 +7300,7 @@
       </c>
       <c r="D105" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E105" s="8" t="inlineStr">
@@ -7350,7 +7361,7 @@
       </c>
       <c r="D106" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E106" s="8" t="inlineStr">
@@ -7411,7 +7422,7 @@
       </c>
       <c r="D107" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E107" s="8" t="inlineStr">
@@ -7472,7 +7483,7 @@
       </c>
       <c r="D108" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E108" s="8" t="inlineStr">
@@ -7533,7 +7544,7 @@
       </c>
       <c r="D109" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 4, верх</t>
         </is>
       </c>
       <c r="E109" s="8" t="inlineStr">
@@ -7569,7 +7580,7 @@
       </c>
       <c r="N109" s="10" t="inlineStr">
         <is>
-          <t>Поддон с обрешеткой, крепление к полу</t>
+          <t>Обрешетка, ставится верхним ярусом на ящики</t>
         </is>
       </c>
       <c r="O109" s="8" t="inlineStr">
@@ -7594,7 +7605,7 @@
       </c>
       <c r="D110" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E110" s="8" t="inlineStr">
@@ -7655,7 +7666,7 @@
       </c>
       <c r="D111" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E111" s="8" t="inlineStr">
@@ -7716,7 +7727,7 @@
       </c>
       <c r="D112" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E112" s="8" t="inlineStr">
@@ -7777,7 +7788,7 @@
       </c>
       <c r="D113" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E113" s="8" t="inlineStr">
@@ -7838,7 +7849,7 @@
       </c>
       <c r="D114" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E114" s="8" t="inlineStr">
@@ -7899,7 +7910,7 @@
       </c>
       <c r="D115" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E115" s="8" t="inlineStr">
@@ -7960,7 +7971,7 @@
       </c>
       <c r="D116" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E116" s="8" t="inlineStr">
@@ -8021,7 +8032,7 @@
       </c>
       <c r="D117" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E117" s="8" t="inlineStr">
@@ -8082,7 +8093,7 @@
       </c>
       <c r="D118" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E118" s="8" t="inlineStr">
@@ -8143,7 +8154,7 @@
       </c>
       <c r="D119" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E119" s="8" t="inlineStr">
@@ -8204,7 +8215,7 @@
       </c>
       <c r="D120" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E120" s="8" t="inlineStr">
@@ -8265,7 +8276,7 @@
       </c>
       <c r="D121" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E121" s="8" t="inlineStr">
@@ -8326,7 +8337,7 @@
       </c>
       <c r="D122" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E122" s="8" t="inlineStr">
@@ -8387,7 +8398,7 @@
       </c>
       <c r="D123" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E123" s="8" t="inlineStr">
@@ -8448,7 +8459,7 @@
       </c>
       <c r="D124" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E124" s="8" t="inlineStr">
@@ -8509,7 +8520,7 @@
       </c>
       <c r="D125" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E125" s="8" t="inlineStr">
@@ -8570,7 +8581,7 @@
       </c>
       <c r="D126" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E126" s="8" t="inlineStr">
@@ -8631,7 +8642,7 @@
       </c>
       <c r="D127" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E127" s="8" t="inlineStr">
@@ -8692,7 +8703,7 @@
       </c>
       <c r="D128" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 4, верх</t>
         </is>
       </c>
       <c r="E128" s="8" t="inlineStr">
@@ -8728,7 +8739,7 @@
       </c>
       <c r="N128" s="10" t="inlineStr">
         <is>
-          <t>Поддон с обрешеткой, крепление к полу</t>
+          <t>Обрешетка, ставится верхним ярусом на ящики</t>
         </is>
       </c>
       <c r="O128" s="8" t="inlineStr">
@@ -8753,7 +8764,7 @@
       </c>
       <c r="D129" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E129" s="8" t="inlineStr">
@@ -8814,7 +8825,7 @@
       </c>
       <c r="D130" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E130" s="8" t="inlineStr">
@@ -8871,7 +8882,7 @@
       </c>
       <c r="D131" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E131" s="8" t="inlineStr">
@@ -8932,7 +8943,7 @@
       </c>
       <c r="D132" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E132" s="8" t="inlineStr">
@@ -8993,7 +9004,7 @@
       </c>
       <c r="D133" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E133" s="8" t="inlineStr">
@@ -9054,7 +9065,7 @@
       </c>
       <c r="D134" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E134" s="8" t="inlineStr">
@@ -9115,7 +9126,7 @@
       </c>
       <c r="D135" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E135" s="8" t="inlineStr">
@@ -9176,7 +9187,7 @@
       </c>
       <c r="D136" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E136" s="8" t="inlineStr">
@@ -9237,7 +9248,7 @@
       </c>
       <c r="D137" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E137" s="8" t="inlineStr">
@@ -9298,7 +9309,7 @@
       </c>
       <c r="D138" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 4, верх</t>
         </is>
       </c>
       <c r="E138" s="8" t="inlineStr">
@@ -9334,7 +9345,7 @@
       </c>
       <c r="N138" s="10" t="inlineStr">
         <is>
-          <t>Поддон с обрешеткой, крепление к полу</t>
+          <t>Обрешетка, ставится верхним ярусом на ящики</t>
         </is>
       </c>
       <c r="O138" s="8" t="inlineStr">
@@ -9359,7 +9370,7 @@
       </c>
       <c r="D139" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E139" s="8" t="inlineStr">
@@ -9420,7 +9431,7 @@
       </c>
       <c r="D140" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E140" s="8" t="inlineStr">
@@ -9481,7 +9492,7 @@
       </c>
       <c r="D141" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E141" s="8" t="inlineStr">
@@ -9542,7 +9553,7 @@
       </c>
       <c r="D142" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E142" s="8" t="inlineStr">
@@ -9603,7 +9614,7 @@
       </c>
       <c r="D143" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E143" s="8" t="inlineStr">
@@ -9664,7 +9675,7 @@
       </c>
       <c r="D144" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E144" s="8" t="inlineStr">
@@ -9725,7 +9736,7 @@
       </c>
       <c r="D145" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E145" s="8" t="inlineStr">
@@ -9786,7 +9797,7 @@
       </c>
       <c r="D146" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E146" s="8" t="inlineStr">
@@ -9847,7 +9858,7 @@
       </c>
       <c r="D147" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E147" s="8" t="inlineStr">
@@ -9908,7 +9919,7 @@
       </c>
       <c r="D148" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E148" s="8" t="inlineStr">
@@ -9969,7 +9980,7 @@
       </c>
       <c r="D149" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E149" s="8" t="inlineStr">
@@ -10030,7 +10041,7 @@
       </c>
       <c r="D150" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E150" s="8" t="inlineStr">
@@ -10091,7 +10102,7 @@
       </c>
       <c r="D151" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E151" s="8" t="inlineStr">
@@ -10152,7 +10163,7 @@
       </c>
       <c r="D152" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E152" s="8" t="inlineStr">
@@ -10213,7 +10224,7 @@
       </c>
       <c r="D153" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E153" s="8" t="inlineStr">
@@ -10274,7 +10285,7 @@
       </c>
       <c r="D154" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E154" s="8" t="inlineStr">
@@ -10396,7 +10407,7 @@
       </c>
       <c r="D156" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E156" s="8" t="inlineStr">
@@ -10457,7 +10468,7 @@
       </c>
       <c r="D157" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E157" s="8" t="inlineStr">
@@ -10518,7 +10529,7 @@
       </c>
       <c r="D158" s="8" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 4, верх</t>
         </is>
       </c>
       <c r="E158" s="8" t="inlineStr">
@@ -10554,7 +10565,7 @@
       </c>
       <c r="N158" s="10" t="inlineStr">
         <is>
-          <t>Поддон с обрешеткой, крепление к полу</t>
+          <t>Обрешетка, ставится верхним ярусом на ящики</t>
         </is>
       </c>
       <c r="O158" s="8" t="inlineStr">
@@ -10579,7 +10590,7 @@
       </c>
       <c r="D159" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E159" s="8" t="inlineStr">
@@ -10640,7 +10651,7 @@
       </c>
       <c r="D160" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E160" s="8" t="inlineStr">
@@ -10697,7 +10708,7 @@
       </c>
       <c r="D161" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 4, верх</t>
         </is>
       </c>
       <c r="E161" s="8" t="inlineStr">
@@ -10733,7 +10744,7 @@
       </c>
       <c r="N161" s="10" t="inlineStr">
         <is>
-          <t>Поддон с обрешеткой, крепление к полу</t>
+          <t>Обрешетка, ставится верхним ярусом на ящики</t>
         </is>
       </c>
       <c r="O161" s="8" t="inlineStr">
@@ -10758,7 +10769,7 @@
       </c>
       <c r="D162" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E162" s="8" t="inlineStr">
@@ -10819,7 +10830,7 @@
       </c>
       <c r="D163" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E163" s="8" t="inlineStr">
@@ -10880,7 +10891,7 @@
       </c>
       <c r="D164" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E164" s="8" t="inlineStr">
@@ -10937,7 +10948,7 @@
       </c>
       <c r="D165" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 4, верх</t>
         </is>
       </c>
       <c r="E165" s="8" t="inlineStr">
@@ -10973,7 +10984,7 @@
       </c>
       <c r="N165" s="10" t="inlineStr">
         <is>
-          <t>Поддон с обрешеткой, крепление к полу</t>
+          <t>Обрешетка, ставится верхним ярусом на ящики</t>
         </is>
       </c>
       <c r="O165" s="8" t="inlineStr">
@@ -10998,7 +11009,7 @@
       </c>
       <c r="D166" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E166" s="8" t="inlineStr">
@@ -11059,7 +11070,7 @@
       </c>
       <c r="D167" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E167" s="8" t="inlineStr">
@@ -11120,7 +11131,7 @@
       </c>
       <c r="D168" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E168" s="8" t="inlineStr">
@@ -11181,7 +11192,7 @@
       </c>
       <c r="D169" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E169" s="8" t="inlineStr">
@@ -11242,7 +11253,7 @@
       </c>
       <c r="D170" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E170" s="8" t="inlineStr">
@@ -11303,7 +11314,7 @@
       </c>
       <c r="D171" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E171" s="8" t="inlineStr">
@@ -11364,7 +11375,7 @@
       </c>
       <c r="D172" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E172" s="8" t="inlineStr">
@@ -11425,7 +11436,7 @@
       </c>
       <c r="D173" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E173" s="8" t="inlineStr">
@@ -11486,7 +11497,7 @@
       </c>
       <c r="D174" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E174" s="8" t="inlineStr">
@@ -11547,7 +11558,7 @@
       </c>
       <c r="D175" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E175" s="8" t="inlineStr">
@@ -11608,7 +11619,7 @@
       </c>
       <c r="D176" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E176" s="8" t="inlineStr">
@@ -11669,7 +11680,7 @@
       </c>
       <c r="D177" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E177" s="8" t="inlineStr">
@@ -11730,7 +11741,7 @@
       </c>
       <c r="D178" s="8" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 4, верх</t>
         </is>
       </c>
       <c r="E178" s="8" t="inlineStr">
@@ -11766,7 +11777,7 @@
       </c>
       <c r="N178" s="10" t="inlineStr">
         <is>
-          <t>Поддон с обрешеткой, крепление к полу</t>
+          <t>Обрешетка, ставится верхним ярусом на ящики</t>
         </is>
       </c>
       <c r="O178" s="8" t="inlineStr">
@@ -11791,7 +11802,7 @@
       </c>
       <c r="D179" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E179" s="8" t="inlineStr">
@@ -11852,7 +11863,7 @@
       </c>
       <c r="D180" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E180" s="8" t="inlineStr">
@@ -11913,7 +11924,7 @@
       </c>
       <c r="D181" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E181" s="8" t="inlineStr">
@@ -11974,7 +11985,7 @@
       </c>
       <c r="D182" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E182" s="8" t="inlineStr">
@@ -12035,7 +12046,7 @@
       </c>
       <c r="D183" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E183" s="8" t="inlineStr">
@@ -12096,7 +12107,7 @@
       </c>
       <c r="D184" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E184" s="8" t="inlineStr">
@@ -12157,7 +12168,7 @@
       </c>
       <c r="D185" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E185" s="8" t="inlineStr">
@@ -12218,7 +12229,7 @@
       </c>
       <c r="D186" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E186" s="8" t="inlineStr">
@@ -12279,7 +12290,7 @@
       </c>
       <c r="D187" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E187" s="8" t="inlineStr">
@@ -12340,7 +12351,7 @@
       </c>
       <c r="D188" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E188" s="8" t="inlineStr">
@@ -12401,7 +12412,7 @@
       </c>
       <c r="D189" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E189" s="8" t="inlineStr">
@@ -12462,7 +12473,7 @@
       </c>
       <c r="D190" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E190" s="8" t="inlineStr">
@@ -12523,7 +12534,7 @@
       </c>
       <c r="D191" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E191" s="8" t="inlineStr">
@@ -12584,7 +12595,7 @@
       </c>
       <c r="D192" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E192" s="8" t="inlineStr">
@@ -12645,7 +12656,7 @@
       </c>
       <c r="D193" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E193" s="8" t="inlineStr">
@@ -12706,7 +12717,7 @@
       </c>
       <c r="D194" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E194" s="8" t="inlineStr">
@@ -12767,7 +12778,7 @@
       </c>
       <c r="D195" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E195" s="8" t="inlineStr">
@@ -12828,7 +12839,7 @@
       </c>
       <c r="D196" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E196" s="8" t="inlineStr">
@@ -12889,7 +12900,7 @@
       </c>
       <c r="D197" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E197" s="8" t="inlineStr">
@@ -13007,7 +13018,7 @@
       </c>
       <c r="D199" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 4, верх</t>
         </is>
       </c>
       <c r="E199" s="8" t="inlineStr">
@@ -13043,7 +13054,7 @@
       </c>
       <c r="N199" s="10" t="inlineStr">
         <is>
-          <t>Поддон с обрешеткой, крепление к полу</t>
+          <t>Обрешетка, ставится верхним ярусом на ящики</t>
         </is>
       </c>
       <c r="O199" s="8" t="inlineStr">
@@ -13068,7 +13079,7 @@
       </c>
       <c r="D200" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 4, верх</t>
         </is>
       </c>
       <c r="E200" s="8" t="inlineStr">
@@ -13104,7 +13115,7 @@
       </c>
       <c r="N200" s="10" t="inlineStr">
         <is>
-          <t>Поддон с обрешеткой, крепление к полу</t>
+          <t>Обрешетка, ставится верхним ярусом на ящики</t>
         </is>
       </c>
       <c r="O200" s="8" t="inlineStr">
@@ -13129,7 +13140,7 @@
       </c>
       <c r="D201" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E201" s="8" t="inlineStr">
@@ -13190,7 +13201,7 @@
       </c>
       <c r="D202" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E202" s="8" t="inlineStr">
@@ -13312,7 +13323,7 @@
       </c>
       <c r="D204" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E204" s="8" t="inlineStr">
@@ -13678,7 +13689,7 @@
       </c>
       <c r="D210" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E210" s="8" t="inlineStr">
@@ -13739,7 +13750,7 @@
       </c>
       <c r="D211" s="8" t="inlineStr">
         <is>
-          <t>Ярус 1, на пол</t>
+          <t>Ярус 1, на настил</t>
         </is>
       </c>
       <c r="E211" s="8" t="inlineStr">
@@ -13922,7 +13933,7 @@
       </c>
       <c r="D214" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E214" s="8" t="inlineStr">
@@ -13983,7 +13994,7 @@
       </c>
       <c r="D215" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E215" s="8" t="inlineStr">
@@ -14105,7 +14116,7 @@
       </c>
       <c r="D217" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E217" s="8" t="inlineStr">
@@ -14166,7 +14177,7 @@
       </c>
       <c r="D218" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E218" s="8" t="inlineStr">
@@ -14227,7 +14238,7 @@
       </c>
       <c r="D219" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E219" s="8" t="inlineStr">
@@ -14284,7 +14295,7 @@
       </c>
       <c r="D220" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E220" s="8" t="inlineStr">
@@ -14345,22 +14356,22 @@
       </c>
       <c r="D221" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E221" s="8" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
+          <t>кингстон</t>
         </is>
       </c>
       <c r="F221" s="8" t="inlineStr">
         <is>
-          <t>Ду20</t>
+          <t>Ду50</t>
         </is>
       </c>
       <c r="G221" s="10" t="inlineStr">
         <is>
-          <t>Клапан муфтовый проходной запорный Ду20Ру16</t>
+          <t>Кингстон донный фланцевый Ду50 Ру2,5</t>
         </is>
       </c>
       <c r="H221" s="8" t="inlineStr"/>
@@ -14368,25 +14379,25 @@
         <v>1</v>
       </c>
       <c r="J221" s="12" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="K221" s="13" t="n">
-        <v>0.002</v>
+        <v>0.012</v>
       </c>
       <c r="L221" s="12" t="n">
-        <v>1000</v>
+        <v>17500</v>
       </c>
       <c r="M221" s="12" t="n">
-        <v>667</v>
+        <v>875</v>
       </c>
       <c r="N221" s="10" t="inlineStr">
         <is>
-          <t>Ящик сплошной, с перегородками</t>
+          <t>Обрешетка на поддоне</t>
         </is>
       </c>
       <c r="O221" s="8" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -14406,22 +14417,22 @@
       </c>
       <c r="D222" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 2</t>
         </is>
       </c>
       <c r="E222" s="8" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
+          <t>клинкет (задвижка)</t>
         </is>
       </c>
       <c r="F222" s="8" t="inlineStr">
         <is>
-          <t>Ду25</t>
+          <t>Ду80</t>
         </is>
       </c>
       <c r="G222" s="10" t="inlineStr">
         <is>
-          <t>Клапан муфтовый проходной запорный Ду25Ру16</t>
+          <t>Задвижка клинкетная Ду80 ( в разборе)</t>
         </is>
       </c>
       <c r="H222" s="8" t="inlineStr"/>
@@ -14429,25 +14440,25 @@
         <v>2</v>
       </c>
       <c r="J222" s="12" t="n">
-        <v>5</v>
+        <v>56</v>
       </c>
       <c r="K222" s="13" t="n">
-        <v>0.006</v>
+        <v>0.06</v>
       </c>
       <c r="L222" s="12" t="n">
-        <v>2500</v>
+        <v>48000</v>
       </c>
       <c r="M222" s="12" t="n">
-        <v>500</v>
+        <v>857</v>
       </c>
       <c r="N222" s="10" t="inlineStr">
         <is>
-          <t>Ящик сплошной, с перегородками</t>
+          <t>Обрешетка на поддоне</t>
         </is>
       </c>
       <c r="O222" s="8" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
     </row>
@@ -14467,48 +14478,48 @@
       </c>
       <c r="D223" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 2</t>
         </is>
       </c>
       <c r="E223" s="8" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
+          <t>клапан фланцевый</t>
         </is>
       </c>
       <c r="F223" s="8" t="inlineStr">
         <is>
-          <t>Ду32</t>
+          <t>Ду100</t>
         </is>
       </c>
       <c r="G223" s="10" t="inlineStr">
         <is>
-          <t>Клапан муфтовый проходной запорный Ду32Ру10</t>
+          <t>Клапана невозвратный проходной фланцевый Ду100 Ру10 (522-03.205)</t>
         </is>
       </c>
       <c r="H223" s="8" t="inlineStr"/>
       <c r="I223" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J223" s="12" t="n">
-        <v>4</v>
+        <v>200</v>
       </c>
       <c r="K223" s="13" t="n">
-        <v>0.005</v>
+        <v>0.225</v>
       </c>
       <c r="L223" s="12" t="n">
-        <v>1500</v>
+        <v>170000</v>
       </c>
       <c r="M223" s="12" t="n">
-        <v>429</v>
+        <v>850</v>
       </c>
       <c r="N223" s="10" t="inlineStr">
         <is>
-          <t>Ящик сплошной, с перегородками</t>
+          <t>Поддон, прокладки между рядами</t>
         </is>
       </c>
       <c r="O223" s="8" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
     </row>
@@ -14528,44 +14539,48 @@
       </c>
       <c r="D224" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 2</t>
         </is>
       </c>
       <c r="E224" s="8" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
+          <t>клапан фланцевый</t>
         </is>
       </c>
       <c r="F224" s="8" t="inlineStr">
         <is>
-          <t>Ду15</t>
+          <t>Ду125</t>
         </is>
       </c>
       <c r="G224" s="10" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной бессальниковый Ду15/1</t>
+          <t>Клапан фланцевый проходной Ду125</t>
         </is>
       </c>
       <c r="H224" s="8" t="inlineStr"/>
       <c r="I224" s="8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J224" s="12" t="n">
-        <v>3</v>
+        <v>330</v>
       </c>
       <c r="K224" s="13" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="L224" s="12" t="n"/>
-      <c r="M224" s="12" t="n"/>
+        <v>0.42</v>
+      </c>
+      <c r="L224" s="12" t="n">
+        <v>276000</v>
+      </c>
+      <c r="M224" s="12" t="n">
+        <v>836</v>
+      </c>
       <c r="N224" s="10" t="inlineStr">
         <is>
-          <t>Ящик сплошной, с перегородками</t>
+          <t>Поддон, прокладки между рядами</t>
         </is>
       </c>
       <c r="O224" s="8" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -14585,44 +14600,48 @@
       </c>
       <c r="D225" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 2</t>
         </is>
       </c>
       <c r="E225" s="8" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
+          <t>клапан фланцевый</t>
         </is>
       </c>
       <c r="F225" s="8" t="inlineStr">
         <is>
-          <t>Ду15</t>
+          <t>Ду125</t>
         </is>
       </c>
       <c r="G225" s="10" t="inlineStr">
         <is>
-          <t>(Кнопка)Клапан самозакрывающий проходной муфтовый Ду15Ру3</t>
+          <t>Клапан фланцевый проходной Ду125 Ру10</t>
         </is>
       </c>
       <c r="H225" s="8" t="inlineStr"/>
       <c r="I225" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J225" s="12" t="n">
-        <v>1</v>
+        <v>165</v>
       </c>
       <c r="K225" s="13" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="L225" s="12" t="n"/>
-      <c r="M225" s="12" t="n"/>
+        <v>0.21</v>
+      </c>
+      <c r="L225" s="12" t="n">
+        <v>138000</v>
+      </c>
+      <c r="M225" s="12" t="n">
+        <v>836</v>
+      </c>
       <c r="N225" s="10" t="inlineStr">
         <is>
-          <t>Ящик сплошной, с перегородками</t>
+          <t>Поддон, прокладки между рядами</t>
         </is>
       </c>
       <c r="O225" s="8" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -14642,18 +14661,22 @@
       </c>
       <c r="D226" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E226" s="8" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
-        </is>
-      </c>
-      <c r="F226" s="8" t="inlineStr"/>
+          <t>клапан фланцевый</t>
+        </is>
+      </c>
+      <c r="F226" s="8" t="inlineStr">
+        <is>
+          <t>Ду80</t>
+        </is>
+      </c>
       <c r="G226" s="10" t="inlineStr">
         <is>
-          <t>Клапан дроссельный угловой штуцерный</t>
+          <t>Клапан фланцевый проходной Ду80 Ру 40 сталь (521-35.3437)</t>
         </is>
       </c>
       <c r="H226" s="8" t="inlineStr"/>
@@ -14661,21 +14684,25 @@
         <v>1</v>
       </c>
       <c r="J226" s="12" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="K226" s="13" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L226" s="12" t="n"/>
-      <c r="M226" s="12" t="n"/>
+        <v>0.03</v>
+      </c>
+      <c r="L226" s="12" t="n">
+        <v>22000</v>
+      </c>
+      <c r="M226" s="12" t="n">
+        <v>786</v>
+      </c>
       <c r="N226" s="10" t="inlineStr">
         <is>
-          <t>Ящик сплошной, с перегородками</t>
+          <t>Обрешетка на поддоне</t>
         </is>
       </c>
       <c r="O226" s="8" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
     </row>
@@ -14695,22 +14722,22 @@
       </c>
       <c r="D227" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E227" s="8" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
+          <t>клапан фланцевый</t>
         </is>
       </c>
       <c r="F227" s="8" t="inlineStr">
         <is>
-          <t>Ду10</t>
+          <t>Ду80</t>
         </is>
       </c>
       <c r="G227" s="10" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду10 Ру100</t>
+          <t>Клапан фланцевый проходной Ду80 Ру 40 сталь (522-01.101)</t>
         </is>
       </c>
       <c r="H227" s="8" t="inlineStr"/>
@@ -14718,21 +14745,25 @@
         <v>1</v>
       </c>
       <c r="J227" s="12" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="K227" s="13" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="L227" s="12" t="n"/>
-      <c r="M227" s="12" t="n"/>
+        <v>0.03</v>
+      </c>
+      <c r="L227" s="12" t="n">
+        <v>22000</v>
+      </c>
+      <c r="M227" s="12" t="n">
+        <v>786</v>
+      </c>
       <c r="N227" s="10" t="inlineStr">
         <is>
-          <t>Ящик сплошной, с перегородками</t>
+          <t>Обрешетка на поддоне</t>
         </is>
       </c>
       <c r="O227" s="8" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
     </row>
@@ -14752,18 +14783,22 @@
       </c>
       <c r="D228" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 2</t>
         </is>
       </c>
       <c r="E228" s="8" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
-        </is>
-      </c>
-      <c r="F228" s="8" t="inlineStr"/>
+          <t>клинкет (задвижка)</t>
+        </is>
+      </c>
+      <c r="F228" s="8" t="inlineStr">
+        <is>
+          <t>Ду80</t>
+        </is>
+      </c>
       <c r="G228" s="10" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду НЕРЖ</t>
+          <t>Задвижка клинкетная ДУ 80, сталь</t>
         </is>
       </c>
       <c r="H228" s="8" t="inlineStr"/>
@@ -14771,45 +14806,1274 @@
         <v>1</v>
       </c>
       <c r="J228" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="K228" s="13" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="L228" s="12" t="n">
+        <v>22000</v>
+      </c>
+      <c r="M228" s="12" t="n">
+        <v>786</v>
+      </c>
+      <c r="N228" s="10" t="inlineStr">
+        <is>
+          <t>Обрешетка на поддоне</t>
+        </is>
+      </c>
+      <c r="O228" s="8" t="inlineStr">
+        <is>
+          <t>Склад 1А/1Б</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="8" t="n">
+        <v>226</v>
+      </c>
+      <c r="B229" s="9" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="C229" s="10" t="inlineStr">
+        <is>
+          <t>3. Прочее, по цене за килограмм</t>
+        </is>
+      </c>
+      <c r="D229" s="8" t="inlineStr">
+        <is>
+          <t>Ярус 2</t>
+        </is>
+      </c>
+      <c r="E229" s="8" t="inlineStr">
+        <is>
+          <t>клинкет (задвижка)</t>
+        </is>
+      </c>
+      <c r="F229" s="8" t="inlineStr">
+        <is>
+          <t>Ду100</t>
+        </is>
+      </c>
+      <c r="G229" s="10" t="inlineStr">
+        <is>
+          <t>Задвижка клинкетная Ду100 без штока и блинов ( в разборе)</t>
+        </is>
+      </c>
+      <c r="H229" s="8" t="inlineStr"/>
+      <c r="I229" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J229" s="12" t="n">
+        <v>45</v>
+      </c>
+      <c r="K229" s="13" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="L229" s="12" t="n">
+        <v>35000</v>
+      </c>
+      <c r="M229" s="12" t="n">
+        <v>778</v>
+      </c>
+      <c r="N229" s="10" t="inlineStr">
+        <is>
+          <t>Поддон, прокладки между рядами</t>
+        </is>
+      </c>
+      <c r="O229" s="8" t="inlineStr">
+        <is>
+          <t>Склад 1А/1Б</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="8" t="n">
+        <v>227</v>
+      </c>
+      <c r="B230" s="9" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="C230" s="10" t="inlineStr">
+        <is>
+          <t>3. Прочее, по цене за килограмм</t>
+        </is>
+      </c>
+      <c r="D230" s="8" t="inlineStr">
+        <is>
+          <t>Ярус 2</t>
+        </is>
+      </c>
+      <c r="E230" s="8" t="inlineStr">
+        <is>
+          <t>клапан фланцевый</t>
+        </is>
+      </c>
+      <c r="F230" s="8" t="inlineStr">
+        <is>
+          <t>Ду125</t>
+        </is>
+      </c>
+      <c r="G230" s="10" t="inlineStr">
+        <is>
+          <t>Клапан фланцевый проходной Ду125 ок.входа</t>
+        </is>
+      </c>
+      <c r="H230" s="8" t="inlineStr"/>
+      <c r="I230" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="K228" s="13" t="n">
+      <c r="J230" s="12" t="n">
+        <v>110</v>
+      </c>
+      <c r="K230" s="13" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="L230" s="12" t="n">
+        <v>75000</v>
+      </c>
+      <c r="M230" s="12" t="n">
+        <v>682</v>
+      </c>
+      <c r="N230" s="10" t="inlineStr">
+        <is>
+          <t>Поддон, прокладки между рядами</t>
+        </is>
+      </c>
+      <c r="O230" s="8" t="inlineStr">
+        <is>
+          <t>Склад 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="8" t="n">
+        <v>228</v>
+      </c>
+      <c r="B231" s="9" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="C231" s="10" t="inlineStr">
+        <is>
+          <t>3. Прочее, по цене за килограмм</t>
+        </is>
+      </c>
+      <c r="D231" s="8" t="inlineStr">
+        <is>
+          <t>Ярус 3</t>
+        </is>
+      </c>
+      <c r="E231" s="8" t="inlineStr">
+        <is>
+          <t>клапан штуцерный</t>
+        </is>
+      </c>
+      <c r="F231" s="8" t="inlineStr">
+        <is>
+          <t>Ду20</t>
+        </is>
+      </c>
+      <c r="G231" s="10" t="inlineStr">
+        <is>
+          <t>Клапан муфтовый проходной запорный Ду20Ру16</t>
+        </is>
+      </c>
+      <c r="H231" s="8" t="inlineStr"/>
+      <c r="I231" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J231" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K231" s="13" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="L231" s="12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="M231" s="12" t="n">
+        <v>667</v>
+      </c>
+      <c r="N231" s="10" t="inlineStr">
+        <is>
+          <t>Ящик сплошной, с перегородками</t>
+        </is>
+      </c>
+      <c r="O231" s="8" t="inlineStr">
+        <is>
+          <t>Склад 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="8" t="n">
+        <v>229</v>
+      </c>
+      <c r="B232" s="9" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="C232" s="10" t="inlineStr">
+        <is>
+          <t>3. Прочее, по цене за килограмм</t>
+        </is>
+      </c>
+      <c r="D232" s="8" t="inlineStr">
+        <is>
+          <t>Ярус 2</t>
+        </is>
+      </c>
+      <c r="E232" s="8" t="inlineStr">
+        <is>
+          <t>клинкет (задвижка)</t>
+        </is>
+      </c>
+      <c r="F232" s="8" t="inlineStr">
+        <is>
+          <t>Ду100</t>
+        </is>
+      </c>
+      <c r="G232" s="10" t="inlineStr">
+        <is>
+          <t>Клинкет Ду 100, сталь</t>
+        </is>
+      </c>
+      <c r="H232" s="8" t="inlineStr"/>
+      <c r="I232" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J232" s="12" t="n">
+        <v>90</v>
+      </c>
+      <c r="K232" s="13" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="L232" s="12" t="n">
+        <v>60000</v>
+      </c>
+      <c r="M232" s="12" t="n">
+        <v>667</v>
+      </c>
+      <c r="N232" s="10" t="inlineStr">
+        <is>
+          <t>Поддон, прокладки между рядами</t>
+        </is>
+      </c>
+      <c r="O232" s="8" t="inlineStr">
+        <is>
+          <t>Фойе</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="8" t="n">
+        <v>230</v>
+      </c>
+      <c r="B233" s="9" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="C233" s="10" t="inlineStr">
+        <is>
+          <t>3. Прочее, по цене за килограмм</t>
+        </is>
+      </c>
+      <c r="D233" s="8" t="inlineStr">
+        <is>
+          <t>Ярус 2</t>
+        </is>
+      </c>
+      <c r="E233" s="8" t="inlineStr">
+        <is>
+          <t>клапан фланцевый</t>
+        </is>
+      </c>
+      <c r="F233" s="8" t="inlineStr">
+        <is>
+          <t>Ду125</t>
+        </is>
+      </c>
+      <c r="G233" s="10" t="inlineStr">
+        <is>
+          <t>Клапан фланцевый проходной Ду 125 (без чертежа)</t>
+        </is>
+      </c>
+      <c r="H233" s="8" t="inlineStr"/>
+      <c r="I233" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J233" s="12" t="n">
+        <v>55</v>
+      </c>
+      <c r="K233" s="13" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="L233" s="12" t="n">
+        <v>30000</v>
+      </c>
+      <c r="M233" s="12" t="n">
+        <v>545</v>
+      </c>
+      <c r="N233" s="10" t="inlineStr">
+        <is>
+          <t>Поддон, прокладки между рядами</t>
+        </is>
+      </c>
+      <c r="O233" s="8" t="inlineStr">
+        <is>
+          <t>Склад 1А/1Б</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="8" t="n">
+        <v>231</v>
+      </c>
+      <c r="B234" s="9" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="C234" s="10" t="inlineStr">
+        <is>
+          <t>3. Прочее, по цене за килограмм</t>
+        </is>
+      </c>
+      <c r="D234" s="8" t="inlineStr">
+        <is>
+          <t>Ярус 3</t>
+        </is>
+      </c>
+      <c r="E234" s="8" t="inlineStr">
+        <is>
+          <t>клапан фланцевый</t>
+        </is>
+      </c>
+      <c r="F234" s="8" t="inlineStr">
+        <is>
+          <t>Ду50</t>
+        </is>
+      </c>
+      <c r="G234" s="10" t="inlineStr">
+        <is>
+          <t>Клапан невозвратно-приемный фланцевый Ду 50 Ру1 (522-35.4043-01)</t>
+        </is>
+      </c>
+      <c r="H234" s="8" t="inlineStr"/>
+      <c r="I234" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="J234" s="12" t="n">
+        <v>84</v>
+      </c>
+      <c r="K234" s="13" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="L234" s="12" t="n">
+        <v>45000</v>
+      </c>
+      <c r="M234" s="12" t="n">
+        <v>536</v>
+      </c>
+      <c r="N234" s="10" t="inlineStr">
+        <is>
+          <t>Обрешетка на поддоне</t>
+        </is>
+      </c>
+      <c r="O234" s="8" t="inlineStr">
+        <is>
+          <t>Склад 1А/1Б</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="8" t="n">
+        <v>232</v>
+      </c>
+      <c r="B235" s="9" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="C235" s="10" t="inlineStr">
+        <is>
+          <t>3. Прочее, по цене за килограмм</t>
+        </is>
+      </c>
+      <c r="D235" s="8" t="inlineStr">
+        <is>
+          <t>Ярус 3</t>
+        </is>
+      </c>
+      <c r="E235" s="8" t="inlineStr">
+        <is>
+          <t>коробка клапанная</t>
+        </is>
+      </c>
+      <c r="F235" s="8" t="inlineStr"/>
+      <c r="G235" s="10" t="inlineStr">
+        <is>
+          <t>Коробка 2-х клапанная корпус</t>
+        </is>
+      </c>
+      <c r="H235" s="8" t="inlineStr"/>
+      <c r="I235" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J235" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="K235" s="13" t="n">
         <v>0.01</v>
       </c>
-      <c r="L228" s="12" t="n"/>
-      <c r="M228" s="12" t="n"/>
-      <c r="N228" s="10" t="inlineStr">
+      <c r="L235" s="12" t="n">
+        <v>20000</v>
+      </c>
+      <c r="M235" s="12" t="n">
+        <v>500</v>
+      </c>
+      <c r="N235" s="10" t="inlineStr">
         <is>
           <t>Ящик сплошной, с перегородками</t>
         </is>
       </c>
-      <c r="O228" s="8" t="inlineStr">
+      <c r="O235" s="8" t="inlineStr">
+        <is>
+          <t>Склад 1А/1Б</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="8" t="n">
+        <v>233</v>
+      </c>
+      <c r="B236" s="9" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="C236" s="10" t="inlineStr">
+        <is>
+          <t>3. Прочее, по цене за килограмм</t>
+        </is>
+      </c>
+      <c r="D236" s="8" t="inlineStr">
+        <is>
+          <t>Ярус 3</t>
+        </is>
+      </c>
+      <c r="E236" s="8" t="inlineStr">
+        <is>
+          <t>клапан штуцерный</t>
+        </is>
+      </c>
+      <c r="F236" s="8" t="inlineStr">
+        <is>
+          <t>Ду25</t>
+        </is>
+      </c>
+      <c r="G236" s="10" t="inlineStr">
+        <is>
+          <t>Клапан муфтовый проходной запорный Ду25Ру16</t>
+        </is>
+      </c>
+      <c r="H236" s="8" t="inlineStr"/>
+      <c r="I236" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J236" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="K236" s="13" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="L236" s="12" t="n">
+        <v>2500</v>
+      </c>
+      <c r="M236" s="12" t="n">
+        <v>500</v>
+      </c>
+      <c r="N236" s="10" t="inlineStr">
+        <is>
+          <t>Ящик сплошной, с перегородками</t>
+        </is>
+      </c>
+      <c r="O236" s="8" t="inlineStr">
         <is>
           <t>Склад 2</t>
         </is>
       </c>
     </row>
-    <row r="229">
-      <c r="G229" s="14" t="inlineStr">
+    <row r="237">
+      <c r="A237" s="8" t="n">
+        <v>234</v>
+      </c>
+      <c r="B237" s="9" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="C237" s="10" t="inlineStr">
+        <is>
+          <t>3. Прочее, по цене за килограмм</t>
+        </is>
+      </c>
+      <c r="D237" s="8" t="inlineStr">
+        <is>
+          <t>Ярус 3</t>
+        </is>
+      </c>
+      <c r="E237" s="8" t="inlineStr">
+        <is>
+          <t>клапан фланцевый</t>
+        </is>
+      </c>
+      <c r="F237" s="8" t="inlineStr">
+        <is>
+          <t>Ду65</t>
+        </is>
+      </c>
+      <c r="G237" s="10" t="inlineStr">
+        <is>
+          <t>Клапан невозвратно-приемный фланцевый Ду 65 Ру1 (522-03.023)</t>
+        </is>
+      </c>
+      <c r="H237" s="8" t="inlineStr"/>
+      <c r="I237" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J237" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="K237" s="13" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="L237" s="12" t="n">
+        <v>19500</v>
+      </c>
+      <c r="M237" s="12" t="n">
+        <v>488</v>
+      </c>
+      <c r="N237" s="10" t="inlineStr">
+        <is>
+          <t>Обрешетка на поддоне</t>
+        </is>
+      </c>
+      <c r="O237" s="8" t="inlineStr">
+        <is>
+          <t>Склад 1А/1Б</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="8" t="n">
+        <v>235</v>
+      </c>
+      <c r="B238" s="9" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="C238" s="10" t="inlineStr">
+        <is>
+          <t>3. Прочее, по цене за килограмм</t>
+        </is>
+      </c>
+      <c r="D238" s="8" t="inlineStr">
+        <is>
+          <t>Ярус 3</t>
+        </is>
+      </c>
+      <c r="E238" s="8" t="inlineStr">
+        <is>
+          <t>клапан фланцевый</t>
+        </is>
+      </c>
+      <c r="F238" s="8" t="inlineStr">
+        <is>
+          <t>Ду65</t>
+        </is>
+      </c>
+      <c r="G238" s="10" t="inlineStr">
+        <is>
+          <t>Клапан невозвратно-приемный фланцевый Ду 65 Ру1 (522-35.4044-01)</t>
+        </is>
+      </c>
+      <c r="H238" s="8" t="inlineStr"/>
+      <c r="I238" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J238" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="K238" s="13" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="L238" s="12" t="n">
+        <v>9750</v>
+      </c>
+      <c r="M238" s="12" t="n">
+        <v>488</v>
+      </c>
+      <c r="N238" s="10" t="inlineStr">
+        <is>
+          <t>Обрешетка на поддоне</t>
+        </is>
+      </c>
+      <c r="O238" s="8" t="inlineStr">
+        <is>
+          <t>Склад 1А/1Б</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="8" t="n">
+        <v>236</v>
+      </c>
+      <c r="B239" s="9" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="C239" s="10" t="inlineStr">
+        <is>
+          <t>3. Прочее, по цене за килограмм</t>
+        </is>
+      </c>
+      <c r="D239" s="8" t="inlineStr">
+        <is>
+          <t>Ярус 3</t>
+        </is>
+      </c>
+      <c r="E239" s="8" t="inlineStr">
+        <is>
+          <t>клапан штуцерный</t>
+        </is>
+      </c>
+      <c r="F239" s="8" t="inlineStr">
+        <is>
+          <t>Ду32</t>
+        </is>
+      </c>
+      <c r="G239" s="10" t="inlineStr">
+        <is>
+          <t>Клапан муфтовый проходной запорный Ду32Ру10</t>
+        </is>
+      </c>
+      <c r="H239" s="8" t="inlineStr"/>
+      <c r="I239" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J239" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K239" s="13" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="L239" s="12" t="n">
+        <v>1500</v>
+      </c>
+      <c r="M239" s="12" t="n">
+        <v>429</v>
+      </c>
+      <c r="N239" s="10" t="inlineStr">
+        <is>
+          <t>Ящик сплошной, с перегородками</t>
+        </is>
+      </c>
+      <c r="O239" s="8" t="inlineStr">
+        <is>
+          <t>Склад 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="8" t="n">
+        <v>237</v>
+      </c>
+      <c r="B240" s="9" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="C240" s="10" t="inlineStr">
+        <is>
+          <t>3. Прочее, по цене за килограмм</t>
+        </is>
+      </c>
+      <c r="D240" s="8" t="inlineStr">
+        <is>
+          <t>Ярус 1, на настил</t>
+        </is>
+      </c>
+      <c r="E240" s="8" t="inlineStr">
+        <is>
+          <t>клинкет (задвижка)</t>
+        </is>
+      </c>
+      <c r="F240" s="8" t="inlineStr">
+        <is>
+          <t>Ду300</t>
+        </is>
+      </c>
+      <c r="G240" s="10" t="inlineStr">
+        <is>
+          <t>Задвижка клинкетная стальная Ду300</t>
+        </is>
+      </c>
+      <c r="H240" s="8" t="inlineStr"/>
+      <c r="I240" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J240" s="12" t="n">
+        <v>600</v>
+      </c>
+      <c r="K240" s="13" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L240" s="12" t="n">
+        <v>150000</v>
+      </c>
+      <c r="M240" s="12" t="n">
+        <v>250</v>
+      </c>
+      <c r="N240" s="10" t="inlineStr">
+        <is>
+          <t>Поддон с обрешеткой, крепление к полу</t>
+        </is>
+      </c>
+      <c r="O240" s="8" t="inlineStr">
+        <is>
+          <t>Склад 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="8" t="n">
+        <v>238</v>
+      </c>
+      <c r="B241" s="9" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="C241" s="10" t="inlineStr">
+        <is>
+          <t>3. Прочее, по цене за килограмм</t>
+        </is>
+      </c>
+      <c r="D241" s="8" t="inlineStr">
+        <is>
+          <t>Ярус 3</t>
+        </is>
+      </c>
+      <c r="E241" s="8" t="inlineStr">
+        <is>
+          <t>клапан штуцерный</t>
+        </is>
+      </c>
+      <c r="F241" s="8" t="inlineStr">
+        <is>
+          <t>Ду15</t>
+        </is>
+      </c>
+      <c r="G241" s="10" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный проходной бессальниковый Ду15/1</t>
+        </is>
+      </c>
+      <c r="H241" s="8" t="inlineStr"/>
+      <c r="I241" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J241" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K241" s="13" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="L241" s="12" t="n"/>
+      <c r="M241" s="12" t="n"/>
+      <c r="N241" s="10" t="inlineStr">
+        <is>
+          <t>Ящик сплошной, с перегородками</t>
+        </is>
+      </c>
+      <c r="O241" s="8" t="inlineStr">
+        <is>
+          <t>Склад 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="8" t="n">
+        <v>239</v>
+      </c>
+      <c r="B242" s="9" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="C242" s="10" t="inlineStr">
+        <is>
+          <t>3. Прочее, по цене за килограмм</t>
+        </is>
+      </c>
+      <c r="D242" s="8" t="inlineStr">
+        <is>
+          <t>Ярус 2</t>
+        </is>
+      </c>
+      <c r="E242" s="8" t="inlineStr">
+        <is>
+          <t>клапан фланцевый</t>
+        </is>
+      </c>
+      <c r="F242" s="8" t="inlineStr">
+        <is>
+          <t>Ду100</t>
+        </is>
+      </c>
+      <c r="G242" s="10" t="inlineStr">
+        <is>
+          <t>Клапан фланцевый проходной титановые Ду100Ру10</t>
+        </is>
+      </c>
+      <c r="H242" s="8" t="inlineStr"/>
+      <c r="I242" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J242" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="K242" s="13" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="L242" s="12" t="n"/>
+      <c r="M242" s="12" t="n"/>
+      <c r="N242" s="10" t="inlineStr">
+        <is>
+          <t>Поддон, прокладки между рядами</t>
+        </is>
+      </c>
+      <c r="O242" s="8" t="inlineStr">
+        <is>
+          <t>Склад 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="8" t="n">
+        <v>240</v>
+      </c>
+      <c r="B243" s="9" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="C243" s="10" t="inlineStr">
+        <is>
+          <t>3. Прочее, по цене за килограмм</t>
+        </is>
+      </c>
+      <c r="D243" s="8" t="inlineStr">
+        <is>
+          <t>Ярус 3</t>
+        </is>
+      </c>
+      <c r="E243" s="8" t="inlineStr">
+        <is>
+          <t>клапан штуцерный</t>
+        </is>
+      </c>
+      <c r="F243" s="8" t="inlineStr">
+        <is>
+          <t>Ду15</t>
+        </is>
+      </c>
+      <c r="G243" s="10" t="inlineStr">
+        <is>
+          <t>(Кнопка)Клапан самозакрывающий проходной муфтовый Ду15Ру3</t>
+        </is>
+      </c>
+      <c r="H243" s="8" t="inlineStr"/>
+      <c r="I243" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J243" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K243" s="13" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="L243" s="12" t="n"/>
+      <c r="M243" s="12" t="n"/>
+      <c r="N243" s="10" t="inlineStr">
+        <is>
+          <t>Ящик сплошной, с перегородками</t>
+        </is>
+      </c>
+      <c r="O243" s="8" t="inlineStr">
+        <is>
+          <t>Склад 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="8" t="n">
+        <v>241</v>
+      </c>
+      <c r="B244" s="9" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="C244" s="10" t="inlineStr">
+        <is>
+          <t>3. Прочее, по цене за килограмм</t>
+        </is>
+      </c>
+      <c r="D244" s="8" t="inlineStr">
+        <is>
+          <t>Ярус 3</t>
+        </is>
+      </c>
+      <c r="E244" s="8" t="inlineStr">
+        <is>
+          <t>клапан штуцерный</t>
+        </is>
+      </c>
+      <c r="F244" s="8" t="inlineStr"/>
+      <c r="G244" s="10" t="inlineStr">
+        <is>
+          <t>Клапан дроссельный угловой штуцерный</t>
+        </is>
+      </c>
+      <c r="H244" s="8" t="inlineStr"/>
+      <c r="I244" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J244" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K244" s="13" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L244" s="12" t="n"/>
+      <c r="M244" s="12" t="n"/>
+      <c r="N244" s="10" t="inlineStr">
+        <is>
+          <t>Ящик сплошной, с перегородками</t>
+        </is>
+      </c>
+      <c r="O244" s="8" t="inlineStr">
+        <is>
+          <t>Склад 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="8" t="n">
+        <v>242</v>
+      </c>
+      <c r="B245" s="9" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="C245" s="10" t="inlineStr">
+        <is>
+          <t>3. Прочее, по цене за килограмм</t>
+        </is>
+      </c>
+      <c r="D245" s="8" t="inlineStr">
+        <is>
+          <t>Ярус 3</t>
+        </is>
+      </c>
+      <c r="E245" s="8" t="inlineStr">
+        <is>
+          <t>клапан штуцерный</t>
+        </is>
+      </c>
+      <c r="F245" s="8" t="inlineStr">
+        <is>
+          <t>Ду10</t>
+        </is>
+      </c>
+      <c r="G245" s="10" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный угловой Ду10 Ру100</t>
+        </is>
+      </c>
+      <c r="H245" s="8" t="inlineStr"/>
+      <c r="I245" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J245" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K245" s="13" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="L245" s="12" t="n"/>
+      <c r="M245" s="12" t="n"/>
+      <c r="N245" s="10" t="inlineStr">
+        <is>
+          <t>Ящик сплошной, с перегородками</t>
+        </is>
+      </c>
+      <c r="O245" s="8" t="inlineStr">
+        <is>
+          <t>Склад 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="8" t="n">
+        <v>243</v>
+      </c>
+      <c r="B246" s="9" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="C246" s="10" t="inlineStr">
+        <is>
+          <t>3. Прочее, по цене за килограмм</t>
+        </is>
+      </c>
+      <c r="D246" s="8" t="inlineStr">
+        <is>
+          <t>Ярус 3</t>
+        </is>
+      </c>
+      <c r="E246" s="8" t="inlineStr">
+        <is>
+          <t>клапан штуцерный</t>
+        </is>
+      </c>
+      <c r="F246" s="8" t="inlineStr"/>
+      <c r="G246" s="10" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный угловой Ду НЕРЖ</t>
+        </is>
+      </c>
+      <c r="H246" s="8" t="inlineStr"/>
+      <c r="I246" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J246" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K246" s="13" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L246" s="12" t="n"/>
+      <c r="M246" s="12" t="n"/>
+      <c r="N246" s="10" t="inlineStr">
+        <is>
+          <t>Ящик сплошной, с перегородками</t>
+        </is>
+      </c>
+      <c r="O246" s="8" t="inlineStr">
+        <is>
+          <t>Склад 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="8" t="n">
+        <v>244</v>
+      </c>
+      <c r="B247" s="9" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="C247" s="10" t="inlineStr">
+        <is>
+          <t>3. Прочее, по цене за килограмм</t>
+        </is>
+      </c>
+      <c r="D247" s="8" t="inlineStr">
+        <is>
+          <t>Ярус 3</t>
+        </is>
+      </c>
+      <c r="E247" s="8" t="inlineStr">
+        <is>
+          <t>прочая арматура</t>
+        </is>
+      </c>
+      <c r="F247" s="8" t="inlineStr">
+        <is>
+          <t>Ду20</t>
+        </is>
+      </c>
+      <c r="G247" s="10" t="inlineStr">
+        <is>
+          <t>Клапан с электромагнитным ручным управлением Ду20/10 перем. 220В</t>
+        </is>
+      </c>
+      <c r="H247" s="8" t="inlineStr"/>
+      <c r="I247" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J247" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="K247" s="13" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="L247" s="12" t="n"/>
+      <c r="M247" s="12" t="n"/>
+      <c r="N247" s="10" t="inlineStr">
+        <is>
+          <t>Ящик сплошной, с перегородками</t>
+        </is>
+      </c>
+      <c r="O247" s="8" t="inlineStr">
+        <is>
+          <t>Склад 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="8" t="n">
+        <v>245</v>
+      </c>
+      <c r="B248" s="9" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="C248" s="10" t="inlineStr">
+        <is>
+          <t>3. Прочее, по цене за килограмм</t>
+        </is>
+      </c>
+      <c r="D248" s="8" t="inlineStr">
+        <is>
+          <t>Ярус 3</t>
+        </is>
+      </c>
+      <c r="E248" s="8" t="inlineStr">
+        <is>
+          <t>прочая арматура</t>
+        </is>
+      </c>
+      <c r="F248" s="8" t="inlineStr"/>
+      <c r="G248" s="10" t="inlineStr">
+        <is>
+          <t>Клапан</t>
+        </is>
+      </c>
+      <c r="H248" s="8" t="inlineStr"/>
+      <c r="I248" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J248" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="K248" s="13" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L248" s="12" t="n"/>
+      <c r="M248" s="12" t="n"/>
+      <c r="N248" s="10" t="inlineStr">
+        <is>
+          <t>Ящик сплошной, с перегородками</t>
+        </is>
+      </c>
+      <c r="O248" s="8" t="inlineStr">
+        <is>
+          <t>Склад 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="8" t="n">
+        <v>246</v>
+      </c>
+      <c r="B249" s="9" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="C249" s="10" t="inlineStr">
+        <is>
+          <t>3. Прочее, по цене за килограмм</t>
+        </is>
+      </c>
+      <c r="D249" s="8" t="inlineStr">
+        <is>
+          <t>Ярус 3</t>
+        </is>
+      </c>
+      <c r="E249" s="8" t="inlineStr">
+        <is>
+          <t>прочая арматура</t>
+        </is>
+      </c>
+      <c r="F249" s="8" t="inlineStr"/>
+      <c r="G249" s="10" t="inlineStr">
+        <is>
+          <t>Клапан фреоновый саленоидный</t>
+        </is>
+      </c>
+      <c r="H249" s="8" t="inlineStr"/>
+      <c r="I249" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J249" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="K249" s="13" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="L249" s="12" t="n"/>
+      <c r="M249" s="12" t="n"/>
+      <c r="N249" s="10" t="inlineStr">
+        <is>
+          <t>Ящик сплошной, с перегородками</t>
+        </is>
+      </c>
+      <c r="O249" s="8" t="inlineStr">
+        <is>
+          <t>Склад 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="G250" s="14" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="I229" s="15">
-        <f>SUM(I4:I228)</f>
+      <c r="I250" s="15">
+        <f>SUM(I4:I249)</f>
         <v/>
       </c>
-      <c r="J229" s="15">
-        <f>SUM(J4:J228)</f>
+      <c r="J250" s="15">
+        <f>SUM(J4:J249)</f>
         <v/>
       </c>
-      <c r="L229" s="15">
-        <f>SUM(L4:L228)</f>
+      <c r="L250" s="15">
+        <f>SUM(L4:L249)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:O228"/>
+  <autoFilter ref="A3:O249"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -14820,7 +16084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O50"/>
+  <dimension ref="A1:O29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -14940,48 +16204,48 @@
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 1, на настил</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>кингстон</t>
+          <t>клинкет (задвижка)</t>
         </is>
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t>Ду50</t>
+          <t>Ду300</t>
         </is>
       </c>
       <c r="G4" s="10" t="inlineStr">
         <is>
-          <t>Кингстон донный фланцевый Ду50 Ру2,5</t>
+          <t>Клинкет Ду 300</t>
         </is>
       </c>
       <c r="H4" s="8" t="inlineStr"/>
       <c r="I4" s="8" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="J4" s="12" t="n">
-        <v>20</v>
+        <v>4800</v>
       </c>
       <c r="K4" s="13" t="n">
-        <v>0.012</v>
+        <v>5.6</v>
       </c>
       <c r="L4" s="12" t="n">
-        <v>17500</v>
+        <v>4000000</v>
       </c>
       <c r="M4" s="12" t="n">
-        <v>875</v>
+        <v>833</v>
       </c>
       <c r="N4" s="10" t="inlineStr">
         <is>
-          <t>Обрешетка на поддоне</t>
+          <t>Поддон с обрешеткой, крепление к полу</t>
         </is>
       </c>
       <c r="O4" s="8" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Фойе</t>
         </is>
       </c>
     </row>
@@ -15001,40 +16265,36 @@
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>клинкет (задвижка)</t>
+          <t>клапан фланцевый</t>
         </is>
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>Ду80</t>
+          <t>Ду50</t>
         </is>
       </c>
       <c r="G5" s="10" t="inlineStr">
         <is>
-          <t>Задвижка клинкетная Ду80 ( в разборе)</t>
+          <t>Клапан фланцевый проходной титановые Ду50Ру10</t>
         </is>
       </c>
       <c r="H5" s="8" t="inlineStr"/>
       <c r="I5" s="8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J5" s="12" t="n">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="K5" s="13" t="n">
         <v>0.06</v>
       </c>
-      <c r="L5" s="12" t="n">
-        <v>48000</v>
-      </c>
-      <c r="M5" s="12" t="n">
-        <v>857</v>
-      </c>
+      <c r="L5" s="12" t="n"/>
+      <c r="M5" s="12" t="n"/>
       <c r="N5" s="10" t="inlineStr">
         <is>
           <t>Обрешетка на поддоне</t>
@@ -15042,7 +16302,7 @@
       </c>
       <c r="O5" s="8" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -15062,48 +16322,44 @@
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>прочая арматура</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>Ду100</t>
+          <t>Ду20</t>
         </is>
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
-          <t>Клапана невозвратный проходной фланцевый Ду100 Ру10 (522-03.205)</t>
+          <t>Клапан редукционный штуц.проход.односедельный Ду20Ру400 у входа</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr"/>
       <c r="I6" s="8" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J6" s="12" t="n">
-        <v>200</v>
+        <v>45</v>
       </c>
       <c r="K6" s="13" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="L6" s="12" t="n">
-        <v>170000</v>
-      </c>
-      <c r="M6" s="12" t="n">
-        <v>850</v>
-      </c>
+        <v>0.018</v>
+      </c>
+      <c r="L6" s="12" t="n"/>
+      <c r="M6" s="12" t="n"/>
       <c r="N6" s="10" t="inlineStr">
         <is>
-          <t>Поддон, прокладки между рядами</t>
+          <t>Ящик сплошной, с перегородками</t>
         </is>
       </c>
       <c r="O6" s="8" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -15123,48 +16379,44 @@
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>прочая арматура</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>Ду125</t>
+          <t>Ду20</t>
         </is>
       </c>
       <c r="G7" s="10" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду125</t>
+          <t>Клапан пусковой Ду20Ру125</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr"/>
       <c r="I7" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J7" s="12" t="n">
-        <v>330</v>
+        <v>35</v>
       </c>
       <c r="K7" s="13" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="L7" s="12" t="n">
-        <v>276000</v>
-      </c>
-      <c r="M7" s="12" t="n">
-        <v>836</v>
-      </c>
+        <v>0.014</v>
+      </c>
+      <c r="L7" s="12" t="n"/>
+      <c r="M7" s="12" t="n"/>
       <c r="N7" s="10" t="inlineStr">
         <is>
-          <t>Поддон, прокладки между рядами</t>
+          <t>Ящик сплошной, с перегородками</t>
         </is>
       </c>
       <c r="O7" s="8" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -15184,48 +16436,44 @@
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>прочая арматура</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>Ду125</t>
+          <t>Ду32</t>
         </is>
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду125 Ру10</t>
+          <t>Клапан пусковой Ду32Ру125</t>
         </is>
       </c>
       <c r="H8" s="8" t="inlineStr"/>
       <c r="I8" s="8" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J8" s="12" t="n">
-        <v>165</v>
+        <v>40</v>
       </c>
       <c r="K8" s="13" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="L8" s="12" t="n">
-        <v>138000</v>
-      </c>
-      <c r="M8" s="12" t="n">
-        <v>836</v>
-      </c>
+        <v>0.04</v>
+      </c>
+      <c r="L8" s="12" t="n"/>
+      <c r="M8" s="12" t="n"/>
       <c r="N8" s="10" t="inlineStr">
         <is>
-          <t>Поддон, прокладки между рядами</t>
+          <t>Ящик сплошной, с перегородками</t>
         </is>
       </c>
       <c r="O8" s="8" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -15245,48 +16493,44 @@
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>Ярус 1, на пол</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>клинкет (задвижка)</t>
+          <t>прочая арматура</t>
         </is>
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>Ду300</t>
+          <t>Ду65</t>
         </is>
       </c>
       <c r="G9" s="10" t="inlineStr">
         <is>
-          <t>Клинкет Ду 300</t>
+          <t>Клапан паровой Ду65Ру10</t>
         </is>
       </c>
       <c r="H9" s="8" t="inlineStr"/>
       <c r="I9" s="8" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="J9" s="12" t="n">
-        <v>4800</v>
+        <v>5</v>
       </c>
       <c r="K9" s="13" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="L9" s="12" t="n">
-        <v>4000000</v>
-      </c>
-      <c r="M9" s="12" t="n">
-        <v>833</v>
-      </c>
+        <v>0.02</v>
+      </c>
+      <c r="L9" s="12" t="n"/>
+      <c r="M9" s="12" t="n"/>
       <c r="N9" s="10" t="inlineStr">
         <is>
-          <t>Поддон с обрешеткой, крепление к полу</t>
+          <t>Обрешетка на поддоне</t>
         </is>
       </c>
       <c r="O9" s="8" t="inlineStr">
         <is>
-          <t>Фойе</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -15306,7 +16550,7 @@
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
@@ -15316,12 +16560,12 @@
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>Ду80</t>
+          <t>Ду50</t>
         </is>
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду80 Ру 40 сталь (521-35.3437)</t>
+          <t>Клапан фланц. концевой пожарный угловой Ду50 Ру25</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr"/>
@@ -15329,17 +16573,13 @@
         <v>1</v>
       </c>
       <c r="J10" s="12" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="K10" s="13" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="L10" s="12" t="n">
-        <v>22000</v>
-      </c>
-      <c r="M10" s="12" t="n">
-        <v>786</v>
-      </c>
+        <v>0.012</v>
+      </c>
+      <c r="L10" s="12" t="n"/>
+      <c r="M10" s="12" t="n"/>
       <c r="N10" s="10" t="inlineStr">
         <is>
           <t>Обрешетка на поддоне</t>
@@ -15347,7 +16587,7 @@
       </c>
       <c r="O10" s="8" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -15367,7 +16607,7 @@
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
@@ -15377,12 +16617,12 @@
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>Ду80</t>
+          <t>Ду50</t>
         </is>
       </c>
       <c r="G11" s="10" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду80 Ру 40 сталь (522-01.101)</t>
+          <t>Клапан фланц. концевой пожарный угловой Ду50 Ру25</t>
         </is>
       </c>
       <c r="H11" s="8" t="inlineStr"/>
@@ -15390,17 +16630,13 @@
         <v>1</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="K11" s="13" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="L11" s="12" t="n">
-        <v>22000</v>
-      </c>
-      <c r="M11" s="12" t="n">
-        <v>786</v>
-      </c>
+        <v>0.012</v>
+      </c>
+      <c r="L11" s="12" t="n"/>
+      <c r="M11" s="12" t="n"/>
       <c r="N11" s="10" t="inlineStr">
         <is>
           <t>Обрешетка на поддоне</t>
@@ -15408,7 +16644,7 @@
       </c>
       <c r="O11" s="8" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -15428,22 +16664,22 @@
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>клинкет (задвижка)</t>
+          <t>клапан фланцевый</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>Ду80</t>
+          <t>Ду32</t>
         </is>
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>Задвижка клинкетная ДУ 80, сталь</t>
+          <t>Клапан фланц. концевой пожарный угловой Ду32 Ру10</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr"/>
@@ -15451,25 +16687,21 @@
         <v>1</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="K12" s="13" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="L12" s="12" t="n">
-        <v>22000</v>
-      </c>
-      <c r="M12" s="12" t="n">
-        <v>786</v>
-      </c>
+        <v>0.005</v>
+      </c>
+      <c r="L12" s="12" t="n"/>
+      <c r="M12" s="12" t="n"/>
       <c r="N12" s="10" t="inlineStr">
         <is>
-          <t>Обрешетка на поддоне</t>
+          <t>Ящик сплошной, с перегородками</t>
         </is>
       </c>
       <c r="O12" s="8" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -15489,48 +16721,44 @@
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>клинкет (задвижка)</t>
+          <t>клапан фланцевый</t>
         </is>
       </c>
       <c r="F13" s="8" t="inlineStr">
         <is>
-          <t>Ду100</t>
+          <t>Ду32</t>
         </is>
       </c>
       <c r="G13" s="10" t="inlineStr">
         <is>
-          <t>Задвижка клинкетная Ду100 без штока и блинов ( в разборе)</t>
+          <t>Клапан фланц. концевой пожарный угловой Ду32 Ру16</t>
         </is>
       </c>
       <c r="H13" s="8" t="inlineStr"/>
       <c r="I13" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="K13" s="13" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="L13" s="12" t="n">
-        <v>35000</v>
-      </c>
-      <c r="M13" s="12" t="n">
-        <v>778</v>
-      </c>
+        <v>0.01</v>
+      </c>
+      <c r="L13" s="12" t="n"/>
+      <c r="M13" s="12" t="n"/>
       <c r="N13" s="10" t="inlineStr">
         <is>
-          <t>Поддон, прокладки между рядами</t>
+          <t>Ящик сплошной, с перегородками</t>
         </is>
       </c>
       <c r="O13" s="8" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -15550,43 +16778,39 @@
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>коробка клапанная</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>Ду125</t>
+          <t>Ду50</t>
         </is>
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду125 ок.входа</t>
+          <t>Коробка 3-х клап.фланцевая Ду50</t>
         </is>
       </c>
       <c r="H14" s="8" t="inlineStr"/>
       <c r="I14" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="K14" s="13" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="L14" s="12" t="n">
-        <v>75000</v>
-      </c>
-      <c r="M14" s="12" t="n">
-        <v>682</v>
-      </c>
+        <v>0.036</v>
+      </c>
+      <c r="L14" s="12" t="n"/>
+      <c r="M14" s="12" t="n"/>
       <c r="N14" s="10" t="inlineStr">
         <is>
-          <t>Поддон, прокладки между рядами</t>
+          <t>Обрешетка на поддоне</t>
         </is>
       </c>
       <c r="O14" s="8" t="inlineStr">
@@ -15611,48 +16835,44 @@
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>клинкет (задвижка)</t>
+          <t>коробка клапанная</t>
         </is>
       </c>
       <c r="F15" s="8" t="inlineStr">
         <is>
-          <t>Ду100</t>
+          <t>Ду80</t>
         </is>
       </c>
       <c r="G15" s="10" t="inlineStr">
         <is>
-          <t>Клинкет Ду 100, сталь</t>
+          <t>Коробка 3-х клап.фланцевая Ду80</t>
         </is>
       </c>
       <c r="H15" s="8" t="inlineStr"/>
       <c r="I15" s="8" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>90</v>
+        <v>360</v>
       </c>
       <c r="K15" s="13" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="L15" s="12" t="n">
-        <v>60000</v>
-      </c>
-      <c r="M15" s="12" t="n">
-        <v>667</v>
-      </c>
+        <v>0.24</v>
+      </c>
+      <c r="L15" s="12" t="n"/>
+      <c r="M15" s="12" t="n"/>
       <c r="N15" s="10" t="inlineStr">
         <is>
-          <t>Поддон, прокладки между рядами</t>
+          <t>Обрешетка на поддоне</t>
         </is>
       </c>
       <c r="O15" s="8" t="inlineStr">
         <is>
-          <t>Фойе</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -15677,17 +16897,17 @@
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>коробка клапанная</t>
         </is>
       </c>
       <c r="F16" s="8" t="inlineStr">
         <is>
-          <t>Ду125</t>
+          <t>Ду100</t>
         </is>
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду 125 (без чертежа)</t>
+          <t>Коробка 3-х клап.фланцевая Ду100</t>
         </is>
       </c>
       <c r="H16" s="8" t="inlineStr"/>
@@ -15695,17 +16915,13 @@
         <v>1</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="K16" s="13" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="L16" s="12" t="n">
-        <v>30000</v>
-      </c>
-      <c r="M16" s="12" t="n">
-        <v>545</v>
-      </c>
+        <v>0.045</v>
+      </c>
+      <c r="L16" s="12" t="n"/>
+      <c r="M16" s="12" t="n"/>
       <c r="N16" s="10" t="inlineStr">
         <is>
           <t>Поддон, прокладки между рядами</t>
@@ -15713,7 +16929,7 @@
       </c>
       <c r="O16" s="8" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -15733,12 +16949,12 @@
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>коробка клапанная</t>
         </is>
       </c>
       <c r="F17" s="8" t="inlineStr">
@@ -15748,25 +16964,21 @@
       </c>
       <c r="G17" s="10" t="inlineStr">
         <is>
-          <t>Клапан невозвратно-приемный фланцевый Ду 50 Ру1 (522-35.4043-01)</t>
+          <t>Коробка 2-х клапановая фланцевая Ду50</t>
         </is>
       </c>
       <c r="H17" s="8" t="inlineStr"/>
       <c r="I17" s="8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="K17" s="13" t="n">
-        <v>0.07199999999999999</v>
-      </c>
-      <c r="L17" s="12" t="n">
-        <v>45000</v>
-      </c>
-      <c r="M17" s="12" t="n">
-        <v>536</v>
-      </c>
+        <v>0.024</v>
+      </c>
+      <c r="L17" s="12" t="n"/>
+      <c r="M17" s="12" t="n"/>
       <c r="N17" s="10" t="inlineStr">
         <is>
           <t>Обрешетка на поддоне</t>
@@ -15774,7 +16986,7 @@
       </c>
       <c r="O17" s="8" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -15794,7 +17006,7 @@
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
@@ -15802,36 +17014,36 @@
           <t>коробка клапанная</t>
         </is>
       </c>
-      <c r="F18" s="8" t="inlineStr"/>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>Ду80</t>
+        </is>
+      </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>Коробка 2-х клапанная корпус</t>
+          <t>Коробка 2-х клапановая фланцевая Ду80</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr"/>
       <c r="I18" s="8" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>40</v>
+        <v>585</v>
       </c>
       <c r="K18" s="13" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L18" s="12" t="n">
-        <v>20000</v>
-      </c>
-      <c r="M18" s="12" t="n">
-        <v>500</v>
-      </c>
+        <v>0.39</v>
+      </c>
+      <c r="L18" s="12" t="n"/>
+      <c r="M18" s="12" t="n"/>
       <c r="N18" s="10" t="inlineStr">
         <is>
-          <t>Ящик сплошной, с перегородками</t>
+          <t>Обрешетка на поддоне</t>
         </is>
       </c>
       <c r="O18" s="8" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -15851,48 +17063,40 @@
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
-        </is>
-      </c>
-      <c r="F19" s="8" t="inlineStr">
-        <is>
-          <t>Ду65</t>
-        </is>
-      </c>
+          <t>прочая арматура</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="inlineStr"/>
       <c r="G19" s="10" t="inlineStr">
         <is>
-          <t>Клапан невозвратно-приемный фланцевый Ду 65 Ру1 (522-03.023)</t>
+          <t>Кланан Рр18-2 45/25</t>
         </is>
       </c>
       <c r="H19" s="8" t="inlineStr"/>
       <c r="I19" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="K19" s="13" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="L19" s="12" t="n">
-        <v>19500</v>
-      </c>
-      <c r="M19" s="12" t="n">
-        <v>488</v>
-      </c>
+        <v>0.01</v>
+      </c>
+      <c r="L19" s="12" t="n"/>
+      <c r="M19" s="12" t="n"/>
       <c r="N19" s="10" t="inlineStr">
         <is>
-          <t>Обрешетка на поддоне</t>
+          <t>Ящик сплошной, с перегородками</t>
         </is>
       </c>
       <c r="O19" s="8" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -15912,48 +17116,40 @@
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
-        </is>
-      </c>
-      <c r="F20" s="8" t="inlineStr">
-        <is>
-          <t>Ду65</t>
-        </is>
-      </c>
+          <t>прочая арматура</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="inlineStr"/>
       <c r="G20" s="10" t="inlineStr">
         <is>
-          <t>Клапан невозвратно-приемный фланцевый Ду 65 Ру1 (522-35.4044-01)</t>
+          <t>Клапан электромагнитный б/у</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr"/>
       <c r="I20" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J20" s="12" t="n">
         <v>20</v>
       </c>
       <c r="K20" s="13" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L20" s="12" t="n">
-        <v>9750</v>
-      </c>
-      <c r="M20" s="12" t="n">
-        <v>488</v>
-      </c>
+        <v>0.04</v>
+      </c>
+      <c r="L20" s="12" t="n"/>
+      <c r="M20" s="12" t="n"/>
       <c r="N20" s="10" t="inlineStr">
         <is>
-          <t>Обрешетка на поддоне</t>
+          <t>Ящик сплошной, с перегородками</t>
         </is>
       </c>
       <c r="O20" s="8" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -15973,48 +17169,44 @@
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>Ярус 1, на пол</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>клинкет (задвижка)</t>
+          <t>клапан штуцерный</t>
         </is>
       </c>
       <c r="F21" s="8" t="inlineStr">
         <is>
-          <t>Ду300</t>
+          <t>Ду50</t>
         </is>
       </c>
       <c r="G21" s="10" t="inlineStr">
         <is>
-          <t>Задвижка клинкетная стальная Ду300</t>
+          <t>Клапан невозв-запорн.с присоед.под дюрит прох. Ду 50</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr"/>
       <c r="I21" s="8" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>600</v>
+        <v>70</v>
       </c>
       <c r="K21" s="13" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="L21" s="12" t="n">
-        <v>150000</v>
-      </c>
-      <c r="M21" s="12" t="n">
-        <v>250</v>
-      </c>
+        <v>0.12</v>
+      </c>
+      <c r="L21" s="12" t="n"/>
+      <c r="M21" s="12" t="n"/>
       <c r="N21" s="10" t="inlineStr">
         <is>
-          <t>Поддон с обрешеткой, крепление к полу</t>
+          <t>Обрешетка на поддоне</t>
         </is>
       </c>
       <c r="O21" s="8" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -16034,33 +17226,33 @@
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>клапан штуцерный</t>
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr">
         <is>
-          <t>Ду50</t>
+          <t>Ду65</t>
         </is>
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной титановые Ду50Ру10</t>
+          <t>Клапан запорн.с присоед.под дюрит прох. Ду65</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr"/>
       <c r="I22" s="8" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>70</v>
+        <v>200</v>
       </c>
       <c r="K22" s="13" t="n">
-        <v>0.06</v>
+        <v>0.4</v>
       </c>
       <c r="L22" s="12" t="n"/>
       <c r="M22" s="12" t="n"/>
@@ -16071,7 +17263,7 @@
       </c>
       <c r="O22" s="8" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -16091,22 +17283,22 @@
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>коробка клапанная</t>
         </is>
       </c>
       <c r="F23" s="8" t="inlineStr">
         <is>
-          <t>Ду100</t>
+          <t>Ду50</t>
         </is>
       </c>
       <c r="G23" s="10" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной титановые Ду100Ру10</t>
+          <t>Коробка 3-х клап.фланцевая запорная Ду50 Ру6</t>
         </is>
       </c>
       <c r="H23" s="8" t="inlineStr"/>
@@ -16114,21 +17306,21 @@
         <v>1</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="K23" s="13" t="n">
-        <v>0.045</v>
+        <v>0.012</v>
       </c>
       <c r="L23" s="12" t="n"/>
       <c r="M23" s="12" t="n"/>
       <c r="N23" s="10" t="inlineStr">
         <is>
-          <t>Поддон, прокладки между рядами</t>
+          <t>Обрешетка на поддоне</t>
         </is>
       </c>
       <c r="O23" s="8" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -16148,44 +17340,44 @@
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>прочая арматура</t>
+          <t>коробка клапанная</t>
         </is>
       </c>
       <c r="F24" s="8" t="inlineStr">
         <is>
-          <t>Ду20</t>
+          <t>Ду50</t>
         </is>
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
-          <t>Клапан редукционный штуц.проход.односедельный Ду20Ру400 у входа</t>
+          <t>Коробка 3-х клап.фланцевая запорная Ду50 Ру6</t>
         </is>
       </c>
       <c r="H24" s="8" t="inlineStr"/>
       <c r="I24" s="8" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="K24" s="13" t="n">
-        <v>0.018</v>
+        <v>0.024</v>
       </c>
       <c r="L24" s="12" t="n"/>
       <c r="M24" s="12" t="n"/>
       <c r="N24" s="10" t="inlineStr">
         <is>
-          <t>Ящик сплошной, с перегородками</t>
+          <t>Обрешетка на поддоне</t>
         </is>
       </c>
       <c r="O24" s="8" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -16205,44 +17397,44 @@
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>прочая арматура</t>
+          <t>коробка клапанная</t>
         </is>
       </c>
       <c r="F25" s="8" t="inlineStr">
         <is>
-          <t>Ду20</t>
+          <t>Ду80</t>
         </is>
       </c>
       <c r="G25" s="10" t="inlineStr">
         <is>
-          <t>Клапан с электромагнитным ручным управлением Ду20/10 перем. 220В</t>
+          <t>Коробка 3-х клап.фланцевая невозврат.Ду80 Ру6</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr"/>
       <c r="I25" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>5</v>
+        <v>90</v>
       </c>
       <c r="K25" s="13" t="n">
-        <v>0.002</v>
+        <v>0.06</v>
       </c>
       <c r="L25" s="12" t="n"/>
       <c r="M25" s="12" t="n"/>
       <c r="N25" s="10" t="inlineStr">
         <is>
-          <t>Ящик сплошной, с перегородками</t>
+          <t>Обрешетка на поддоне</t>
         </is>
       </c>
       <c r="O25" s="8" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -16262,40 +17454,44 @@
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>прочая арматура</t>
-        </is>
-      </c>
-      <c r="F26" s="8" t="inlineStr"/>
+          <t>коробка клапанная</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>Ду80</t>
+        </is>
+      </c>
       <c r="G26" s="10" t="inlineStr">
         <is>
-          <t>Клапан</t>
+          <t>Коробка 3-х клап.фланцевая Ду80</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr"/>
       <c r="I26" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>5</v>
+        <v>135</v>
       </c>
       <c r="K26" s="13" t="n">
-        <v>0.01</v>
+        <v>0.09</v>
       </c>
       <c r="L26" s="12" t="n"/>
       <c r="M26" s="12" t="n"/>
       <c r="N26" s="10" t="inlineStr">
         <is>
-          <t>Ящик сплошной, с перегородками</t>
+          <t>Обрешетка на поддоне</t>
         </is>
       </c>
       <c r="O26" s="8" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -16315,29 +17511,29 @@
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 2</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>прочая арматура</t>
+          <t>клинкет (задвижка)</t>
         </is>
       </c>
       <c r="F27" s="8" t="inlineStr"/>
       <c r="G27" s="10" t="inlineStr">
         <is>
-          <t>Клапан фреоновый саленоидный</t>
+          <t>Задвижки (желтая) ок. крышек</t>
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr"/>
       <c r="I27" s="8" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>10</v>
+        <v>520</v>
       </c>
       <c r="K27" s="13" t="n">
-        <v>0.02</v>
+        <v>0.13</v>
       </c>
       <c r="L27" s="12" t="n"/>
       <c r="M27" s="12" t="n"/>
@@ -16348,7 +17544,7 @@
       </c>
       <c r="O27" s="8" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -16368,1253 +17564,68 @@
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 2</t>
         </is>
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>прочая арматура</t>
+          <t>клинкет (задвижка)</t>
         </is>
       </c>
       <c r="F28" s="8" t="inlineStr">
         <is>
-          <t>Ду20</t>
+          <t>Ду100</t>
         </is>
       </c>
       <c r="G28" s="10" t="inlineStr">
         <is>
-          <t>Клапан пусковой Ду20Ру125</t>
+          <t>Блины к клинкету Ду100</t>
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr"/>
       <c r="I28" s="8" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>35</v>
+        <v>495</v>
       </c>
       <c r="K28" s="13" t="n">
-        <v>0.014</v>
+        <v>0.495</v>
       </c>
       <c r="L28" s="12" t="n"/>
       <c r="M28" s="12" t="n"/>
       <c r="N28" s="10" t="inlineStr">
         <is>
-          <t>Ящик сплошной, с перегородками</t>
+          <t>Поддон, прокладки между рядами</t>
         </is>
       </c>
       <c r="O28" s="8" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад электрики</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="8" t="n">
-        <v>26</v>
-      </c>
-      <c r="B29" s="16" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="C29" s="10" t="inlineStr">
-        <is>
-          <t>3. Прочее, по цене за килограмм</t>
-        </is>
-      </c>
-      <c r="D29" s="8" t="inlineStr">
-        <is>
-          <t>Ярус 4, верх</t>
-        </is>
-      </c>
-      <c r="E29" s="8" t="inlineStr">
-        <is>
-          <t>прочая арматура</t>
-        </is>
-      </c>
-      <c r="F29" s="8" t="inlineStr">
-        <is>
-          <t>Ду32</t>
-        </is>
-      </c>
-      <c r="G29" s="10" t="inlineStr">
-        <is>
-          <t>Клапан пусковой Ду32Ру125</t>
-        </is>
-      </c>
-      <c r="H29" s="8" t="inlineStr"/>
-      <c r="I29" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="J29" s="12" t="n">
-        <v>40</v>
-      </c>
-      <c r="K29" s="13" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="L29" s="12" t="n"/>
-      <c r="M29" s="12" t="n"/>
-      <c r="N29" s="10" t="inlineStr">
-        <is>
-          <t>Ящик сплошной, с перегородками</t>
-        </is>
-      </c>
-      <c r="O29" s="8" t="inlineStr">
-        <is>
-          <t>Склад 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="8" t="n">
-        <v>27</v>
-      </c>
-      <c r="B30" s="16" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="C30" s="10" t="inlineStr">
-        <is>
-          <t>3. Прочее, по цене за килограмм</t>
-        </is>
-      </c>
-      <c r="D30" s="8" t="inlineStr">
-        <is>
-          <t>Ярус 4, верх</t>
-        </is>
-      </c>
-      <c r="E30" s="8" t="inlineStr">
-        <is>
-          <t>прочая арматура</t>
-        </is>
-      </c>
-      <c r="F30" s="8" t="inlineStr">
-        <is>
-          <t>Ду65</t>
-        </is>
-      </c>
-      <c r="G30" s="10" t="inlineStr">
-        <is>
-          <t>Клапан паровой Ду65Ру10</t>
-        </is>
-      </c>
-      <c r="H30" s="8" t="inlineStr"/>
-      <c r="I30" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J30" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="K30" s="13" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L30" s="12" t="n"/>
-      <c r="M30" s="12" t="n"/>
-      <c r="N30" s="10" t="inlineStr">
-        <is>
-          <t>Обрешетка на поддоне</t>
-        </is>
-      </c>
-      <c r="O30" s="8" t="inlineStr">
-        <is>
-          <t>Склад 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="8" t="n">
-        <v>28</v>
-      </c>
-      <c r="B31" s="16" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="C31" s="10" t="inlineStr">
-        <is>
-          <t>3. Прочее, по цене за килограмм</t>
-        </is>
-      </c>
-      <c r="D31" s="8" t="inlineStr">
-        <is>
-          <t>Ярус 4, верх</t>
-        </is>
-      </c>
-      <c r="E31" s="8" t="inlineStr">
-        <is>
-          <t>клапан фланцевый</t>
-        </is>
-      </c>
-      <c r="F31" s="8" t="inlineStr">
-        <is>
-          <t>Ду50</t>
-        </is>
-      </c>
-      <c r="G31" s="10" t="inlineStr">
-        <is>
-          <t>Клапан фланц. концевой пожарный угловой Ду50 Ру25</t>
-        </is>
-      </c>
-      <c r="H31" s="8" t="inlineStr"/>
-      <c r="I31" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J31" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="K31" s="13" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="L31" s="12" t="n"/>
-      <c r="M31" s="12" t="n"/>
-      <c r="N31" s="10" t="inlineStr">
-        <is>
-          <t>Обрешетка на поддоне</t>
-        </is>
-      </c>
-      <c r="O31" s="8" t="inlineStr">
-        <is>
-          <t>Склад 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="8" t="n">
-        <v>29</v>
-      </c>
-      <c r="B32" s="16" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="C32" s="10" t="inlineStr">
-        <is>
-          <t>3. Прочее, по цене за килограмм</t>
-        </is>
-      </c>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t>Ярус 4, верх</t>
-        </is>
-      </c>
-      <c r="E32" s="8" t="inlineStr">
-        <is>
-          <t>клапан фланцевый</t>
-        </is>
-      </c>
-      <c r="F32" s="8" t="inlineStr">
-        <is>
-          <t>Ду50</t>
-        </is>
-      </c>
-      <c r="G32" s="10" t="inlineStr">
-        <is>
-          <t>Клапан фланц. концевой пожарный угловой Ду50 Ру25</t>
-        </is>
-      </c>
-      <c r="H32" s="8" t="inlineStr"/>
-      <c r="I32" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J32" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="K32" s="13" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="L32" s="12" t="n"/>
-      <c r="M32" s="12" t="n"/>
-      <c r="N32" s="10" t="inlineStr">
-        <is>
-          <t>Обрешетка на поддоне</t>
-        </is>
-      </c>
-      <c r="O32" s="8" t="inlineStr">
-        <is>
-          <t>Склад 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="8" t="n">
-        <v>30</v>
-      </c>
-      <c r="B33" s="16" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="C33" s="10" t="inlineStr">
-        <is>
-          <t>3. Прочее, по цене за килограмм</t>
-        </is>
-      </c>
-      <c r="D33" s="8" t="inlineStr">
-        <is>
-          <t>Ярус 4, верх</t>
-        </is>
-      </c>
-      <c r="E33" s="8" t="inlineStr">
-        <is>
-          <t>клапан фланцевый</t>
-        </is>
-      </c>
-      <c r="F33" s="8" t="inlineStr">
-        <is>
-          <t>Ду32</t>
-        </is>
-      </c>
-      <c r="G33" s="10" t="inlineStr">
-        <is>
-          <t>Клапан фланц. концевой пожарный угловой Ду32 Ру10</t>
-        </is>
-      </c>
-      <c r="H33" s="8" t="inlineStr"/>
-      <c r="I33" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J33" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="K33" s="13" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="L33" s="12" t="n"/>
-      <c r="M33" s="12" t="n"/>
-      <c r="N33" s="10" t="inlineStr">
-        <is>
-          <t>Ящик сплошной, с перегородками</t>
-        </is>
-      </c>
-      <c r="O33" s="8" t="inlineStr">
-        <is>
-          <t>Склад 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="8" t="n">
-        <v>31</v>
-      </c>
-      <c r="B34" s="16" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="C34" s="10" t="inlineStr">
-        <is>
-          <t>3. Прочее, по цене за килограмм</t>
-        </is>
-      </c>
-      <c r="D34" s="8" t="inlineStr">
-        <is>
-          <t>Ярус 4, верх</t>
-        </is>
-      </c>
-      <c r="E34" s="8" t="inlineStr">
-        <is>
-          <t>клапан фланцевый</t>
-        </is>
-      </c>
-      <c r="F34" s="8" t="inlineStr">
-        <is>
-          <t>Ду32</t>
-        </is>
-      </c>
-      <c r="G34" s="10" t="inlineStr">
-        <is>
-          <t>Клапан фланц. концевой пожарный угловой Ду32 Ру16</t>
-        </is>
-      </c>
-      <c r="H34" s="8" t="inlineStr"/>
-      <c r="I34" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="J34" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="K34" s="13" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L34" s="12" t="n"/>
-      <c r="M34" s="12" t="n"/>
-      <c r="N34" s="10" t="inlineStr">
-        <is>
-          <t>Ящик сплошной, с перегородками</t>
-        </is>
-      </c>
-      <c r="O34" s="8" t="inlineStr">
-        <is>
-          <t>Склад 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="8" t="n">
-        <v>32</v>
-      </c>
-      <c r="B35" s="16" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="C35" s="10" t="inlineStr">
-        <is>
-          <t>3. Прочее, по цене за килограмм</t>
-        </is>
-      </c>
-      <c r="D35" s="8" t="inlineStr">
-        <is>
-          <t>Ярус 4, верх</t>
-        </is>
-      </c>
-      <c r="E35" s="8" t="inlineStr">
-        <is>
-          <t>коробка клапанная</t>
-        </is>
-      </c>
-      <c r="F35" s="8" t="inlineStr">
-        <is>
-          <t>Ду50</t>
-        </is>
-      </c>
-      <c r="G35" s="10" t="inlineStr">
-        <is>
-          <t>Коробка 3-х клап.фланцевая Ду50</t>
-        </is>
-      </c>
-      <c r="H35" s="8" t="inlineStr"/>
-      <c r="I35" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="J35" s="12" t="n">
-        <v>75</v>
-      </c>
-      <c r="K35" s="13" t="n">
-        <v>0.036</v>
-      </c>
-      <c r="L35" s="12" t="n"/>
-      <c r="M35" s="12" t="n"/>
-      <c r="N35" s="10" t="inlineStr">
-        <is>
-          <t>Обрешетка на поддоне</t>
-        </is>
-      </c>
-      <c r="O35" s="8" t="inlineStr">
-        <is>
-          <t>Склад 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="8" t="n">
-        <v>33</v>
-      </c>
-      <c r="B36" s="16" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="C36" s="10" t="inlineStr">
-        <is>
-          <t>3. Прочее, по цене за килограмм</t>
-        </is>
-      </c>
-      <c r="D36" s="8" t="inlineStr">
-        <is>
-          <t>Ярус 4, верх</t>
-        </is>
-      </c>
-      <c r="E36" s="8" t="inlineStr">
-        <is>
-          <t>коробка клапанная</t>
-        </is>
-      </c>
-      <c r="F36" s="8" t="inlineStr">
-        <is>
-          <t>Ду80</t>
-        </is>
-      </c>
-      <c r="G36" s="10" t="inlineStr">
-        <is>
-          <t>Коробка 3-х клап.фланцевая Ду80</t>
-        </is>
-      </c>
-      <c r="H36" s="8" t="inlineStr"/>
-      <c r="I36" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="J36" s="12" t="n">
-        <v>360</v>
-      </c>
-      <c r="K36" s="13" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="L36" s="12" t="n"/>
-      <c r="M36" s="12" t="n"/>
-      <c r="N36" s="10" t="inlineStr">
-        <is>
-          <t>Обрешетка на поддоне</t>
-        </is>
-      </c>
-      <c r="O36" s="8" t="inlineStr">
-        <is>
-          <t>Склад 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="8" t="n">
-        <v>34</v>
-      </c>
-      <c r="B37" s="16" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="C37" s="10" t="inlineStr">
-        <is>
-          <t>3. Прочее, по цене за килограмм</t>
-        </is>
-      </c>
-      <c r="D37" s="8" t="inlineStr">
-        <is>
-          <t>Ярус 2</t>
-        </is>
-      </c>
-      <c r="E37" s="8" t="inlineStr">
-        <is>
-          <t>коробка клапанная</t>
-        </is>
-      </c>
-      <c r="F37" s="8" t="inlineStr">
-        <is>
-          <t>Ду100</t>
-        </is>
-      </c>
-      <c r="G37" s="10" t="inlineStr">
-        <is>
-          <t>Коробка 3-х клап.фланцевая Ду100</t>
-        </is>
-      </c>
-      <c r="H37" s="8" t="inlineStr"/>
-      <c r="I37" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J37" s="12" t="n">
-        <v>60</v>
-      </c>
-      <c r="K37" s="13" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="L37" s="12" t="n"/>
-      <c r="M37" s="12" t="n"/>
-      <c r="N37" s="10" t="inlineStr">
-        <is>
-          <t>Поддон, прокладки между рядами</t>
-        </is>
-      </c>
-      <c r="O37" s="8" t="inlineStr">
-        <is>
-          <t>Склад 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="8" t="n">
-        <v>35</v>
-      </c>
-      <c r="B38" s="16" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="C38" s="10" t="inlineStr">
-        <is>
-          <t>3. Прочее, по цене за килограмм</t>
-        </is>
-      </c>
-      <c r="D38" s="8" t="inlineStr">
-        <is>
-          <t>Ярус 4, верх</t>
-        </is>
-      </c>
-      <c r="E38" s="8" t="inlineStr">
-        <is>
-          <t>коробка клапанная</t>
-        </is>
-      </c>
-      <c r="F38" s="8" t="inlineStr">
-        <is>
-          <t>Ду50</t>
-        </is>
-      </c>
-      <c r="G38" s="10" t="inlineStr">
-        <is>
-          <t>Коробка 2-х клапановая фланцевая Ду50</t>
-        </is>
-      </c>
-      <c r="H38" s="8" t="inlineStr"/>
-      <c r="I38" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="J38" s="12" t="n">
-        <v>50</v>
-      </c>
-      <c r="K38" s="13" t="n">
-        <v>0.024</v>
-      </c>
-      <c r="L38" s="12" t="n"/>
-      <c r="M38" s="12" t="n"/>
-      <c r="N38" s="10" t="inlineStr">
-        <is>
-          <t>Обрешетка на поддоне</t>
-        </is>
-      </c>
-      <c r="O38" s="8" t="inlineStr">
-        <is>
-          <t>Склад 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="8" t="n">
-        <v>36</v>
-      </c>
-      <c r="B39" s="16" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="C39" s="10" t="inlineStr">
-        <is>
-          <t>3. Прочее, по цене за килограмм</t>
-        </is>
-      </c>
-      <c r="D39" s="8" t="inlineStr">
-        <is>
-          <t>Ярус 4, верх</t>
-        </is>
-      </c>
-      <c r="E39" s="8" t="inlineStr">
-        <is>
-          <t>коробка клапанная</t>
-        </is>
-      </c>
-      <c r="F39" s="8" t="inlineStr">
-        <is>
-          <t>Ду80</t>
-        </is>
-      </c>
-      <c r="G39" s="10" t="inlineStr">
-        <is>
-          <t>Коробка 2-х клапановая фланцевая Ду80</t>
-        </is>
-      </c>
-      <c r="H39" s="8" t="inlineStr"/>
-      <c r="I39" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="J39" s="12" t="n">
-        <v>585</v>
-      </c>
-      <c r="K39" s="13" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="L39" s="12" t="n"/>
-      <c r="M39" s="12" t="n"/>
-      <c r="N39" s="10" t="inlineStr">
-        <is>
-          <t>Обрешетка на поддоне</t>
-        </is>
-      </c>
-      <c r="O39" s="8" t="inlineStr">
-        <is>
-          <t>Склад 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="8" t="n">
-        <v>37</v>
-      </c>
-      <c r="B40" s="16" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="C40" s="10" t="inlineStr">
-        <is>
-          <t>3. Прочее, по цене за килограмм</t>
-        </is>
-      </c>
-      <c r="D40" s="8" t="inlineStr">
-        <is>
-          <t>Ярус 4, верх</t>
-        </is>
-      </c>
-      <c r="E40" s="8" t="inlineStr">
-        <is>
-          <t>прочая арматура</t>
-        </is>
-      </c>
-      <c r="F40" s="8" t="inlineStr"/>
-      <c r="G40" s="10" t="inlineStr">
-        <is>
-          <t>Кланан Рр18-2 45/25</t>
-        </is>
-      </c>
-      <c r="H40" s="8" t="inlineStr"/>
-      <c r="I40" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J40" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="K40" s="13" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L40" s="12" t="n"/>
-      <c r="M40" s="12" t="n"/>
-      <c r="N40" s="10" t="inlineStr">
-        <is>
-          <t>Ящик сплошной, с перегородками</t>
-        </is>
-      </c>
-      <c r="O40" s="8" t="inlineStr">
-        <is>
-          <t>Склад 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="8" t="n">
-        <v>38</v>
-      </c>
-      <c r="B41" s="16" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="C41" s="10" t="inlineStr">
-        <is>
-          <t>3. Прочее, по цене за килограмм</t>
-        </is>
-      </c>
-      <c r="D41" s="8" t="inlineStr">
-        <is>
-          <t>Ярус 4, верх</t>
-        </is>
-      </c>
-      <c r="E41" s="8" t="inlineStr">
-        <is>
-          <t>прочая арматура</t>
-        </is>
-      </c>
-      <c r="F41" s="8" t="inlineStr"/>
-      <c r="G41" s="10" t="inlineStr">
-        <is>
-          <t>Клапан электромагнитный б/у</t>
-        </is>
-      </c>
-      <c r="H41" s="8" t="inlineStr"/>
-      <c r="I41" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="J41" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="K41" s="13" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="L41" s="12" t="n"/>
-      <c r="M41" s="12" t="n"/>
-      <c r="N41" s="10" t="inlineStr">
-        <is>
-          <t>Ящик сплошной, с перегородками</t>
-        </is>
-      </c>
-      <c r="O41" s="8" t="inlineStr">
-        <is>
-          <t>Склад 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="8" t="n">
-        <v>39</v>
-      </c>
-      <c r="B42" s="16" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="C42" s="10" t="inlineStr">
-        <is>
-          <t>3. Прочее, по цене за килограмм</t>
-        </is>
-      </c>
-      <c r="D42" s="8" t="inlineStr">
-        <is>
-          <t>Ярус 4, верх</t>
-        </is>
-      </c>
-      <c r="E42" s="8" t="inlineStr">
-        <is>
-          <t>клапан штуцерный</t>
-        </is>
-      </c>
-      <c r="F42" s="8" t="inlineStr">
-        <is>
-          <t>Ду50</t>
-        </is>
-      </c>
-      <c r="G42" s="10" t="inlineStr">
-        <is>
-          <t>Клапан невозв-запорн.с присоед.под дюрит прох. Ду 50</t>
-        </is>
-      </c>
-      <c r="H42" s="8" t="inlineStr"/>
-      <c r="I42" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="J42" s="12" t="n">
-        <v>70</v>
-      </c>
-      <c r="K42" s="13" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="L42" s="12" t="n"/>
-      <c r="M42" s="12" t="n"/>
-      <c r="N42" s="10" t="inlineStr">
-        <is>
-          <t>Обрешетка на поддоне</t>
-        </is>
-      </c>
-      <c r="O42" s="8" t="inlineStr">
-        <is>
-          <t>Склад 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="B43" s="16" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="C43" s="10" t="inlineStr">
-        <is>
-          <t>3. Прочее, по цене за килограмм</t>
-        </is>
-      </c>
-      <c r="D43" s="8" t="inlineStr">
-        <is>
-          <t>Ярус 4, верх</t>
-        </is>
-      </c>
-      <c r="E43" s="8" t="inlineStr">
-        <is>
-          <t>клапан штуцерный</t>
-        </is>
-      </c>
-      <c r="F43" s="8" t="inlineStr">
-        <is>
-          <t>Ду65</t>
-        </is>
-      </c>
-      <c r="G43" s="10" t="inlineStr">
-        <is>
-          <t>Клапан запорн.с присоед.под дюрит прох. Ду65</t>
-        </is>
-      </c>
-      <c r="H43" s="8" t="inlineStr"/>
-      <c r="I43" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="J43" s="12" t="n">
-        <v>200</v>
-      </c>
-      <c r="K43" s="13" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L43" s="12" t="n"/>
-      <c r="M43" s="12" t="n"/>
-      <c r="N43" s="10" t="inlineStr">
-        <is>
-          <t>Обрешетка на поддоне</t>
-        </is>
-      </c>
-      <c r="O43" s="8" t="inlineStr">
-        <is>
-          <t>Склад 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="8" t="n">
-        <v>41</v>
-      </c>
-      <c r="B44" s="16" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="C44" s="10" t="inlineStr">
-        <is>
-          <t>3. Прочее, по цене за килограмм</t>
-        </is>
-      </c>
-      <c r="D44" s="8" t="inlineStr">
-        <is>
-          <t>Ярус 4, верх</t>
-        </is>
-      </c>
-      <c r="E44" s="8" t="inlineStr">
-        <is>
-          <t>коробка клапанная</t>
-        </is>
-      </c>
-      <c r="F44" s="8" t="inlineStr">
-        <is>
-          <t>Ду50</t>
-        </is>
-      </c>
-      <c r="G44" s="10" t="inlineStr">
-        <is>
-          <t>Коробка 3-х клап.фланцевая запорная Ду50 Ру6</t>
-        </is>
-      </c>
-      <c r="H44" s="8" t="inlineStr"/>
-      <c r="I44" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J44" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="K44" s="13" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="L44" s="12" t="n"/>
-      <c r="M44" s="12" t="n"/>
-      <c r="N44" s="10" t="inlineStr">
-        <is>
-          <t>Обрешетка на поддоне</t>
-        </is>
-      </c>
-      <c r="O44" s="8" t="inlineStr">
-        <is>
-          <t>Склад 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="8" t="n">
-        <v>42</v>
-      </c>
-      <c r="B45" s="16" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="C45" s="10" t="inlineStr">
-        <is>
-          <t>3. Прочее, по цене за килограмм</t>
-        </is>
-      </c>
-      <c r="D45" s="8" t="inlineStr">
-        <is>
-          <t>Ярус 4, верх</t>
-        </is>
-      </c>
-      <c r="E45" s="8" t="inlineStr">
-        <is>
-          <t>коробка клапанная</t>
-        </is>
-      </c>
-      <c r="F45" s="8" t="inlineStr">
-        <is>
-          <t>Ду50</t>
-        </is>
-      </c>
-      <c r="G45" s="10" t="inlineStr">
-        <is>
-          <t>Коробка 3-х клап.фланцевая запорная Ду50 Ру6</t>
-        </is>
-      </c>
-      <c r="H45" s="8" t="inlineStr"/>
-      <c r="I45" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="J45" s="12" t="n">
-        <v>50</v>
-      </c>
-      <c r="K45" s="13" t="n">
-        <v>0.024</v>
-      </c>
-      <c r="L45" s="12" t="n"/>
-      <c r="M45" s="12" t="n"/>
-      <c r="N45" s="10" t="inlineStr">
-        <is>
-          <t>Обрешетка на поддоне</t>
-        </is>
-      </c>
-      <c r="O45" s="8" t="inlineStr">
-        <is>
-          <t>Склад 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="8" t="n">
-        <v>43</v>
-      </c>
-      <c r="B46" s="16" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="C46" s="10" t="inlineStr">
-        <is>
-          <t>3. Прочее, по цене за килограмм</t>
-        </is>
-      </c>
-      <c r="D46" s="8" t="inlineStr">
-        <is>
-          <t>Ярус 4, верх</t>
-        </is>
-      </c>
-      <c r="E46" s="8" t="inlineStr">
-        <is>
-          <t>коробка клапанная</t>
-        </is>
-      </c>
-      <c r="F46" s="8" t="inlineStr">
-        <is>
-          <t>Ду80</t>
-        </is>
-      </c>
-      <c r="G46" s="10" t="inlineStr">
-        <is>
-          <t>Коробка 3-х клап.фланцевая невозврат.Ду80 Ру6</t>
-        </is>
-      </c>
-      <c r="H46" s="8" t="inlineStr"/>
-      <c r="I46" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="J46" s="12" t="n">
-        <v>90</v>
-      </c>
-      <c r="K46" s="13" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="L46" s="12" t="n"/>
-      <c r="M46" s="12" t="n"/>
-      <c r="N46" s="10" t="inlineStr">
-        <is>
-          <t>Обрешетка на поддоне</t>
-        </is>
-      </c>
-      <c r="O46" s="8" t="inlineStr">
-        <is>
-          <t>Склад 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="8" t="n">
-        <v>44</v>
-      </c>
-      <c r="B47" s="16" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="C47" s="10" t="inlineStr">
-        <is>
-          <t>3. Прочее, по цене за килограмм</t>
-        </is>
-      </c>
-      <c r="D47" s="8" t="inlineStr">
-        <is>
-          <t>Ярус 4, верх</t>
-        </is>
-      </c>
-      <c r="E47" s="8" t="inlineStr">
-        <is>
-          <t>коробка клапанная</t>
-        </is>
-      </c>
-      <c r="F47" s="8" t="inlineStr">
-        <is>
-          <t>Ду80</t>
-        </is>
-      </c>
-      <c r="G47" s="10" t="inlineStr">
-        <is>
-          <t>Коробка 3-х клап.фланцевая Ду80</t>
-        </is>
-      </c>
-      <c r="H47" s="8" t="inlineStr"/>
-      <c r="I47" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="J47" s="12" t="n">
-        <v>135</v>
-      </c>
-      <c r="K47" s="13" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="L47" s="12" t="n"/>
-      <c r="M47" s="12" t="n"/>
-      <c r="N47" s="10" t="inlineStr">
-        <is>
-          <t>Обрешетка на поддоне</t>
-        </is>
-      </c>
-      <c r="O47" s="8" t="inlineStr">
-        <is>
-          <t>Склад 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="8" t="n">
-        <v>45</v>
-      </c>
-      <c r="B48" s="16" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="C48" s="10" t="inlineStr">
-        <is>
-          <t>3. Прочее, по цене за килограмм</t>
-        </is>
-      </c>
-      <c r="D48" s="8" t="inlineStr">
-        <is>
-          <t>Ярус 2</t>
-        </is>
-      </c>
-      <c r="E48" s="8" t="inlineStr">
-        <is>
-          <t>клинкет (задвижка)</t>
-        </is>
-      </c>
-      <c r="F48" s="8" t="inlineStr"/>
-      <c r="G48" s="10" t="inlineStr">
-        <is>
-          <t>Задвижки (желтая) ок. крышек</t>
-        </is>
-      </c>
-      <c r="H48" s="8" t="inlineStr"/>
-      <c r="I48" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="J48" s="12" t="n">
-        <v>520</v>
-      </c>
-      <c r="K48" s="13" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="L48" s="12" t="n"/>
-      <c r="M48" s="12" t="n"/>
-      <c r="N48" s="10" t="inlineStr">
-        <is>
-          <t>Ящик сплошной, с перегородками</t>
-        </is>
-      </c>
-      <c r="O48" s="8" t="inlineStr">
-        <is>
-          <t>Склад 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="8" t="n">
-        <v>46</v>
-      </c>
-      <c r="B49" s="16" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="C49" s="10" t="inlineStr">
-        <is>
-          <t>3. Прочее, по цене за килограмм</t>
-        </is>
-      </c>
-      <c r="D49" s="8" t="inlineStr">
-        <is>
-          <t>Ярус 2</t>
-        </is>
-      </c>
-      <c r="E49" s="8" t="inlineStr">
-        <is>
-          <t>клинкет (задвижка)</t>
-        </is>
-      </c>
-      <c r="F49" s="8" t="inlineStr">
-        <is>
-          <t>Ду100</t>
-        </is>
-      </c>
-      <c r="G49" s="10" t="inlineStr">
-        <is>
-          <t>Блины к клинкету Ду100</t>
-        </is>
-      </c>
-      <c r="H49" s="8" t="inlineStr"/>
-      <c r="I49" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="J49" s="12" t="n">
-        <v>495</v>
-      </c>
-      <c r="K49" s="13" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="L49" s="12" t="n"/>
-      <c r="M49" s="12" t="n"/>
-      <c r="N49" s="10" t="inlineStr">
-        <is>
-          <t>Поддон, прокладки между рядами</t>
-        </is>
-      </c>
-      <c r="O49" s="8" t="inlineStr">
-        <is>
-          <t>Склад электрики</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="G50" s="14" t="inlineStr">
+      <c r="G29" s="14" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="I50" s="15">
-        <f>SUM(I4:I49)</f>
+      <c r="I29" s="15">
+        <f>SUM(I4:I28)</f>
         <v/>
       </c>
-      <c r="J50" s="15">
-        <f>SUM(J4:J49)</f>
+      <c r="J29" s="15">
+        <f>SUM(J4:J28)</f>
         <v/>
       </c>
-      <c r="L50" s="15">
-        <f>SUM(L4:L49)</f>
+      <c r="L29" s="15">
+        <f>SUM(L4:L28)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:O49"/>
+  <autoFilter ref="A3:O28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -17625,7 +17636,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:D45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -17776,12 +17787,12 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>Грузим ярусами: ярус, доска, ярус, доска</t>
+          <t>Грузим ярусами: настил, ярус, доска, ярус</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>На пол идут тяжелые клинкеты и задвижки Ду200 и выше, ближе к середине длины контейнера. На них доска 40 мм поперек на всю ширину, сверху второй ярус задвижек и арматуры Ду100-150, снова доска, на нее фильтры забортной воды, и только сверху ящики с мелкими клапанами. Доска обязательна между каждыми двумя ярусами: без нее фланец верхнего ряда стоит на маховике нижнего.</t>
+          <t>Сначала настил доской 40 мм на пол контейнера. На него задвижки Ду350, Ду300, Ду250 и Ду200, ближе к середине длины. Сверху доска, на нее остальная арматура Ду100-150, снова доска, на нее ящики с мелкими клапанами, и только сверху фильтры. Доска обязательна и под нижним ярусом, и между каждыми двумя ярусами: без нее фланец верхнего ряда стоит на маховике нижнего.</t>
         </is>
       </c>
     </row>
@@ -17845,149 +17856,155 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>Ярус 1, на пол</t>
-        </is>
-      </c>
-      <c r="B18" s="10" t="inlineStr">
-        <is>
-          <t>Клинкеты и задвижки Ду200 и выше</t>
-        </is>
-      </c>
-      <c r="C18" s="10" t="inlineStr">
-        <is>
-          <t>Доска 40 мм поперек, на всю ширину поддона</t>
-        </is>
-      </c>
-      <c r="D18" s="12" t="n">
-        <v>6560</v>
+      <c r="A18" s="17" t="inlineStr">
+        <is>
+          <t>Пол контейнера</t>
+        </is>
+      </c>
+      <c r="B18" s="18" t="inlineStr">
+        <is>
+          <t>Сплошной настил доской 40 мм под первый ярус</t>
+        </is>
+      </c>
+      <c r="C18" s="18" t="inlineStr">
+        <is>
+          <t>Настил кладем до погрузки, по всей площади под задвижки</t>
+        </is>
+      </c>
+      <c r="D18" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 1, на настил</t>
         </is>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>Остальные клинкеты, задвижки и арматура Ду100-150</t>
+          <t>Задвижки и клинкеты Ду200, 250, 300, 350</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>Доска 25-40 мм поперек</t>
+          <t>Доска 40 мм поперек, на всю ширину</t>
         </is>
       </c>
       <c r="D19" s="12" t="n">
-        <v>6982</v>
+        <v>7160</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 2</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Фильтры забортной воды</t>
+          <t>Остальные клинкеты, задвижки и арматура Ду100-150</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>Доска 25 мм, под крупный фильтр — сплошной настил</t>
+          <t>Доска 25-40 мм поперек</t>
         </is>
       </c>
       <c r="D20" s="12" t="n">
-        <v>584</v>
+        <v>6911</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
+          <t>Ярус 3</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>Ящики с мелкой арматурой до Ду80</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>Сплошной настил доской по верху ящиков, под фильтры</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="n">
+        <v>9154</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
           <t>Ярус 4, верх</t>
         </is>
       </c>
-      <c r="B21" s="10" t="inlineStr">
-        <is>
-          <t>Ящики с мелкой арматурой до Ду80</t>
-        </is>
-      </c>
-      <c r="C21" s="10" t="inlineStr">
-        <is>
-          <t>Ящики вяжутся между собой и к стенке, сверху ничего</t>
-        </is>
-      </c>
-      <c r="D21" s="12" t="n">
-        <v>8874</v>
-      </c>
-    </row>
-    <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="17" t="inlineStr">
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>Фильтры забортной воды</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>Сверху ничего не кладем</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="n">
+        <v>1774</v>
+      </c>
+    </row>
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
         <is>
           <t>Ярусы идут снизу вверх. Порядок погрузки обратный порядку выгрузки: что нужно покупателю первым, ставим ближе к дверям.</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="17" t="inlineStr">
-        <is>
-          <t>Ящиков с мелкой арматурой 8.9 т, а фильтров под ними всего 584 кг. Весь четвертый ярус на фильтры ставить нельзя: часть ящиков идет наверх задвижек, часть — отдельной колонной у дверей.</t>
-        </is>
-      </c>
-    </row>
     <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="17" t="inlineStr">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>Фильтры (1774 кг) стоят на ящиках, значит ящики должны быть каркасные: брус по углам и по верху. Фильтр Ду200 весит 120 кг, Ду300 — 230 кг, тонкая обрешетка под ним сложится. Крупные фильтры ставим над углами ящиков, а не над серединой крышки.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="28" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
         <is>
           <t>Между ярусами доска ложится не абы как, а над стенками ящиков и над корпусами, а не над маховиками и штоками.</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
         <is>
           <t>Сколько тары заказать</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="24" customHeight="1">
-      <c r="A28" s="5" t="inlineStr">
+    <row r="29" ht="24" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>Тип упаковки</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>Позиций</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>Штук</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>Вес, кг</t>
         </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="10" t="inlineStr">
-        <is>
-          <t>Поддон с обрешеткой, крепление к полу</t>
-        </is>
-      </c>
-      <c r="B29" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="C29" s="8" t="n">
-        <v>61</v>
-      </c>
-      <c r="D29" s="12" t="n">
-        <v>8854</v>
       </c>
     </row>
     <row r="30">
@@ -17997,29 +18014,29 @@
         </is>
       </c>
       <c r="B30" s="8" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="C30" s="8" t="n">
-        <v>405</v>
+        <v>420</v>
       </c>
       <c r="D30" s="12" t="n">
-        <v>8120</v>
+        <v>8424</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>Ящик сплошной, с перегородками</t>
+          <t>Поддон с обрешеткой, крепление к полу</t>
         </is>
       </c>
       <c r="B31" s="8" t="n">
-        <v>152</v>
+        <v>8</v>
       </c>
       <c r="C31" s="8" t="n">
-        <v>2077</v>
+        <v>39</v>
       </c>
       <c r="D31" s="12" t="n">
-        <v>3016</v>
+        <v>7680</v>
       </c>
     </row>
     <row r="32">
@@ -18029,75 +18046,114 @@
         </is>
       </c>
       <c r="B32" s="8" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C32" s="8" t="n">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="D32" s="12" t="n">
-        <v>3010</v>
+        <v>4045</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>Ящик сплошной, с перегородками</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="n">
+        <v>156</v>
+      </c>
+      <c r="C33" s="8" t="n">
+        <v>2082</v>
+      </c>
+      <c r="D33" s="12" t="n">
+        <v>3076</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="inlineStr">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>Обрешетка, ставится верхним ярусом на ящики</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="C34" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="D34" s="12" t="n">
+        <v>1774</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
         <is>
           <t>Что купить до начала упаковки</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="18" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="20" t="inlineStr">
         <is>
           <t>— Поддоны: считать по весу, на один поддон берем не больше 700-800 кг</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="18" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="20" t="inlineStr">
         <is>
           <t>— Доска 25-40 мм на прокладки между рядами и распорные бруски</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="18" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="20" t="inlineStr">
         <is>
           <t>— Фанера или плотный картон на заглушки фланцев</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="18" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="20" t="inlineStr">
         <is>
           <t>— Стрейч-пленка и стальная или полиэстеровая обвязочная лента</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="18" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="20" t="inlineStr">
         <is>
           <t>— Стяжные ремни для крепления поддонов к рымам контейнера</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="18" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="20" t="inlineStr">
         <is>
           <t>— Влагопоглотитель под крышу контейнера: месяц дороги дает конденсат</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="18" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="20" t="inlineStr">
         <is>
           <t>— Маркер и бирки на каждое место</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="18" t="inlineStr">
-        <is>
-          <t>— Доска 40 мм — отдельно, под первый ярус: 25 мм под задвижками Ду250-350 ломается</t>
+    <row r="44">
+      <c r="A44" s="20" t="inlineStr">
+        <is>
+          <t>— Доска 40 мм на настил по полу и под первый ярус: 25 мм под задвижками Ду250-350 ломается</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="20" t="inlineStr">
+        <is>
+          <t>— Брус 50х50 в углы и по верху ящиков с мелочью: на них встанут фильтры</t>
         </is>
       </c>
     </row>

--- a/outputs/marine_equipment/Отгрузка_Питер.xlsx
+++ b/outputs/marine_equipment/Отгрузка_Питер.xlsx
@@ -20575,7 +20575,7 @@
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>Между рядами кладем доску 25-40 мм на всю ширину. Штабель без прокладок за дорогу садится, и нижний ряд принимает вес всего штабеля точечно.</t>
+          <t>Между рядами кладем необрезную доску 25 мм на всю ширину. Под тяжелыми задвижками доски кладем чаще, с шагом 300-400 мм: двадцатипятка держит, если опереть ее почаще. Штабель без прокладок за дорогу садится, и нижний ряд принимает вес всего штабеля точечно.</t>
         </is>
       </c>
     </row>
@@ -20620,7 +20620,7 @@
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>Сначала настил доской 40 мм на пол контейнера. На него задвижки Ду350, Ду300, Ду250 и Ду200, ближе к середине длины. Сверху доска, на нее остальная арматура Ду100-150, снова доска, на нее ящики с мелкими клапанами, и только сверху фильтры. Доска обязательна и под нижним ярусом, и между каждыми двумя ярусами: без нее фланец верхнего ряда стоит на маховике нижнего.</t>
+          <t>Сначала настил необрезной доской 25 мм на пол контейнера. На него задвижки Ду350, Ду300, Ду250 и Ду200, ближе к середине длины. Сверху доска, на нее остальная арматура Ду100-150, снова доска, на нее ящики с мелкими клапанами, и только сверху фильтры. Доска обязательна и под нижним ярусом, и между каждыми двумя ярусами: без нее фланец верхнего ряда стоит на маховике нижнего.</t>
         </is>
       </c>
     </row>
@@ -20691,7 +20691,7 @@
       </c>
       <c r="B18" s="18" t="inlineStr">
         <is>
-          <t>Сплошной настил доской 40 мм под первый ярус</t>
+          <t>Сплошной настил необрезной доской 25 мм под первый ярус</t>
         </is>
       </c>
       <c r="C18" s="18" t="inlineStr">
@@ -20718,7 +20718,7 @@
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>Доска 40 мм поперек, на всю ширину</t>
+          <t>Необрезная доска 25 мм поперек, на всю ширину, шаг 300-400 мм</t>
         </is>
       </c>
       <c r="D19" s="12" t="n">
@@ -20738,7 +20738,7 @@
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>Доска 25-40 мм поперек</t>
+          <t>Необрезная доска 25 мм поперек</t>
         </is>
       </c>
       <c r="D20" s="12" t="n">
@@ -20932,7 +20932,7 @@
     <row r="38">
       <c r="A38" s="20" t="inlineStr">
         <is>
-          <t>— Доска 25-40 мм на прокладки между рядами и распорные бруски</t>
+          <t>— Доска необрезная 25 мм на настил, прокладки между рядами и распорные бруски</t>
         </is>
       </c>
     </row>
@@ -20974,7 +20974,7 @@
     <row r="44">
       <c r="A44" s="20" t="inlineStr">
         <is>
-          <t>— Доска 40 мм на настил по полу и под первый ярус: 25 мм под задвижками Ду250-350 ломается</t>
+          <t>— Доски берем с запасом: под задвижками Ду250-350 кладем их чаще, шаг 300-400 мм вместо 600</t>
         </is>
       </c>
     </row>

--- a/outputs/marine_equipment/Отгрузка_Питер.xlsx
+++ b/outputs/marine_equipment/Отгрузка_Питер.xlsx
@@ -537,7 +537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -756,22 +756,22 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>337</v>
+        <v>316</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>6.72</v>
+        <v>6.33</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>6.7</v>
+        <v>6.4</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>8523250</v>
+        <v>7908250</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>1269</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="14">
@@ -806,22 +806,22 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="E15" s="6" t="n">
         <v>0.3</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>1672200</v>
+        <v>1613200</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>8074</v>
+        <v>8042</v>
       </c>
     </row>
     <row r="16">
@@ -852,76 +852,247 @@
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>захлопка</t>
+          <t>клапан быстрозапорный</t>
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C17" s="6" t="n">
         <v>11</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>0.27</v>
+        <v>0.24</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>342500</v>
+        <v>420000</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>1269</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>кингстон</t>
+          <t>захлопка</t>
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C18" s="6" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>0.11</v>
+        <v>0.27</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>99000</v>
+        <v>342500</v>
       </c>
       <c r="G18" s="7" t="n">
-        <v>900</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>прочая арматура</t>
+          <t>клапан пожарный</t>
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>0.06</v>
+        <v>0.14</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="F19" s="7" t="n">
+        <v>195000</v>
+      </c>
+      <c r="G19" s="7" t="n">
+        <v>1393</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>кингстон</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F20" s="7" t="n">
+        <v>99000</v>
+      </c>
+      <c r="G20" s="7" t="n">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>клапан без описания — уточнить</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F21" s="7" t="n">
         <v>57000</v>
       </c>
-      <c r="G19" s="7" t="n">
-        <v>950</v>
+      <c r="G21" s="7" t="n">
+        <v>2280</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>клапан предохранительный</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="7" t="n">
+        <v>34500</v>
+      </c>
+      <c r="G22" s="7" t="n">
+        <v>12321</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>клапан педальный</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="7" t="n">
+        <v>12500</v>
+      </c>
+      <c r="G23" s="7" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>клапан редукционный</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="7" t="n">
+        <v>12000</v>
+      </c>
+      <c r="G24" s="7" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>клапан электромагнитный</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F25" s="7" t="n"/>
+      <c r="G25" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>клапан паровой</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="7" t="n"/>
+      <c r="G26" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2870,7 +3041,7 @@
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>прочая арматура</t>
+          <t>клапан без описания — уточнить</t>
         </is>
       </c>
       <c r="F29" s="8" t="inlineStr">
@@ -3414,7 +3585,7 @@
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>прочая арматура</t>
+          <t>клапан без описания — уточнить</t>
         </is>
       </c>
       <c r="F37" s="8" t="inlineStr"/>
@@ -3614,7 +3785,7 @@
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>клапан пожарный</t>
         </is>
       </c>
       <c r="F40" s="8" t="inlineStr">
@@ -3682,7 +3853,7 @@
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>клапан пожарный</t>
         </is>
       </c>
       <c r="F41" s="8" t="inlineStr">
@@ -3750,7 +3921,7 @@
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>клапан пожарный</t>
         </is>
       </c>
       <c r="F42" s="8" t="inlineStr">
@@ -3818,7 +3989,7 @@
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>клапан быстрозапорный</t>
         </is>
       </c>
       <c r="F43" s="8" t="inlineStr">
@@ -3886,7 +4057,7 @@
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>клапан быстрозапорный</t>
         </is>
       </c>
       <c r="F44" s="8" t="inlineStr">
@@ -3954,7 +4125,7 @@
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>клапан быстрозапорный</t>
         </is>
       </c>
       <c r="F45" s="8" t="inlineStr">
@@ -4022,7 +4193,7 @@
       </c>
       <c r="E46" s="8" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>клапан быстрозапорный</t>
         </is>
       </c>
       <c r="F46" s="8" t="inlineStr">
@@ -4226,7 +4397,7 @@
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>клапан пожарный</t>
         </is>
       </c>
       <c r="F49" s="8" t="inlineStr">
@@ -6738,7 +6909,7 @@
       </c>
       <c r="E86" s="8" t="inlineStr">
         <is>
-          <t>прочая арматура</t>
+          <t>клапан без описания — уточнить</t>
         </is>
       </c>
       <c r="F86" s="8" t="inlineStr"/>
@@ -6798,7 +6969,7 @@
       </c>
       <c r="E87" s="8" t="inlineStr">
         <is>
-          <t>прочая арматура</t>
+          <t>клапан электромагнитный</t>
         </is>
       </c>
       <c r="F87" s="8" t="inlineStr"/>
@@ -6858,7 +7029,7 @@
       </c>
       <c r="E88" s="8" t="inlineStr">
         <is>
-          <t>прочая арматура</t>
+          <t>клапан паровой</t>
         </is>
       </c>
       <c r="F88" s="8" t="inlineStr">
@@ -6922,7 +7093,7 @@
       </c>
       <c r="E89" s="8" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>клапан пожарный</t>
         </is>
       </c>
       <c r="F89" s="8" t="inlineStr">
@@ -6986,7 +7157,7 @@
       </c>
       <c r="E90" s="8" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>клапан пожарный</t>
         </is>
       </c>
       <c r="F90" s="8" t="inlineStr">
@@ -7050,7 +7221,7 @@
       </c>
       <c r="E91" s="8" t="inlineStr">
         <is>
-          <t>прочая арматура</t>
+          <t>клапан без описания — уточнить</t>
         </is>
       </c>
       <c r="F91" s="8" t="inlineStr"/>
@@ -7110,7 +7281,7 @@
       </c>
       <c r="E92" s="8" t="inlineStr">
         <is>
-          <t>прочая арматура</t>
+          <t>клапан электромагнитный</t>
         </is>
       </c>
       <c r="F92" s="8" t="inlineStr"/>
@@ -7238,7 +7409,7 @@
       </c>
       <c r="E94" s="8" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
+          <t>клапан предохранительный</t>
         </is>
       </c>
       <c r="F94" s="8" t="inlineStr">
@@ -7578,7 +7749,7 @@
       </c>
       <c r="E99" s="8" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
+          <t>клапан предохранительный</t>
         </is>
       </c>
       <c r="F99" s="8" t="inlineStr">
@@ -7646,7 +7817,7 @@
       </c>
       <c r="E100" s="8" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
+          <t>клапан предохранительный</t>
         </is>
       </c>
       <c r="F100" s="8" t="inlineStr">
@@ -7850,7 +8021,7 @@
       </c>
       <c r="E103" s="8" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
+          <t>клапан редукционный</t>
         </is>
       </c>
       <c r="F103" s="8" t="inlineStr">
@@ -7918,7 +8089,7 @@
       </c>
       <c r="E104" s="8" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
+          <t>клапан редукционный</t>
         </is>
       </c>
       <c r="F104" s="8" t="inlineStr">
@@ -7986,7 +8157,7 @@
       </c>
       <c r="E105" s="8" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
+          <t>клапан предохранительный</t>
         </is>
       </c>
       <c r="F105" s="8" t="inlineStr">
@@ -8054,7 +8225,7 @@
       </c>
       <c r="E106" s="8" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
+          <t>клапан предохранительный</t>
         </is>
       </c>
       <c r="F106" s="8" t="inlineStr">
@@ -10298,7 +10469,7 @@
       </c>
       <c r="E139" s="8" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
+          <t>клапан педальный</t>
         </is>
       </c>
       <c r="F139" s="8" t="inlineStr">
@@ -11415,7 +11586,7 @@
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
+          <t>клапан педальный</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
@@ -15925,7 +16096,7 @@
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>клапан быстрозапорный</t>
         </is>
       </c>
       <c r="F69" s="8" t="inlineStr">
@@ -16587,7 +16758,7 @@
       </c>
       <c r="E78" s="8" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>клапан пожарный</t>
         </is>
       </c>
       <c r="F78" s="8" t="inlineStr">
@@ -16735,7 +16906,7 @@
       </c>
       <c r="E80" s="8" t="inlineStr">
         <is>
-          <t>прочая арматура</t>
+          <t>клапан без описания — уточнить</t>
         </is>
       </c>
       <c r="F80" s="8" t="inlineStr">
@@ -17179,7 +17350,7 @@
       </c>
       <c r="E86" s="8" t="inlineStr">
         <is>
-          <t>прочая арматура</t>
+          <t>колонка указательная</t>
         </is>
       </c>
       <c r="F86" s="8" t="inlineStr">
@@ -17817,7 +17988,7 @@
       </c>
       <c r="E95" s="8" t="inlineStr">
         <is>
-          <t>прочая арматура</t>
+          <t>клапан редукционный</t>
         </is>
       </c>
       <c r="F95" s="8" t="inlineStr">
@@ -17887,7 +18058,7 @@
       </c>
       <c r="E96" s="8" t="inlineStr">
         <is>
-          <t>прочая арматура</t>
+          <t>клапан электромагнитный</t>
         </is>
       </c>
       <c r="F96" s="8" t="inlineStr">
@@ -17957,7 +18128,7 @@
       </c>
       <c r="E97" s="8" t="inlineStr">
         <is>
-          <t>прочая арматура</t>
+          <t>клапан пусковой</t>
         </is>
       </c>
       <c r="F97" s="8" t="inlineStr">
@@ -18027,7 +18198,7 @@
       </c>
       <c r="E98" s="8" t="inlineStr">
         <is>
-          <t>прочая арматура</t>
+          <t>клапан пусковой</t>
         </is>
       </c>
       <c r="F98" s="8" t="inlineStr">
@@ -18097,7 +18268,7 @@
       </c>
       <c r="E99" s="8" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>клапан пожарный</t>
         </is>
       </c>
       <c r="F99" s="8" t="inlineStr">
@@ -18167,7 +18338,7 @@
       </c>
       <c r="E100" s="8" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>клапан пожарный</t>
         </is>
       </c>
       <c r="F100" s="8" t="inlineStr">

--- a/outputs/marine_equipment/Отгрузка_Питер.xlsx
+++ b/outputs/marine_equipment/Отгрузка_Питер.xlsx
@@ -1740,7 +1740,7 @@
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
@@ -2388,7 +2388,7 @@
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E28" s="8" t="inlineStr">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
@@ -3308,7 +3308,7 @@
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E34" s="8" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
@@ -3580,7 +3580,7 @@
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
@@ -3712,7 +3712,7 @@
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
@@ -3780,7 +3780,7 @@
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E40" s="8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E42" s="8" t="inlineStr">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
@@ -4052,7 +4052,7 @@
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E44" s="8" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E46" s="8" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
@@ -4324,7 +4324,7 @@
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E48" s="8" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
@@ -4460,7 +4460,7 @@
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E50" s="8" t="inlineStr">
@@ -4528,7 +4528,7 @@
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E52" s="8" t="inlineStr">
@@ -4664,7 +4664,7 @@
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E54" s="8" t="inlineStr">
@@ -4800,7 +4800,7 @@
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E56" s="8" t="inlineStr">
@@ -4936,7 +4936,7 @@
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
@@ -5004,7 +5004,7 @@
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E58" s="8" t="inlineStr">
@@ -5204,7 +5204,7 @@
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
@@ -5272,7 +5272,7 @@
       </c>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E62" s="8" t="inlineStr">
@@ -5340,7 +5340,7 @@
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
@@ -5408,7 +5408,7 @@
       </c>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="E64" s="8" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="D66" s="8" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="E66" s="8" t="inlineStr">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr">
@@ -5748,7 +5748,7 @@
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="E70" s="8" t="inlineStr">
@@ -5884,7 +5884,7 @@
       </c>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr">
@@ -5952,7 +5952,7 @@
       </c>
       <c r="D72" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E72" s="8" t="inlineStr">
@@ -6020,7 +6020,7 @@
       </c>
       <c r="D73" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E73" s="8" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="D74" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E74" s="8" t="inlineStr">
@@ -6156,7 +6156,7 @@
       </c>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E75" s="8" t="inlineStr">
@@ -6224,7 +6224,7 @@
       </c>
       <c r="D76" s="8" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E76" s="8" t="inlineStr">
@@ -6292,7 +6292,7 @@
       </c>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="E77" s="8" t="inlineStr">
@@ -6360,7 +6360,7 @@
       </c>
       <c r="D78" s="8" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="E78" s="8" t="inlineStr">
@@ -6428,7 +6428,7 @@
       </c>
       <c r="D79" s="8" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="E79" s="8" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="D80" s="8" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E80" s="8" t="inlineStr">
@@ -6564,7 +6564,7 @@
       </c>
       <c r="D81" s="8" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="E81" s="8" t="inlineStr">
@@ -6632,7 +6632,7 @@
       </c>
       <c r="D82" s="8" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="E82" s="8" t="inlineStr">
@@ -6700,7 +6700,7 @@
       </c>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E83" s="8" t="inlineStr">
@@ -6768,7 +6768,7 @@
       </c>
       <c r="D84" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E84" s="8" t="inlineStr">
@@ -6836,7 +6836,7 @@
       </c>
       <c r="D85" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E85" s="8" t="inlineStr">
@@ -6904,7 +6904,7 @@
       </c>
       <c r="D86" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E86" s="8" t="inlineStr">
@@ -6964,7 +6964,7 @@
       </c>
       <c r="D87" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
@@ -7024,7 +7024,7 @@
       </c>
       <c r="D88" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E88" s="8" t="inlineStr">
@@ -7088,7 +7088,7 @@
       </c>
       <c r="D89" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E89" s="8" t="inlineStr">
@@ -7152,7 +7152,7 @@
       </c>
       <c r="D90" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E90" s="8" t="inlineStr">
@@ -7216,7 +7216,7 @@
       </c>
       <c r="D91" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E91" s="8" t="inlineStr">
@@ -7276,7 +7276,7 @@
       </c>
       <c r="D92" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E92" s="8" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="D93" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E93" s="8" t="inlineStr">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="D94" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E94" s="8" t="inlineStr">
@@ -7472,7 +7472,7 @@
       </c>
       <c r="D95" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E95" s="8" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="D96" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E96" s="8" t="inlineStr">
@@ -7608,7 +7608,7 @@
       </c>
       <c r="D97" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="D98" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E98" s="8" t="inlineStr">
@@ -7744,7 +7744,7 @@
       </c>
       <c r="D99" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E99" s="8" t="inlineStr">
@@ -7812,7 +7812,7 @@
       </c>
       <c r="D100" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E100" s="8" t="inlineStr">
@@ -7880,7 +7880,7 @@
       </c>
       <c r="D101" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E101" s="8" t="inlineStr">
@@ -7948,7 +7948,7 @@
       </c>
       <c r="D102" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E102" s="8" t="inlineStr">
@@ -8016,7 +8016,7 @@
       </c>
       <c r="D103" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E103" s="8" t="inlineStr">
@@ -8084,7 +8084,7 @@
       </c>
       <c r="D104" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E104" s="8" t="inlineStr">
@@ -8152,7 +8152,7 @@
       </c>
       <c r="D105" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E105" s="8" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="D106" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E106" s="8" t="inlineStr">
@@ -8288,7 +8288,7 @@
       </c>
       <c r="D107" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E107" s="8" t="inlineStr">
@@ -8356,7 +8356,7 @@
       </c>
       <c r="D108" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E108" s="8" t="inlineStr">
@@ -8424,7 +8424,7 @@
       </c>
       <c r="D109" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E109" s="8" t="inlineStr">
@@ -8492,7 +8492,7 @@
       </c>
       <c r="D110" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E110" s="8" t="inlineStr">
@@ -8560,7 +8560,7 @@
       </c>
       <c r="D111" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E111" s="8" t="inlineStr">
@@ -8628,7 +8628,7 @@
       </c>
       <c r="D112" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E112" s="8" t="inlineStr">
@@ -8696,7 +8696,7 @@
       </c>
       <c r="D113" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E113" s="8" t="inlineStr">
@@ -8764,7 +8764,7 @@
       </c>
       <c r="D114" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E114" s="8" t="inlineStr">
@@ -8832,7 +8832,7 @@
       </c>
       <c r="D115" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E115" s="8" t="inlineStr">
@@ -8900,7 +8900,7 @@
       </c>
       <c r="D116" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E116" s="8" t="inlineStr">
@@ -8968,7 +8968,7 @@
       </c>
       <c r="D117" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E117" s="8" t="inlineStr">
@@ -9036,7 +9036,7 @@
       </c>
       <c r="D118" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E118" s="8" t="inlineStr">
@@ -9104,7 +9104,7 @@
       </c>
       <c r="D119" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E119" s="8" t="inlineStr">
@@ -9172,7 +9172,7 @@
       </c>
       <c r="D120" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E120" s="8" t="inlineStr">
@@ -9240,7 +9240,7 @@
       </c>
       <c r="D121" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E121" s="8" t="inlineStr">
@@ -9308,7 +9308,7 @@
       </c>
       <c r="D122" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E122" s="8" t="inlineStr">
@@ -9376,7 +9376,7 @@
       </c>
       <c r="D123" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E123" s="8" t="inlineStr">
@@ -9444,7 +9444,7 @@
       </c>
       <c r="D124" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E124" s="8" t="inlineStr">
@@ -9512,7 +9512,7 @@
       </c>
       <c r="D125" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E125" s="8" t="inlineStr">
@@ -9580,7 +9580,7 @@
       </c>
       <c r="D126" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E126" s="8" t="inlineStr">
@@ -9648,7 +9648,7 @@
       </c>
       <c r="D127" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E127" s="8" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="D128" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E128" s="8" t="inlineStr">
@@ -9784,7 +9784,7 @@
       </c>
       <c r="D129" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E129" s="8" t="inlineStr">
@@ -9852,7 +9852,7 @@
       </c>
       <c r="D130" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E130" s="8" t="inlineStr">
@@ -9920,7 +9920,7 @@
       </c>
       <c r="D131" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E131" s="8" t="inlineStr">
@@ -9988,7 +9988,7 @@
       </c>
       <c r="D132" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E132" s="8" t="inlineStr">
@@ -10056,7 +10056,7 @@
       </c>
       <c r="D133" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E133" s="8" t="inlineStr">
@@ -10124,7 +10124,7 @@
       </c>
       <c r="D134" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E134" s="8" t="inlineStr">
@@ -10192,7 +10192,7 @@
       </c>
       <c r="D135" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E135" s="8" t="inlineStr">
@@ -10260,7 +10260,7 @@
       </c>
       <c r="D136" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E136" s="8" t="inlineStr">
@@ -10328,7 +10328,7 @@
       </c>
       <c r="D137" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E137" s="8" t="inlineStr">
@@ -10396,7 +10396,7 @@
       </c>
       <c r="D138" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E138" s="8" t="inlineStr">
@@ -10464,7 +10464,7 @@
       </c>
       <c r="D139" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E139" s="8" t="inlineStr">
@@ -10532,7 +10532,7 @@
       </c>
       <c r="D140" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E140" s="8" t="inlineStr">
@@ -10600,7 +10600,7 @@
       </c>
       <c r="D141" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E141" s="8" t="inlineStr">
@@ -10668,7 +10668,7 @@
       </c>
       <c r="D142" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E142" s="8" t="inlineStr">
@@ -10736,7 +10736,7 @@
       </c>
       <c r="D143" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E143" s="8" t="inlineStr">
@@ -10804,7 +10804,7 @@
       </c>
       <c r="D144" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E144" s="8" t="inlineStr">
@@ -10872,7 +10872,7 @@
       </c>
       <c r="D145" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E145" s="8" t="inlineStr">
@@ -10940,7 +10940,7 @@
       </c>
       <c r="D146" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E146" s="8" t="inlineStr">
@@ -11008,7 +11008,7 @@
       </c>
       <c r="D147" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E147" s="8" t="inlineStr">
@@ -11076,7 +11076,7 @@
       </c>
       <c r="D148" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E148" s="8" t="inlineStr">
@@ -11297,7 +11297,7 @@
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
@@ -11363,7 +11363,7 @@
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -11433,7 +11433,7 @@
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
@@ -11507,7 +11507,7 @@
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
@@ -11581,7 +11581,7 @@
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
@@ -11655,7 +11655,7 @@
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
@@ -11729,7 +11729,7 @@
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
@@ -11803,7 +11803,7 @@
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
@@ -11877,7 +11877,7 @@
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
@@ -11951,7 +11951,7 @@
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
@@ -12025,7 +12025,7 @@
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
@@ -12099,7 +12099,7 @@
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
@@ -12173,7 +12173,7 @@
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
@@ -12247,7 +12247,7 @@
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
@@ -12321,7 +12321,7 @@
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
@@ -12395,7 +12395,7 @@
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
@@ -12469,7 +12469,7 @@
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
@@ -12543,7 +12543,7 @@
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
@@ -12617,7 +12617,7 @@
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
@@ -12691,7 +12691,7 @@
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
@@ -12765,7 +12765,7 @@
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
@@ -12839,7 +12839,7 @@
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
@@ -12913,7 +12913,7 @@
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr">
@@ -12987,7 +12987,7 @@
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
@@ -13061,7 +13061,7 @@
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E28" s="8" t="inlineStr">
@@ -13135,7 +13135,7 @@
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
@@ -13209,7 +13209,7 @@
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr">
@@ -13283,7 +13283,7 @@
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
@@ -13357,7 +13357,7 @@
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E32" s="8" t="inlineStr">
@@ -13431,7 +13431,7 @@
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
@@ -13505,7 +13505,7 @@
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E34" s="8" t="inlineStr">
@@ -13579,7 +13579,7 @@
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
@@ -13653,7 +13653,7 @@
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E36" s="8" t="inlineStr">
@@ -13727,7 +13727,7 @@
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
@@ -13801,7 +13801,7 @@
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E38" s="8" t="inlineStr">
@@ -13875,7 +13875,7 @@
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
@@ -13949,7 +13949,7 @@
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E40" s="8" t="inlineStr">
@@ -14023,7 +14023,7 @@
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
@@ -14097,7 +14097,7 @@
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E42" s="8" t="inlineStr">
@@ -14171,7 +14171,7 @@
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
@@ -14245,7 +14245,7 @@
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E44" s="8" t="inlineStr">
@@ -14319,7 +14319,7 @@
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
@@ -14393,7 +14393,7 @@
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E46" s="8" t="inlineStr">
@@ -14467,7 +14467,7 @@
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
@@ -14541,7 +14541,7 @@
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E48" s="8" t="inlineStr">
@@ -14615,7 +14615,7 @@
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
@@ -14685,7 +14685,7 @@
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E50" s="8" t="inlineStr">
@@ -14759,7 +14759,7 @@
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
@@ -14833,7 +14833,7 @@
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E52" s="8" t="inlineStr">
@@ -14907,7 +14907,7 @@
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
@@ -14981,7 +14981,7 @@
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E54" s="8" t="inlineStr">
@@ -15055,7 +15055,7 @@
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
@@ -15129,7 +15129,7 @@
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E56" s="8" t="inlineStr">
@@ -15203,7 +15203,7 @@
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
@@ -15277,7 +15277,7 @@
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E58" s="8" t="inlineStr">
@@ -15351,7 +15351,7 @@
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
@@ -15425,7 +15425,7 @@
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E60" s="8" t="inlineStr">
@@ -15499,7 +15499,7 @@
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
@@ -15573,7 +15573,7 @@
       </c>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E62" s="8" t="inlineStr">
@@ -15647,7 +15647,7 @@
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
@@ -15721,7 +15721,7 @@
       </c>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E64" s="8" t="inlineStr">
@@ -15795,7 +15795,7 @@
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
@@ -15869,7 +15869,7 @@
       </c>
       <c r="D66" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E66" s="8" t="inlineStr">
@@ -15943,7 +15943,7 @@
       </c>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr">
@@ -16017,7 +16017,7 @@
       </c>
       <c r="D68" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E68" s="8" t="inlineStr">
@@ -16091,7 +16091,7 @@
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr">
@@ -16165,7 +16165,7 @@
       </c>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E70" s="8" t="inlineStr">
@@ -16239,7 +16239,7 @@
       </c>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr">
@@ -16313,7 +16313,7 @@
       </c>
       <c r="D72" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E72" s="8" t="inlineStr">
@@ -16387,7 +16387,7 @@
       </c>
       <c r="D73" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E73" s="8" t="inlineStr">
@@ -16461,7 +16461,7 @@
       </c>
       <c r="D74" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E74" s="8" t="inlineStr">
@@ -16605,7 +16605,7 @@
       </c>
       <c r="D76" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E76" s="8" t="inlineStr">
@@ -16679,7 +16679,7 @@
       </c>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E77" s="8" t="inlineStr">
@@ -16753,7 +16753,7 @@
       </c>
       <c r="D78" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E78" s="8" t="inlineStr">
@@ -16827,7 +16827,7 @@
       </c>
       <c r="D79" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E79" s="8" t="inlineStr">
@@ -16901,7 +16901,7 @@
       </c>
       <c r="D80" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E80" s="8" t="inlineStr">
@@ -16975,7 +16975,7 @@
       </c>
       <c r="D81" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E81" s="8" t="inlineStr">
@@ -17049,7 +17049,7 @@
       </c>
       <c r="D82" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E82" s="8" t="inlineStr">
@@ -17123,7 +17123,7 @@
       </c>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E83" s="8" t="inlineStr">
@@ -17197,7 +17197,7 @@
       </c>
       <c r="D84" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E84" s="8" t="inlineStr">
@@ -17271,7 +17271,7 @@
       </c>
       <c r="D85" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E85" s="8" t="inlineStr">
@@ -17345,7 +17345,7 @@
       </c>
       <c r="D86" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E86" s="8" t="inlineStr">
@@ -17419,7 +17419,7 @@
       </c>
       <c r="D87" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
@@ -17493,7 +17493,7 @@
       </c>
       <c r="D88" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E88" s="8" t="inlineStr">
@@ -17567,7 +17567,7 @@
       </c>
       <c r="D89" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E89" s="8" t="inlineStr">
@@ -17641,7 +17641,7 @@
       </c>
       <c r="D90" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E90" s="8" t="inlineStr">
@@ -17711,7 +17711,7 @@
       </c>
       <c r="D91" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E91" s="8" t="inlineStr">
@@ -17781,7 +17781,7 @@
       </c>
       <c r="D92" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E92" s="8" t="inlineStr">
@@ -17847,7 +17847,7 @@
       </c>
       <c r="D93" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E93" s="8" t="inlineStr">
@@ -17917,7 +17917,7 @@
       </c>
       <c r="D94" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E94" s="8" t="inlineStr">
@@ -17983,7 +17983,7 @@
       </c>
       <c r="D95" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E95" s="8" t="inlineStr">
@@ -18053,7 +18053,7 @@
       </c>
       <c r="D96" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E96" s="8" t="inlineStr">
@@ -18123,7 +18123,7 @@
       </c>
       <c r="D97" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr">
@@ -18193,7 +18193,7 @@
       </c>
       <c r="D98" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E98" s="8" t="inlineStr">
@@ -18263,7 +18263,7 @@
       </c>
       <c r="D99" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E99" s="8" t="inlineStr">
@@ -18333,7 +18333,7 @@
       </c>
       <c r="D100" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E100" s="8" t="inlineStr">
@@ -18403,7 +18403,7 @@
       </c>
       <c r="D101" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E101" s="8" t="inlineStr">
@@ -18473,7 +18473,7 @@
       </c>
       <c r="D102" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E102" s="8" t="inlineStr">
@@ -18696,7 +18696,7 @@
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
@@ -18770,7 +18770,7 @@
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -18844,7 +18844,7 @@
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
@@ -18918,7 +18918,7 @@
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
@@ -18996,7 +18996,7 @@
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
@@ -19070,7 +19070,7 @@
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
@@ -19144,7 +19144,7 @@
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
@@ -19218,7 +19218,7 @@
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
@@ -19296,7 +19296,7 @@
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
@@ -19374,7 +19374,7 @@
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
@@ -19452,7 +19452,7 @@
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
@@ -19530,7 +19530,7 @@
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
@@ -19678,7 +19678,7 @@
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
@@ -19748,7 +19748,7 @@
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
@@ -19818,7 +19818,7 @@
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
@@ -19888,7 +19888,7 @@
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
@@ -19958,7 +19958,7 @@
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
@@ -20028,7 +20028,7 @@
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
@@ -20098,7 +20098,7 @@
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
@@ -20168,7 +20168,7 @@
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
@@ -20238,7 +20238,7 @@
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
@@ -20308,7 +20308,7 @@
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr">
@@ -20386,7 +20386,7 @@
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
@@ -20464,7 +20464,7 @@
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E28" s="8" t="inlineStr">
@@ -20542,7 +20542,7 @@
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
@@ -20884,12 +20884,12 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>Задвижки и клинкеты Ду200, 250, 300, 350</t>
+          <t>Клинкеты Ду200, 250, 300, 350 — один слой</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>Необрезная доска 25 мм поперек, на всю ширину, шаг 300-400 мм</t>
+          <t>Необрезная доска 25 мм сплошным настилом поверх слоя</t>
         </is>
       </c>
       <c r="D19" s="12" t="n">
@@ -20899,12 +20899,12 @@
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>Ярус 2</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Остальные клинкеты, задвижки и арматура Ду100-150</t>
+          <t>Клапанные коробки и тяжелая арматура от Ду100</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
@@ -20913,27 +20913,27 @@
         </is>
       </c>
       <c r="D20" s="12" t="n">
-        <v>6753</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>Ящики с мелкой арматурой до Ду80</t>
+          <t>Ящики с мелкой арматурой, включая клинкеты до Ду150</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>Сплошной настил доской по верху ящиков, под верхний ярус</t>
+          <t>Два яруса ящиков высотой не больше 0,91 м каждый</t>
         </is>
       </c>
       <c r="D21" s="12" t="n">
-        <v>5235</v>
+        <v>9893</v>
       </c>
     </row>
     <row r="22">

--- a/outputs/marine_equipment/Отгрузка_Питер.xlsx
+++ b/outputs/marine_equipment/Отгрузка_Питер.xlsx
@@ -537,7 +537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -731,19 +731,19 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>16.02</v>
+        <v>15.97</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>17.9</v>
+        <v>17.8</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>13679000</v>
+        <v>13644000</v>
       </c>
       <c r="G12" s="7" t="n">
         <v>854</v>
@@ -781,22 +781,22 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>3330000</v>
+        <v>3290000</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>2160</v>
+        <v>2179</v>
       </c>
     </row>
     <row r="15">
@@ -977,32 +977,32 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>клапан предохранительный</t>
+          <t>сетка к фильтру</t>
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C22" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>34500</v>
+        <v>40000</v>
       </c>
       <c r="G22" s="7" t="n">
-        <v>12321</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>клапан педальный</t>
+          <t>блины к клинкету</t>
         </is>
       </c>
       <c r="B23" s="6" t="n">
@@ -1012,29 +1012,29 @@
         <v>1</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="E23" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>12500</v>
+        <v>35000</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>5000</v>
+        <v>778</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>клапан редукционный</t>
+          <t>клапан предохранительный</t>
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C24" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D24" s="6" t="n">
         <v>0</v>
@@ -1043,55 +1043,105 @@
         <v>0</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>12000</v>
+        <v>34500</v>
       </c>
       <c r="G24" s="7" t="n">
-        <v>10000</v>
+        <v>12321</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>клапан электромагнитный</t>
+          <t>клапан педальный</t>
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C25" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F25" s="7" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="F25" s="7" t="n">
+        <v>12500</v>
+      </c>
       <c r="G25" s="7" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>клапан паровой</t>
+          <t>клапан редукционный</t>
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C26" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="E26" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F26" s="7" t="n"/>
+      <c r="F26" s="7" t="n">
+        <v>12000</v>
+      </c>
       <c r="G26" s="7" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>клапан электромагнитный</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F27" s="7" t="n"/>
+      <c r="G27" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>клапан паровой</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="7" t="n"/>
+      <c r="G28" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1264,7 +1314,7 @@
       </c>
       <c r="H4" s="11" t="inlineStr">
         <is>
-          <t>проверить: везем бронзу и латунь</t>
+          <t>бронза/латунь</t>
         </is>
       </c>
       <c r="I4" s="8" t="n">
@@ -1336,7 +1386,7 @@
       </c>
       <c r="H5" s="11" t="inlineStr">
         <is>
-          <t>проверить: везем бронзу и латунь</t>
+          <t>бронза/латунь</t>
         </is>
       </c>
       <c r="I5" s="8" t="n">
@@ -1408,7 +1458,7 @@
       </c>
       <c r="H6" s="11" t="inlineStr">
         <is>
-          <t>проверить: везем бронзу и латунь</t>
+          <t>бронза/латунь</t>
         </is>
       </c>
       <c r="I6" s="8" t="n">
@@ -1480,7 +1530,7 @@
       </c>
       <c r="H7" s="11" t="inlineStr">
         <is>
-          <t>проверить: везем бронзу и латунь</t>
+          <t>бронза/латунь</t>
         </is>
       </c>
       <c r="I7" s="8" t="n">
@@ -1552,7 +1602,7 @@
       </c>
       <c r="H8" s="11" t="inlineStr">
         <is>
-          <t>проверить: везем бронзу и латунь</t>
+          <t>бронза/латунь</t>
         </is>
       </c>
       <c r="I8" s="8" t="n">
@@ -3054,7 +3104,11 @@
           <t>Клапан проходной ДУ 125 корпус</t>
         </is>
       </c>
-      <c r="H29" s="8" t="inlineStr"/>
+      <c r="H29" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I29" s="8" t="n">
         <v>1</v>
       </c>
@@ -3122,7 +3176,11 @@
           <t>Фильтр забортной воды Ду 50</t>
         </is>
       </c>
-      <c r="H30" s="8" t="inlineStr"/>
+      <c r="H30" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I30" s="8" t="n">
         <v>1</v>
       </c>
@@ -3190,7 +3248,11 @@
           <t>Фильтр фланц.прох. забортной воды Ду100 Ру4</t>
         </is>
       </c>
-      <c r="H31" s="8" t="inlineStr"/>
+      <c r="H31" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I31" s="8" t="n">
         <v>3</v>
       </c>
@@ -3258,7 +3320,11 @@
           <t>Фильтр забортной воды Ду 100</t>
         </is>
       </c>
-      <c r="H32" s="8" t="inlineStr"/>
+      <c r="H32" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I32" s="8" t="n">
         <v>1</v>
       </c>
@@ -3326,7 +3392,11 @@
           <t>Задвижка клинкетная Ду 50, без клиньев</t>
         </is>
       </c>
-      <c r="H33" s="8" t="inlineStr"/>
+      <c r="H33" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I33" s="8" t="n">
         <v>1</v>
       </c>
@@ -3394,7 +3464,11 @@
           <t>Захлопка фланцевая вертикальная Ду50Ру63</t>
         </is>
       </c>
-      <c r="H34" s="8" t="inlineStr"/>
+      <c r="H34" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I34" s="8" t="n">
         <v>1</v>
       </c>
@@ -3462,7 +3536,11 @@
           <t>Захлопка фланцевая горизонтальная Ду50</t>
         </is>
       </c>
-      <c r="H35" s="8" t="inlineStr"/>
+      <c r="H35" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I35" s="8" t="n">
         <v>1</v>
       </c>
@@ -3530,7 +3608,11 @@
           <t>Фильтр забортной воды Ду200 Большой</t>
         </is>
       </c>
-      <c r="H36" s="8" t="inlineStr"/>
+      <c r="H36" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I36" s="8" t="n">
         <v>8</v>
       </c>
@@ -3594,7 +3676,11 @@
           <t>Судовая запорная арматура</t>
         </is>
       </c>
-      <c r="H37" s="8" t="inlineStr"/>
+      <c r="H37" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I37" s="8" t="n">
         <v>2</v>
       </c>
@@ -3662,7 +3748,11 @@
           <t>Фильтр заборной воды ДУ 150</t>
         </is>
       </c>
-      <c r="H38" s="8" t="inlineStr"/>
+      <c r="H38" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I38" s="8" t="n">
         <v>5</v>
       </c>
@@ -3730,7 +3820,11 @@
           <t>Клапан фланцевый проходной невозвратный Ду 50 РУ 25 (522-01.164)</t>
         </is>
       </c>
-      <c r="H39" s="8" t="inlineStr"/>
+      <c r="H39" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I39" s="8" t="n">
         <v>1</v>
       </c>
@@ -3798,7 +3892,11 @@
           <t>Клапан Пожарный фланцевый угловой Ду50 Ру16</t>
         </is>
       </c>
-      <c r="H40" s="8" t="inlineStr"/>
+      <c r="H40" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I40" s="8" t="n">
         <v>3</v>
       </c>
@@ -3866,7 +3964,11 @@
           <t>Клапан Пожарный фланцевый угловой Ду50 Ру16</t>
         </is>
       </c>
-      <c r="H41" s="8" t="inlineStr"/>
+      <c r="H41" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I41" s="8" t="n">
         <v>1</v>
       </c>
@@ -3934,7 +4036,11 @@
           <t>Клапан Пожарный фланцевый угловой Ду50 Ру16</t>
         </is>
       </c>
-      <c r="H42" s="8" t="inlineStr"/>
+      <c r="H42" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I42" s="8" t="n">
         <v>2</v>
       </c>
@@ -4002,7 +4108,11 @@
           <t>Клапан быстрозапор. фланц.проход.с тросиков.приводом Ду65 Ру6,3</t>
         </is>
       </c>
-      <c r="H43" s="8" t="inlineStr"/>
+      <c r="H43" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I43" s="8" t="n">
         <v>1</v>
       </c>
@@ -4070,7 +4180,11 @@
           <t>Клапан быстрозапор. фланц. проход. с тросиков. приводом Ду65Ру6,3</t>
         </is>
       </c>
-      <c r="H44" s="8" t="inlineStr"/>
+      <c r="H44" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I44" s="8" t="n">
         <v>5</v>
       </c>
@@ -4138,7 +4252,11 @@
           <t>Клапан быстрозапор. фланц.проход.с тросиков.приводом Ду70 Ру6,3</t>
         </is>
       </c>
-      <c r="H45" s="8" t="inlineStr"/>
+      <c r="H45" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I45" s="8" t="n">
         <v>3</v>
       </c>
@@ -4206,7 +4324,11 @@
           <t>Клапан быстрозапор. фланц.проход.с тросиков.приводом Ду80 Ру6,3</t>
         </is>
       </c>
-      <c r="H46" s="8" t="inlineStr"/>
+      <c r="H46" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I46" s="8" t="n">
         <v>2</v>
       </c>
@@ -4274,7 +4396,11 @@
           <t>Клапан фланцевый проходной Ду50</t>
         </is>
       </c>
-      <c r="H47" s="8" t="inlineStr"/>
+      <c r="H47" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I47" s="8" t="n">
         <v>66</v>
       </c>
@@ -4342,7 +4468,11 @@
           <t>Клапан фланцевый проходной Ду50 Ру25</t>
         </is>
       </c>
-      <c r="H48" s="8" t="inlineStr"/>
+      <c r="H48" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I48" s="8" t="n">
         <v>5</v>
       </c>
@@ -4410,7 +4540,11 @@
           <t>Клапан Пожарный фланцевый проходной Ду50 Ру16</t>
         </is>
       </c>
-      <c r="H49" s="8" t="inlineStr"/>
+      <c r="H49" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I49" s="8" t="n">
         <v>2</v>
       </c>
@@ -4478,7 +4612,11 @@
           <t>Захлопка Ду50Ру6 - БРАК</t>
         </is>
       </c>
-      <c r="H50" s="8" t="inlineStr"/>
+      <c r="H50" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I50" s="8" t="n">
         <v>3</v>
       </c>
@@ -4546,7 +4684,11 @@
           <t>Клапан фланцевый проходной Ду50 Ру 10 + ДУ 50 Ру 25</t>
         </is>
       </c>
-      <c r="H51" s="8" t="inlineStr"/>
+      <c r="H51" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I51" s="8" t="n">
         <v>98</v>
       </c>
@@ -4614,7 +4756,11 @@
           <t>Клапан фланцевый проходной Ду65</t>
         </is>
       </c>
-      <c r="H52" s="8" t="inlineStr"/>
+      <c r="H52" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I52" s="8" t="n">
         <v>25</v>
       </c>
@@ -4682,7 +4828,11 @@
           <t>Клапан фланцевый проходной Ду65 Ру10</t>
         </is>
       </c>
-      <c r="H53" s="8" t="inlineStr"/>
+      <c r="H53" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I53" s="8" t="n">
         <v>1</v>
       </c>
@@ -4750,7 +4900,11 @@
           <t>Клапан фланцевый проходной Ду70 Ру10</t>
         </is>
       </c>
-      <c r="H54" s="8" t="inlineStr"/>
+      <c r="H54" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I54" s="8" t="n">
         <v>5</v>
       </c>
@@ -4818,7 +4972,11 @@
           <t>Клапан фланцевый проходной Ду70 Ру10</t>
         </is>
       </c>
-      <c r="H55" s="8" t="inlineStr"/>
+      <c r="H55" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I55" s="8" t="n">
         <v>2</v>
       </c>
@@ -4886,7 +5044,11 @@
           <t>Клапан проходной фланцевый Ду50 - БРАК</t>
         </is>
       </c>
-      <c r="H56" s="8" t="inlineStr"/>
+      <c r="H56" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I56" s="8" t="n">
         <v>8</v>
       </c>
@@ -4954,7 +5116,11 @@
           <t>Клапан фланцевый проходной Ду80</t>
         </is>
       </c>
-      <c r="H57" s="8" t="inlineStr"/>
+      <c r="H57" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I57" s="8" t="n">
         <v>6</v>
       </c>
@@ -5018,7 +5184,11 @@
           <t>Электропривод к задвижке</t>
         </is>
       </c>
-      <c r="H58" s="8" t="inlineStr"/>
+      <c r="H58" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I58" s="8" t="n">
         <v>1</v>
       </c>
@@ -5068,12 +5238,12 @@
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t>фильтр забортной воды</t>
+          <t>сетка к фильтру</t>
         </is>
       </c>
       <c r="F59" s="8" t="inlineStr">
@@ -5086,7 +5256,11 @@
           <t>Сетка на фильтр Ду100 или Ду80</t>
         </is>
       </c>
-      <c r="H59" s="8" t="inlineStr"/>
+      <c r="H59" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I59" s="8" t="n">
         <v>2</v>
       </c>
@@ -5104,7 +5278,7 @@
       </c>
       <c r="N59" s="10" t="inlineStr">
         <is>
-          <t>Обрешетка, ставится верхним ярусом на ящики</t>
+          <t>Поддон, прокладки между рядами</t>
         </is>
       </c>
       <c r="O59" s="8" t="inlineStr">
@@ -5136,12 +5310,12 @@
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
-          <t>фильтр забортной воды</t>
+          <t>сетка к фильтру</t>
         </is>
       </c>
       <c r="F60" s="8" t="inlineStr">
@@ -5154,7 +5328,11 @@
           <t>Сетка на фильтр Ду100 (медь) на кингстон РС-300</t>
         </is>
       </c>
-      <c r="H60" s="8" t="inlineStr"/>
+      <c r="H60" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I60" s="8" t="n">
         <v>2</v>
       </c>
@@ -5172,7 +5350,7 @@
       </c>
       <c r="N60" s="10" t="inlineStr">
         <is>
-          <t>Обрешетка, ставится верхним ярусом на ящики</t>
+          <t>Поддон, прокладки между рядами</t>
         </is>
       </c>
       <c r="O60" s="8" t="inlineStr">
@@ -5222,7 +5400,11 @@
           <t>Клапан фланцевый проходной Ду200</t>
         </is>
       </c>
-      <c r="H61" s="8" t="inlineStr"/>
+      <c r="H61" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I61" s="8" t="n">
         <v>3</v>
       </c>
@@ -5290,7 +5472,11 @@
           <t>Клапан фланцевый проходной Ду 80 Ру 10, 521 -35.3451</t>
         </is>
       </c>
-      <c r="H62" s="8" t="inlineStr"/>
+      <c r="H62" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I62" s="8" t="n">
         <v>1</v>
       </c>
@@ -5358,7 +5544,11 @@
           <t>Захлопка фланцевая проходная Ду100Ру6,3</t>
         </is>
       </c>
-      <c r="H63" s="8" t="inlineStr"/>
+      <c r="H63" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I63" s="8" t="n">
         <v>1</v>
       </c>
@@ -5426,7 +5616,11 @@
           <t>Захлопка фланцевая горизон. Ду100 Ру10</t>
         </is>
       </c>
-      <c r="H64" s="8" t="inlineStr"/>
+      <c r="H64" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I64" s="8" t="n">
         <v>3</v>
       </c>
@@ -5494,7 +5688,11 @@
           <t>Захлопка фланцевая вертикальная Ду100</t>
         </is>
       </c>
-      <c r="H65" s="8" t="inlineStr"/>
+      <c r="H65" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I65" s="8" t="n">
         <v>1</v>
       </c>
@@ -5562,7 +5760,11 @@
           <t>Захлопка фланцевая угловая Ду100Ру10</t>
         </is>
       </c>
-      <c r="H66" s="8" t="inlineStr"/>
+      <c r="H66" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I66" s="8" t="n">
         <v>1</v>
       </c>
@@ -5630,7 +5832,11 @@
           <t>Задвижка клинкетная Ду60</t>
         </is>
       </c>
-      <c r="H67" s="8" t="inlineStr"/>
+      <c r="H67" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I67" s="8" t="n">
         <v>1</v>
       </c>
@@ -5698,7 +5904,11 @@
           <t>Клинкет Ду 200</t>
         </is>
       </c>
-      <c r="H68" s="8" t="inlineStr"/>
+      <c r="H68" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I68" s="8" t="n">
         <v>11</v>
       </c>
@@ -5766,7 +5976,11 @@
           <t>Клапан фланцевый проходной Ду150</t>
         </is>
       </c>
-      <c r="H69" s="8" t="inlineStr"/>
+      <c r="H69" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I69" s="8" t="n">
         <v>2</v>
       </c>
@@ -5834,7 +6048,11 @@
           <t>Клапан фланцевый проходной Ду100 Ру10</t>
         </is>
       </c>
-      <c r="H70" s="8" t="inlineStr"/>
+      <c r="H70" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I70" s="8" t="n">
         <v>5</v>
       </c>
@@ -5902,7 +6120,11 @@
           <t>Клапан фланцевый проходной Ду200 Ру6</t>
         </is>
       </c>
-      <c r="H71" s="8" t="inlineStr"/>
+      <c r="H71" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I71" s="8" t="n">
         <v>1</v>
       </c>
@@ -5970,7 +6192,11 @@
           <t>Кингстон донный фланцевый Ду80 Ру2,5</t>
         </is>
       </c>
-      <c r="H72" s="8" t="inlineStr"/>
+      <c r="H72" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I72" s="8" t="n">
         <v>2</v>
       </c>
@@ -6038,7 +6264,11 @@
           <t>Клапан проходной фланцевый Ду65 КОРПУС - БРАК</t>
         </is>
       </c>
-      <c r="H73" s="8" t="inlineStr"/>
+      <c r="H73" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I73" s="8" t="n">
         <v>1</v>
       </c>
@@ -6106,7 +6336,11 @@
           <t>Кингстон донный фланцевый Ду50 Ру2,5</t>
         </is>
       </c>
-      <c r="H74" s="8" t="inlineStr"/>
+      <c r="H74" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I74" s="8" t="n">
         <v>1</v>
       </c>
@@ -6174,7 +6408,11 @@
           <t>Кингстон донный фланцевый Ду50 Ру2,5</t>
         </is>
       </c>
-      <c r="H75" s="8" t="inlineStr"/>
+      <c r="H75" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I75" s="8" t="n">
         <v>1</v>
       </c>
@@ -6242,7 +6480,11 @@
           <t>Задвижка клинкетная Ду80 ( в разборе)</t>
         </is>
       </c>
-      <c r="H76" s="8" t="inlineStr"/>
+      <c r="H76" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I76" s="8" t="n">
         <v>2</v>
       </c>
@@ -6310,7 +6552,11 @@
           <t>Клапана невозвратный проходной фланцевый Ду100 Ру10 (522-03.205)</t>
         </is>
       </c>
-      <c r="H77" s="8" t="inlineStr"/>
+      <c r="H77" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I77" s="8" t="n">
         <v>5</v>
       </c>
@@ -6378,7 +6624,11 @@
           <t>Клапан фланцевый проходной Ду125</t>
         </is>
       </c>
-      <c r="H78" s="8" t="inlineStr"/>
+      <c r="H78" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I78" s="8" t="n">
         <v>6</v>
       </c>
@@ -6446,7 +6696,11 @@
           <t>Клапан фланцевый проходной Ду125 Ру10</t>
         </is>
       </c>
-      <c r="H79" s="8" t="inlineStr"/>
+      <c r="H79" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I79" s="8" t="n">
         <v>3</v>
       </c>
@@ -6496,12 +6750,12 @@
       </c>
       <c r="D80" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3, ящики</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="E80" s="8" t="inlineStr">
         <is>
-          <t>клинкет (задвижка)</t>
+          <t>блины к клинкету</t>
         </is>
       </c>
       <c r="F80" s="8" t="inlineStr">
@@ -6514,7 +6768,11 @@
           <t>Задвижка клинкетная Ду100 без штока и блинов ( в разборе)</t>
         </is>
       </c>
-      <c r="H80" s="8" t="inlineStr"/>
+      <c r="H80" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I80" s="8" t="n">
         <v>1</v>
       </c>
@@ -6582,7 +6840,11 @@
           <t>Клапан фланцевый проходной Ду125 ок.входа</t>
         </is>
       </c>
-      <c r="H81" s="8" t="inlineStr"/>
+      <c r="H81" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I81" s="8" t="n">
         <v>2</v>
       </c>
@@ -6650,7 +6912,11 @@
           <t>Клапан фланцевый проходной Ду 125 (без чертежа)</t>
         </is>
       </c>
-      <c r="H82" s="8" t="inlineStr"/>
+      <c r="H82" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I82" s="8" t="n">
         <v>1</v>
       </c>
@@ -6718,7 +6984,11 @@
           <t>Клапан невозвратно-приемный фланцевый Ду 50 Ру1 (522-35.4043-01)</t>
         </is>
       </c>
-      <c r="H83" s="8" t="inlineStr"/>
+      <c r="H83" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I83" s="8" t="n">
         <v>6</v>
       </c>
@@ -6786,7 +7056,11 @@
           <t>Клапан невозвратно-приемный фланцевый Ду 65 Ру1 (522-03.023)</t>
         </is>
       </c>
-      <c r="H84" s="8" t="inlineStr"/>
+      <c r="H84" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I84" s="8" t="n">
         <v>2</v>
       </c>
@@ -6854,7 +7128,11 @@
           <t>Клапан невозвратно-приемный фланцевый Ду 65 Ру1 (522-35.4044-01)</t>
         </is>
       </c>
-      <c r="H85" s="8" t="inlineStr"/>
+      <c r="H85" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I85" s="8" t="n">
         <v>1</v>
       </c>
@@ -6918,7 +7196,11 @@
           <t>Клапан</t>
         </is>
       </c>
-      <c r="H86" s="8" t="inlineStr"/>
+      <c r="H86" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I86" s="8" t="n">
         <v>1</v>
       </c>
@@ -6978,7 +7260,11 @@
           <t>Клапан фреоновый саленоидный</t>
         </is>
       </c>
-      <c r="H87" s="8" t="inlineStr"/>
+      <c r="H87" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I87" s="8" t="n">
         <v>2</v>
       </c>
@@ -7042,7 +7328,11 @@
           <t>Клапан паровой Ду65Ру10</t>
         </is>
       </c>
-      <c r="H88" s="8" t="inlineStr"/>
+      <c r="H88" s="8" t="inlineStr">
+        <is>
+          <t>сталь</t>
+        </is>
+      </c>
       <c r="I88" s="8" t="n">
         <v>1</v>
       </c>
@@ -7106,7 +7396,11 @@
           <t>Клапан фланц. концевой пожарный угловой Ду50 Ру25</t>
         </is>
       </c>
-      <c r="H89" s="8" t="inlineStr"/>
+      <c r="H89" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I89" s="8" t="n">
         <v>1</v>
       </c>
@@ -7170,7 +7464,11 @@
           <t>Клапан фланц. концевой пожарный угловой Ду50 Ру25</t>
         </is>
       </c>
-      <c r="H90" s="8" t="inlineStr"/>
+      <c r="H90" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I90" s="8" t="n">
         <v>1</v>
       </c>
@@ -7230,7 +7528,11 @@
           <t>Кланан Рр18-2 45/25</t>
         </is>
       </c>
-      <c r="H91" s="8" t="inlineStr"/>
+      <c r="H91" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I91" s="8" t="n">
         <v>1</v>
       </c>
@@ -7290,7 +7592,11 @@
           <t>Клапан электромагнитный б/у</t>
         </is>
       </c>
-      <c r="H92" s="8" t="inlineStr"/>
+      <c r="H92" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I92" s="8" t="n">
         <v>4</v>
       </c>
@@ -7354,7 +7660,11 @@
           <t>Клапан штуцерный угловой Ду10 Ру100</t>
         </is>
       </c>
-      <c r="H93" s="8" t="inlineStr"/>
+      <c r="H93" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I93" s="8" t="n">
         <v>1</v>
       </c>
@@ -7422,7 +7732,11 @@
           <t>Клапан предохранительный штуцерный угловой Ду6,5-9</t>
         </is>
       </c>
-      <c r="H94" s="8" t="inlineStr"/>
+      <c r="H94" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I94" s="8" t="n">
         <v>1</v>
       </c>
@@ -7490,7 +7804,11 @@
           <t>Клапан для манометра штущерный Ду3Ру400 новый</t>
         </is>
       </c>
-      <c r="H95" s="8" t="inlineStr"/>
+      <c r="H95" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I95" s="8" t="n">
         <v>2</v>
       </c>
@@ -7558,7 +7876,11 @@
           <t>Клапан для манометра штущерный сальниковый Ду6Ру100 новый</t>
         </is>
       </c>
-      <c r="H96" s="8" t="inlineStr"/>
+      <c r="H96" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I96" s="8" t="n">
         <v>95</v>
       </c>
@@ -7626,7 +7948,11 @@
           <t>Клапан для манометра штущерный сальниковый Ду6Ру100 б/у</t>
         </is>
       </c>
-      <c r="H97" s="8" t="inlineStr"/>
+      <c r="H97" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I97" s="8" t="n">
         <v>1</v>
       </c>
@@ -7694,7 +8020,11 @@
           <t>Клапан для манометра штущерный сальниковый Ду6Ру100 б/у</t>
         </is>
       </c>
-      <c r="H98" s="8" t="inlineStr"/>
+      <c r="H98" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I98" s="8" t="n">
         <v>1</v>
       </c>
@@ -7762,7 +8092,11 @@
           <t>Клапан предохранительный штуцерный сигнальный Ду6 Ру100-230</t>
         </is>
       </c>
-      <c r="H99" s="8" t="inlineStr"/>
+      <c r="H99" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I99" s="8" t="n">
         <v>1</v>
       </c>
@@ -7830,7 +8164,11 @@
           <t>Клапан предохранительный штуцерный сигнальный Ду6Ру100-250</t>
         </is>
       </c>
-      <c r="H100" s="8" t="inlineStr"/>
+      <c r="H100" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I100" s="8" t="n">
         <v>2</v>
       </c>
@@ -7898,7 +8236,11 @@
           <t>Клапан штуцерный проходной Ду 10 Ру400</t>
         </is>
       </c>
-      <c r="H101" s="8" t="inlineStr"/>
+      <c r="H101" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I101" s="8" t="n">
         <v>1</v>
       </c>
@@ -7966,7 +8308,11 @@
           <t>Клапан штуцерный проходной Ду 10 Ру400</t>
         </is>
       </c>
-      <c r="H102" s="8" t="inlineStr"/>
+      <c r="H102" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I102" s="8" t="n">
         <v>2</v>
       </c>
@@ -8034,7 +8380,11 @@
           <t>Клапан редукционный штуцерный угловой Ду10Ру200…30 с манометром</t>
         </is>
       </c>
-      <c r="H103" s="8" t="inlineStr"/>
+      <c r="H103" s="8" t="inlineStr">
+        <is>
+          <t>сталь</t>
+        </is>
+      </c>
       <c r="I103" s="8" t="n">
         <v>1</v>
       </c>
@@ -8102,7 +8452,11 @@
           <t>Клапан редукционный штуцерный угловой Ду10Ру200…30 с манометром</t>
         </is>
       </c>
-      <c r="H104" s="8" t="inlineStr"/>
+      <c r="H104" s="8" t="inlineStr">
+        <is>
+          <t>сталь</t>
+        </is>
+      </c>
       <c r="I104" s="8" t="n">
         <v>1</v>
       </c>
@@ -8170,7 +8524,11 @@
           <t>Клапан предохранительный штуцерный сигнальный Ду10Ру1,3-6,5</t>
         </is>
       </c>
-      <c r="H105" s="8" t="inlineStr"/>
+      <c r="H105" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I105" s="8" t="n">
         <v>1</v>
       </c>
@@ -8238,7 +8596,11 @@
           <t>Клапан предохранительный штуцерный сигнальный Ду10Ру2,5-6,5</t>
         </is>
       </c>
-      <c r="H106" s="8" t="inlineStr"/>
+      <c r="H106" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I106" s="8" t="n">
         <v>1</v>
       </c>
@@ -8306,7 +8668,11 @@
           <t>Клапан штущерный проходной Ду15</t>
         </is>
       </c>
-      <c r="H107" s="8" t="inlineStr"/>
+      <c r="H107" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I107" s="8" t="n">
         <v>44</v>
       </c>
@@ -8374,7 +8740,11 @@
           <t>Клапан штуцерный угловой Ду15 Ру160</t>
         </is>
       </c>
-      <c r="H108" s="8" t="inlineStr"/>
+      <c r="H108" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I108" s="8" t="n">
         <v>4</v>
       </c>
@@ -8442,7 +8812,11 @@
           <t>Клапан штуцерный угловой Ду15</t>
         </is>
       </c>
-      <c r="H109" s="8" t="inlineStr"/>
+      <c r="H109" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I109" s="8" t="n">
         <v>10</v>
       </c>
@@ -8510,7 +8884,11 @@
           <t>Клапан штуцерный проходной Ду 10 Ру100</t>
         </is>
       </c>
-      <c r="H110" s="8" t="inlineStr"/>
+      <c r="H110" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I110" s="8" t="n">
         <v>7</v>
       </c>
@@ -8578,7 +8956,11 @@
           <t>Кран штуцерный спусковой самозапорный проходной Ду15 Ру25</t>
         </is>
       </c>
-      <c r="H111" s="8" t="inlineStr"/>
+      <c r="H111" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I111" s="8" t="n">
         <v>4</v>
       </c>
@@ -8646,7 +9028,11 @@
           <t>Клапан штуцерный проходной невозвратный Ду10Ру100</t>
         </is>
       </c>
-      <c r="H112" s="8" t="inlineStr"/>
+      <c r="H112" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I112" s="8" t="n">
         <v>5</v>
       </c>
@@ -8714,7 +9100,11 @@
           <t>Клапан штуцерный проходной невозвратный Ду10Ру100</t>
         </is>
       </c>
-      <c r="H113" s="8" t="inlineStr"/>
+      <c r="H113" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I113" s="8" t="n">
         <v>1</v>
       </c>
@@ -8782,7 +9172,11 @@
           <t>Клапан запорный штуцерный проходной Ду10 Ру16</t>
         </is>
       </c>
-      <c r="H114" s="8" t="inlineStr"/>
+      <c r="H114" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I114" s="8" t="n">
         <v>6</v>
       </c>
@@ -8850,7 +9244,11 @@
           <t>Клапан штуцерный угловой Ду10 Р160</t>
         </is>
       </c>
-      <c r="H115" s="8" t="inlineStr"/>
+      <c r="H115" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I115" s="8" t="n">
         <v>6</v>
       </c>
@@ -8918,7 +9316,11 @@
           <t>Клапан штуцерный проходной Ду 15 Ру40</t>
         </is>
       </c>
-      <c r="H116" s="8" t="inlineStr"/>
+      <c r="H116" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I116" s="8" t="n">
         <v>1</v>
       </c>
@@ -8986,7 +9388,11 @@
           <t>Клапан штуцерный проходной Ду 15 Ру40</t>
         </is>
       </c>
-      <c r="H117" s="8" t="inlineStr"/>
+      <c r="H117" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I117" s="8" t="n">
         <v>1</v>
       </c>
@@ -9054,7 +9460,11 @@
           <t>Клапан штуцерный проходной Ду 15 Ру 40</t>
         </is>
       </c>
-      <c r="H118" s="8" t="inlineStr"/>
+      <c r="H118" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I118" s="8" t="n">
         <v>2</v>
       </c>
@@ -9122,7 +9532,11 @@
           <t>Клапан штуцерный проходной Ду 15 Ру 40</t>
         </is>
       </c>
-      <c r="H119" s="8" t="inlineStr"/>
+      <c r="H119" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I119" s="8" t="n">
         <v>1</v>
       </c>
@@ -9190,7 +9604,11 @@
           <t>Клапан штуцерный проходной Ду 15</t>
         </is>
       </c>
-      <c r="H120" s="8" t="inlineStr"/>
+      <c r="H120" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I120" s="8" t="n">
         <v>1</v>
       </c>
@@ -9258,7 +9676,11 @@
           <t>Клапан штуцерный проходной Ду 15</t>
         </is>
       </c>
-      <c r="H121" s="8" t="inlineStr"/>
+      <c r="H121" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I121" s="8" t="n">
         <v>1</v>
       </c>
@@ -9326,7 +9748,11 @@
           <t>Клапан штуцерный проходной Ду 15 Ру 100</t>
         </is>
       </c>
-      <c r="H122" s="8" t="inlineStr"/>
+      <c r="H122" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I122" s="8" t="n">
         <v>2</v>
       </c>
@@ -9394,7 +9820,11 @@
           <t>Клапан штуцерный проходной Ду 15 Ру 100</t>
         </is>
       </c>
-      <c r="H123" s="8" t="inlineStr"/>
+      <c r="H123" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I123" s="8" t="n">
         <v>1</v>
       </c>
@@ -9462,7 +9892,11 @@
           <t>Клапан штуцерный угловой Ду20 Ру160</t>
         </is>
       </c>
-      <c r="H124" s="8" t="inlineStr"/>
+      <c r="H124" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I124" s="8" t="n">
         <v>1</v>
       </c>
@@ -9530,7 +9964,11 @@
           <t>Кран штуцерный спусковой самозапорный проходной Ду20 Ру10</t>
         </is>
       </c>
-      <c r="H125" s="8" t="inlineStr"/>
+      <c r="H125" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I125" s="8" t="n">
         <v>36</v>
       </c>
@@ -9598,7 +10036,11 @@
           <t>Кран трехходовой штуцерный Ду20 Ру16</t>
         </is>
       </c>
-      <c r="H126" s="8" t="inlineStr"/>
+      <c r="H126" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I126" s="8" t="n">
         <v>7</v>
       </c>
@@ -9666,7 +10108,11 @@
           <t>Клапан штуцерный угловой Ду15Ру40</t>
         </is>
       </c>
-      <c r="H127" s="8" t="inlineStr"/>
+      <c r="H127" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I127" s="8" t="n">
         <v>2</v>
       </c>
@@ -9734,7 +10180,11 @@
           <t>Клапан штуцерный угловой Ду15Ру100</t>
         </is>
       </c>
-      <c r="H128" s="8" t="inlineStr"/>
+      <c r="H128" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I128" s="8" t="n">
         <v>3</v>
       </c>
@@ -9802,7 +10252,11 @@
           <t>Клапан штуцерный угловой Ду15Ру100</t>
         </is>
       </c>
-      <c r="H129" s="8" t="inlineStr"/>
+      <c r="H129" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I129" s="8" t="n">
         <v>6</v>
       </c>
@@ -9870,7 +10324,11 @@
           <t>Клапан штуцерный угловой Ду15Ру100</t>
         </is>
       </c>
-      <c r="H130" s="8" t="inlineStr"/>
+      <c r="H130" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I130" s="8" t="n">
         <v>7</v>
       </c>
@@ -9938,7 +10396,11 @@
           <t>Клапан штуцерный угловой Ду15 Ру100</t>
         </is>
       </c>
-      <c r="H131" s="8" t="inlineStr"/>
+      <c r="H131" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I131" s="8" t="n">
         <v>15</v>
       </c>
@@ -10006,7 +10468,11 @@
           <t>Клапан штуцерный угловой Ду15 Ру100</t>
         </is>
       </c>
-      <c r="H132" s="8" t="inlineStr"/>
+      <c r="H132" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I132" s="8" t="n">
         <v>2</v>
       </c>
@@ -10074,7 +10540,11 @@
           <t>Клапан штуцерный угловой Ду15 Ру100</t>
         </is>
       </c>
-      <c r="H133" s="8" t="inlineStr"/>
+      <c r="H133" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I133" s="8" t="n">
         <v>1</v>
       </c>
@@ -10142,7 +10612,11 @@
           <t>Клапан штуцерный угловой Ду15 Ру100</t>
         </is>
       </c>
-      <c r="H134" s="8" t="inlineStr"/>
+      <c r="H134" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I134" s="8" t="n">
         <v>3</v>
       </c>
@@ -10210,7 +10684,11 @@
           <t>Клапан штуцерный угловой Ду15 Ру100</t>
         </is>
       </c>
-      <c r="H135" s="8" t="inlineStr"/>
+      <c r="H135" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I135" s="8" t="n">
         <v>3</v>
       </c>
@@ -10278,7 +10756,11 @@
           <t>Клапан штуцерный угловой Ду15 Ру100</t>
         </is>
       </c>
-      <c r="H136" s="8" t="inlineStr"/>
+      <c r="H136" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I136" s="8" t="n">
         <v>1</v>
       </c>
@@ -10346,7 +10828,11 @@
           <t>Клапан штуцерный угловой Ду15 Ру160</t>
         </is>
       </c>
-      <c r="H137" s="8" t="inlineStr"/>
+      <c r="H137" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I137" s="8" t="n">
         <v>4</v>
       </c>
@@ -10414,7 +10900,11 @@
           <t>Клапан штуцерный проходной Ду 10 Ру40</t>
         </is>
       </c>
-      <c r="H138" s="8" t="inlineStr"/>
+      <c r="H138" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I138" s="8" t="n">
         <v>18</v>
       </c>
@@ -10482,7 +10972,11 @@
           <t>Клапан педальный Ду25</t>
         </is>
       </c>
-      <c r="H139" s="8" t="inlineStr"/>
+      <c r="H139" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I139" s="8" t="n">
         <v>1</v>
       </c>
@@ -10550,7 +11044,11 @@
           <t>Клапан штуцерный угловой Ду6Ру100</t>
         </is>
       </c>
-      <c r="H140" s="8" t="inlineStr"/>
+      <c r="H140" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I140" s="8" t="n">
         <v>3</v>
       </c>
@@ -10618,7 +11116,11 @@
           <t>Клапан штуцерный проходной Ду 20</t>
         </is>
       </c>
-      <c r="H141" s="8" t="inlineStr"/>
+      <c r="H141" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I141" s="8" t="n">
         <v>4</v>
       </c>
@@ -10686,7 +11188,11 @@
           <t>Клапан штуцерный проходной Ду 10 Ру100</t>
         </is>
       </c>
-      <c r="H142" s="8" t="inlineStr"/>
+      <c r="H142" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I142" s="8" t="n">
         <v>2</v>
       </c>
@@ -10754,7 +11260,11 @@
           <t>Кран трехходовой штуцерный Ду32 Ру10</t>
         </is>
       </c>
-      <c r="H143" s="8" t="inlineStr"/>
+      <c r="H143" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I143" s="8" t="n">
         <v>2</v>
       </c>
@@ -10822,7 +11332,11 @@
           <t>Клапан невозвратный штуцерный проходной Ду20Ру160</t>
         </is>
       </c>
-      <c r="H144" s="8" t="inlineStr"/>
+      <c r="H144" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I144" s="8" t="n">
         <v>1</v>
       </c>
@@ -10890,7 +11404,11 @@
           <t>Клапан штуцерный проходной Ду 20</t>
         </is>
       </c>
-      <c r="H145" s="8" t="inlineStr"/>
+      <c r="H145" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I145" s="8" t="n">
         <v>1</v>
       </c>
@@ -10958,7 +11476,11 @@
           <t>Клапан штуцерный проходной Ду 20 Ру 40</t>
         </is>
       </c>
-      <c r="H146" s="8" t="inlineStr"/>
+      <c r="H146" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I146" s="8" t="n">
         <v>2</v>
       </c>
@@ -11026,7 +11548,11 @@
           <t>Клапан штуцерный проходной Ду 20 Ру 40</t>
         </is>
       </c>
-      <c r="H147" s="8" t="inlineStr"/>
+      <c r="H147" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I147" s="8" t="n">
         <v>1</v>
       </c>
@@ -11094,7 +11620,11 @@
           <t>Клапан штуцерный проходной Ду 10 Ру6</t>
         </is>
       </c>
-      <c r="H148" s="8" t="inlineStr"/>
+      <c r="H148" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I148" s="8" t="n">
         <v>1</v>
       </c>
@@ -11311,7 +11841,11 @@
           <t>Задвижки (желтая) ок. крышек</t>
         </is>
       </c>
-      <c r="H4" s="8" t="inlineStr"/>
+      <c r="H4" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I4" s="8" t="n">
         <v>13</v>
       </c>
@@ -11363,12 +11897,12 @@
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3, ящики</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>клинкет (задвижка)</t>
+          <t>блины к клинкету</t>
         </is>
       </c>
       <c r="F5" s="8" t="inlineStr">
@@ -11381,7 +11915,11 @@
           <t>Блины к клинкету Ду100</t>
         </is>
       </c>
-      <c r="H5" s="8" t="inlineStr"/>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I5" s="8" t="n">
         <v>11</v>
       </c>
@@ -11451,7 +11989,11 @@
           <t>Клапан штуцерный проходной Ду 10 Ру40 (СУНДУК)</t>
         </is>
       </c>
-      <c r="H6" s="8" t="inlineStr"/>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I6" s="8" t="n">
         <v>798</v>
       </c>
@@ -11525,7 +12067,11 @@
           <t>Клапан штуцерный проходной Ду 10</t>
         </is>
       </c>
-      <c r="H7" s="8" t="inlineStr"/>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I7" s="8" t="n">
         <v>83</v>
       </c>
@@ -11599,7 +12145,11 @@
           <t>Клапан педальный Ду25 Китай</t>
         </is>
       </c>
-      <c r="H8" s="8" t="inlineStr"/>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I8" s="8" t="n">
         <v>62</v>
       </c>
@@ -11673,7 +12223,11 @@
           <t>Клапан штуцерный проходной Ду 20</t>
         </is>
       </c>
-      <c r="H9" s="8" t="inlineStr"/>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I9" s="8" t="n">
         <v>100</v>
       </c>
@@ -11747,7 +12301,11 @@
           <t>Клапан штуцерный проходной Ду 25 (Китай)</t>
         </is>
       </c>
-      <c r="H10" s="8" t="inlineStr"/>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I10" s="8" t="n">
         <v>79</v>
       </c>
@@ -11821,7 +12379,11 @@
           <t>Клапан штуцерный проходной Ду 20 Ру10</t>
         </is>
       </c>
-      <c r="H11" s="8" t="inlineStr"/>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I11" s="8" t="n">
         <v>5</v>
       </c>
@@ -11895,7 +12457,11 @@
           <t>Клапан штуцерный проходной Ду 20 Ру 40</t>
         </is>
       </c>
-      <c r="H12" s="8" t="inlineStr"/>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I12" s="8" t="n">
         <v>4</v>
       </c>
@@ -11969,7 +12535,11 @@
           <t>Клапан штуцерный проходной Ду 20 Ру 40</t>
         </is>
       </c>
-      <c r="H13" s="8" t="inlineStr"/>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I13" s="8" t="n">
         <v>72</v>
       </c>
@@ -12043,7 +12613,11 @@
           <t>Клапан штуцерный проходной Ду 20 Ру 40</t>
         </is>
       </c>
-      <c r="H14" s="8" t="inlineStr"/>
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I14" s="8" t="n">
         <v>11</v>
       </c>
@@ -12117,7 +12691,11 @@
           <t>Клапан штуцерный проходной Ду 20 Ру 40</t>
         </is>
       </c>
-      <c r="H15" s="8" t="inlineStr"/>
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I15" s="8" t="n">
         <v>11</v>
       </c>
@@ -12191,7 +12769,11 @@
           <t>Клапан штуцерный проходной Ду 20 Ру 40</t>
         </is>
       </c>
-      <c r="H16" s="8" t="inlineStr"/>
+      <c r="H16" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I16" s="8" t="n">
         <v>23</v>
       </c>
@@ -12265,7 +12847,11 @@
           <t>Клапан штуцерный проходной Ду 20 Ру 40</t>
         </is>
       </c>
-      <c r="H17" s="8" t="inlineStr"/>
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I17" s="8" t="n">
         <v>3</v>
       </c>
@@ -12339,7 +12925,11 @@
           <t>Клапан штуцерный проходной Ду 20 Ру 64</t>
         </is>
       </c>
-      <c r="H18" s="8" t="inlineStr"/>
+      <c r="H18" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I18" s="8" t="n">
         <v>1</v>
       </c>
@@ -12413,7 +13003,11 @@
           <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
         </is>
       </c>
-      <c r="H19" s="8" t="inlineStr"/>
+      <c r="H19" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I19" s="8" t="n">
         <v>1</v>
       </c>
@@ -12487,7 +13081,11 @@
           <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
         </is>
       </c>
-      <c r="H20" s="8" t="inlineStr"/>
+      <c r="H20" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I20" s="8" t="n">
         <v>13</v>
       </c>
@@ -12561,7 +13159,11 @@
           <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
         </is>
       </c>
-      <c r="H21" s="8" t="inlineStr"/>
+      <c r="H21" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I21" s="8" t="n">
         <v>102</v>
       </c>
@@ -12635,7 +13237,11 @@
           <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
         </is>
       </c>
-      <c r="H22" s="8" t="inlineStr"/>
+      <c r="H22" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I22" s="8" t="n">
         <v>1</v>
       </c>
@@ -12709,7 +13315,11 @@
           <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
         </is>
       </c>
-      <c r="H23" s="8" t="inlineStr"/>
+      <c r="H23" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I23" s="8" t="n">
         <v>2</v>
       </c>
@@ -12783,7 +13393,11 @@
           <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
         </is>
       </c>
-      <c r="H24" s="8" t="inlineStr"/>
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I24" s="8" t="n">
         <v>2</v>
       </c>
@@ -12857,7 +13471,11 @@
           <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
         </is>
       </c>
-      <c r="H25" s="8" t="inlineStr"/>
+      <c r="H25" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I25" s="8" t="n">
         <v>21</v>
       </c>
@@ -12931,7 +13549,11 @@
           <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
         </is>
       </c>
-      <c r="H26" s="8" t="inlineStr"/>
+      <c r="H26" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I26" s="8" t="n">
         <v>16</v>
       </c>
@@ -13005,7 +13627,11 @@
           <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
         </is>
       </c>
-      <c r="H27" s="8" t="inlineStr"/>
+      <c r="H27" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I27" s="8" t="n">
         <v>2</v>
       </c>
@@ -13079,7 +13705,11 @@
           <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
         </is>
       </c>
-      <c r="H28" s="8" t="inlineStr"/>
+      <c r="H28" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I28" s="8" t="n">
         <v>7</v>
       </c>
@@ -13153,7 +13783,11 @@
           <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
         </is>
       </c>
-      <c r="H29" s="8" t="inlineStr"/>
+      <c r="H29" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I29" s="8" t="n">
         <v>9</v>
       </c>
@@ -13227,7 +13861,11 @@
           <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
         </is>
       </c>
-      <c r="H30" s="8" t="inlineStr"/>
+      <c r="H30" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I30" s="8" t="n">
         <v>1</v>
       </c>
@@ -13301,7 +13939,11 @@
           <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
         </is>
       </c>
-      <c r="H31" s="8" t="inlineStr"/>
+      <c r="H31" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I31" s="8" t="n">
         <v>1</v>
       </c>
@@ -13375,7 +14017,11 @@
           <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
         </is>
       </c>
-      <c r="H32" s="8" t="inlineStr"/>
+      <c r="H32" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I32" s="8" t="n">
         <v>3</v>
       </c>
@@ -13449,7 +14095,11 @@
           <t>Клапан штуцерный проходной Ду 32 Ру 40</t>
         </is>
       </c>
-      <c r="H33" s="8" t="inlineStr"/>
+      <c r="H33" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I33" s="8" t="n">
         <v>3</v>
       </c>
@@ -13523,7 +14173,11 @@
           <t>Клапан штуцерный угловой Ду10 Ру100</t>
         </is>
       </c>
-      <c r="H34" s="8" t="inlineStr"/>
+      <c r="H34" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I34" s="8" t="n">
         <v>1</v>
       </c>
@@ -13597,7 +14251,11 @@
           <t>Клапан штуцерный угловой Ду10 Ру100</t>
         </is>
       </c>
-      <c r="H35" s="8" t="inlineStr"/>
+      <c r="H35" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I35" s="8" t="n">
         <v>1</v>
       </c>
@@ -13671,7 +14329,11 @@
           <t>Клапан штуцерный проходной Ду 10 Ру 40</t>
         </is>
       </c>
-      <c r="H36" s="8" t="inlineStr"/>
+      <c r="H36" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I36" s="8" t="n">
         <v>4</v>
       </c>
@@ -13745,7 +14407,11 @@
           <t>Клапан штуцерный проходной Ду 10 Ру 40</t>
         </is>
       </c>
-      <c r="H37" s="8" t="inlineStr"/>
+      <c r="H37" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I37" s="8" t="n">
         <v>1</v>
       </c>
@@ -13819,7 +14485,11 @@
           <t>Клапан штуцерный проходной Ду 10 Ру100</t>
         </is>
       </c>
-      <c r="H38" s="8" t="inlineStr"/>
+      <c r="H38" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I38" s="8" t="n">
         <v>5</v>
       </c>
@@ -13893,7 +14563,11 @@
           <t>Клапан штуцерный проходной Ду 10 Ру100</t>
         </is>
       </c>
-      <c r="H39" s="8" t="inlineStr"/>
+      <c r="H39" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I39" s="8" t="n">
         <v>3</v>
       </c>
@@ -13967,7 +14641,11 @@
           <t>Клапан штуцерный проходной Ду 10 Ру100</t>
         </is>
       </c>
-      <c r="H40" s="8" t="inlineStr"/>
+      <c r="H40" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I40" s="8" t="n">
         <v>3</v>
       </c>
@@ -14041,7 +14719,11 @@
           <t>Клапан штуцерный проходной Ду 10 Ру100</t>
         </is>
       </c>
-      <c r="H41" s="8" t="inlineStr"/>
+      <c r="H41" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I41" s="8" t="n">
         <v>1</v>
       </c>
@@ -14115,7 +14797,11 @@
           <t>Клапан штуцерный проходной Ду 10 Ру100</t>
         </is>
       </c>
-      <c r="H42" s="8" t="inlineStr"/>
+      <c r="H42" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I42" s="8" t="n">
         <v>2</v>
       </c>
@@ -14189,7 +14875,11 @@
           <t>Клапан штуцерный проходной Ду 10 Ру100</t>
         </is>
       </c>
-      <c r="H43" s="8" t="inlineStr"/>
+      <c r="H43" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I43" s="8" t="n">
         <v>1</v>
       </c>
@@ -14263,7 +14953,11 @@
           <t>Клапан штуцерный проходной Ду 10</t>
         </is>
       </c>
-      <c r="H44" s="8" t="inlineStr"/>
+      <c r="H44" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I44" s="8" t="n">
         <v>4</v>
       </c>
@@ -14337,7 +15031,11 @@
           <t>Клапан невозв-запор.цапковый угловой под дюрит Ду20Ру6</t>
         </is>
       </c>
-      <c r="H45" s="8" t="inlineStr"/>
+      <c r="H45" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I45" s="8" t="n">
         <v>2</v>
       </c>
@@ -14411,7 +15109,11 @@
           <t>Клапан штуцерный угловой Ду25</t>
         </is>
       </c>
-      <c r="H46" s="8" t="inlineStr"/>
+      <c r="H46" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I46" s="8" t="n">
         <v>1</v>
       </c>
@@ -14485,7 +15187,11 @@
           <t>Клапан штуцерный угловой Ду25</t>
         </is>
       </c>
-      <c r="H47" s="8" t="inlineStr"/>
+      <c r="H47" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I47" s="8" t="n">
         <v>1</v>
       </c>
@@ -14559,7 +15265,11 @@
           <t>Клапан штуцерный угловой Ду25</t>
         </is>
       </c>
-      <c r="H48" s="8" t="inlineStr"/>
+      <c r="H48" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I48" s="8" t="n">
         <v>6</v>
       </c>
@@ -14629,7 +15339,11 @@
           <t>Клапан для манометра штуцерный сальниковый</t>
         </is>
       </c>
-      <c r="H49" s="8" t="inlineStr"/>
+      <c r="H49" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I49" s="8" t="n">
         <v>18</v>
       </c>
@@ -14703,7 +15417,11 @@
           <t>Клапан штуцерный угловой Ду20 ру 40</t>
         </is>
       </c>
-      <c r="H50" s="8" t="inlineStr"/>
+      <c r="H50" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I50" s="8" t="n">
         <v>1</v>
       </c>
@@ -14777,7 +15495,11 @@
           <t>Клапан штуцерный угловой Ду20 ру 40</t>
         </is>
       </c>
-      <c r="H51" s="8" t="inlineStr"/>
+      <c r="H51" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I51" s="8" t="n">
         <v>2</v>
       </c>
@@ -14851,7 +15573,11 @@
           <t>Клапан штуцерный угловой Ду20 ру 40</t>
         </is>
       </c>
-      <c r="H52" s="8" t="inlineStr"/>
+      <c r="H52" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I52" s="8" t="n">
         <v>1</v>
       </c>
@@ -14925,7 +15651,11 @@
           <t>Клапан штуцерный угловой Ду20 Ру160</t>
         </is>
       </c>
-      <c r="H53" s="8" t="inlineStr"/>
+      <c r="H53" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I53" s="8" t="n">
         <v>3</v>
       </c>
@@ -14999,7 +15729,11 @@
           <t>Клапан штуцерный угловой Ду25 Ру100</t>
         </is>
       </c>
-      <c r="H54" s="8" t="inlineStr"/>
+      <c r="H54" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I54" s="8" t="n">
         <v>8</v>
       </c>
@@ -15073,7 +15807,11 @@
           <t>Клапан штуцерный угловой Ду25 Ру100</t>
         </is>
       </c>
-      <c r="H55" s="8" t="inlineStr"/>
+      <c r="H55" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I55" s="8" t="n">
         <v>1</v>
       </c>
@@ -15147,7 +15885,11 @@
           <t>Клапан штуцерный угловой Ду25 Ру100</t>
         </is>
       </c>
-      <c r="H56" s="8" t="inlineStr"/>
+      <c r="H56" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I56" s="8" t="n">
         <v>2</v>
       </c>
@@ -15221,7 +15963,11 @@
           <t>Клапан штуцерный угловой Ду32Ру100 (Яшик мет.)</t>
         </is>
       </c>
-      <c r="H57" s="8" t="inlineStr"/>
+      <c r="H57" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I57" s="8" t="n">
         <v>31</v>
       </c>
@@ -15295,7 +16041,11 @@
           <t>Клапан штуцерный угловой Ду32Ру100 (Яшик мет.)</t>
         </is>
       </c>
-      <c r="H58" s="8" t="inlineStr"/>
+      <c r="H58" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I58" s="8" t="n">
         <v>14</v>
       </c>
@@ -15369,7 +16119,11 @@
           <t>Клапан штуцерный угловой Ду32Ру100 (Яшик мет.)</t>
         </is>
       </c>
-      <c r="H59" s="8" t="inlineStr"/>
+      <c r="H59" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I59" s="8" t="n">
         <v>1</v>
       </c>
@@ -15443,7 +16197,11 @@
           <t>Клапан штуцерный угловой Ду32Ру100 (Яшик мет.)</t>
         </is>
       </c>
-      <c r="H60" s="8" t="inlineStr"/>
+      <c r="H60" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I60" s="8" t="n">
         <v>1</v>
       </c>
@@ -15517,7 +16275,11 @@
           <t>Клапан штуцерный угловой Ду32</t>
         </is>
       </c>
-      <c r="H61" s="8" t="inlineStr"/>
+      <c r="H61" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I61" s="8" t="n">
         <v>8</v>
       </c>
@@ -15591,7 +16353,11 @@
           <t>Клапан штуцерный угловой Ду32 Ру100</t>
         </is>
       </c>
-      <c r="H62" s="8" t="inlineStr"/>
+      <c r="H62" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I62" s="8" t="n">
         <v>39</v>
       </c>
@@ -15665,7 +16431,11 @@
           <t>Клапан штуцерный угловой Ду32 Ру100</t>
         </is>
       </c>
-      <c r="H63" s="8" t="inlineStr"/>
+      <c r="H63" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I63" s="8" t="n">
         <v>2</v>
       </c>
@@ -15739,7 +16509,11 @@
           <t>Клапан штуцерный угловой Ду32 Ру100</t>
         </is>
       </c>
-      <c r="H64" s="8" t="inlineStr"/>
+      <c r="H64" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I64" s="8" t="n">
         <v>1</v>
       </c>
@@ -15813,7 +16587,11 @@
           <t>Клапан штуцерный угловой Ду32 Ру160</t>
         </is>
       </c>
-      <c r="H65" s="8" t="inlineStr"/>
+      <c r="H65" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I65" s="8" t="n">
         <v>8</v>
       </c>
@@ -15887,7 +16665,11 @@
           <t>Клапан штуцерный угловой Ду32 Ру160</t>
         </is>
       </c>
-      <c r="H66" s="8" t="inlineStr"/>
+      <c r="H66" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I66" s="8" t="n">
         <v>16</v>
       </c>
@@ -15961,7 +16743,11 @@
           <t>Клапан невозвратный штуцерный проходной Ду20 Ру40</t>
         </is>
       </c>
-      <c r="H67" s="8" t="inlineStr"/>
+      <c r="H67" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I67" s="8" t="n">
         <v>1</v>
       </c>
@@ -16035,7 +16821,11 @@
           <t>Кран двухходовой штуцерный Ду20 Ру16</t>
         </is>
       </c>
-      <c r="H68" s="8" t="inlineStr"/>
+      <c r="H68" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I68" s="8" t="n">
         <v>3</v>
       </c>
@@ -16109,7 +16899,11 @@
           <t>Клапан быстрозапор. фланц. проход. с тросиков. приводом Ду40Ру6,3</t>
         </is>
       </c>
-      <c r="H69" s="8" t="inlineStr"/>
+      <c r="H69" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I69" s="8" t="n">
         <v>7</v>
       </c>
@@ -16183,7 +16977,11 @@
           <t>Клапан фланцевый проходной ДУ20 Ру25</t>
         </is>
       </c>
-      <c r="H70" s="8" t="inlineStr"/>
+      <c r="H70" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I70" s="8" t="n">
         <v>8</v>
       </c>
@@ -16257,7 +17055,11 @@
           <t>Кран двухходовой фланцевый Ду32 Ру6</t>
         </is>
       </c>
-      <c r="H71" s="8" t="inlineStr"/>
+      <c r="H71" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I71" s="8" t="n">
         <v>1</v>
       </c>
@@ -16331,7 +17133,11 @@
           <t>Клапан фланцевый проходной ДУ25 ???</t>
         </is>
       </c>
-      <c r="H72" s="8" t="inlineStr"/>
+      <c r="H72" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I72" s="8" t="n">
         <v>1</v>
       </c>
@@ -16405,7 +17211,11 @@
           <t>Клапан штуцерный угловой Ду20 Ру100</t>
         </is>
       </c>
-      <c r="H73" s="8" t="inlineStr"/>
+      <c r="H73" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I73" s="8" t="n">
         <v>5</v>
       </c>
@@ -16475,7 +17285,11 @@
           <t>Клапан штуцерный угловой Рр150/10</t>
         </is>
       </c>
-      <c r="H74" s="8" t="inlineStr"/>
+      <c r="H74" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I74" s="8" t="n">
         <v>8</v>
       </c>
@@ -16531,12 +17345,12 @@
       </c>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t>Ярус 4, верх</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E75" s="8" t="inlineStr">
         <is>
-          <t>фильтр забортной воды</t>
+          <t>сетка к фильтру</t>
         </is>
       </c>
       <c r="F75" s="8" t="inlineStr">
@@ -16549,7 +17363,11 @@
           <t>Сетка на фильтр Ду20 маленькая</t>
         </is>
       </c>
-      <c r="H75" s="8" t="inlineStr"/>
+      <c r="H75" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I75" s="8" t="n">
         <v>1</v>
       </c>
@@ -16567,7 +17385,7 @@
       </c>
       <c r="N75" s="10" t="inlineStr">
         <is>
-          <t>Обрешетка, ставится верхним ярусом на ящики</t>
+          <t>Ящик сплошной, с перегородками</t>
         </is>
       </c>
       <c r="O75" s="8" t="inlineStr">
@@ -16623,7 +17441,11 @@
           <t>Клапан фланцевый проходной ДУ32 Ру25</t>
         </is>
       </c>
-      <c r="H76" s="8" t="inlineStr"/>
+      <c r="H76" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I76" s="8" t="n">
         <v>2</v>
       </c>
@@ -16697,7 +17519,11 @@
           <t>Клапан фланцевый проходной ДУ32 Ру25</t>
         </is>
       </c>
-      <c r="H77" s="8" t="inlineStr"/>
+      <c r="H77" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I77" s="8" t="n">
         <v>6</v>
       </c>
@@ -16771,7 +17597,11 @@
           <t>Клапан Пожарный фланцевый угловой Ду32</t>
         </is>
       </c>
-      <c r="H78" s="8" t="inlineStr"/>
+      <c r="H78" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I78" s="8" t="n">
         <v>1</v>
       </c>
@@ -16845,7 +17675,11 @@
           <t>Клапан угловой фланцевый Ду 40 - БРАК</t>
         </is>
       </c>
-      <c r="H79" s="8" t="inlineStr"/>
+      <c r="H79" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I79" s="8" t="n">
         <v>3</v>
       </c>
@@ -16919,7 +17753,11 @@
           <t>Клапан Ду20/10</t>
         </is>
       </c>
-      <c r="H80" s="8" t="inlineStr"/>
+      <c r="H80" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I80" s="8" t="n">
         <v>3</v>
       </c>
@@ -16993,7 +17831,11 @@
           <t>Клапан проходной фланцевый Ду32 - БРАК</t>
         </is>
       </c>
-      <c r="H81" s="8" t="inlineStr"/>
+      <c r="H81" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I81" s="8" t="n">
         <v>6</v>
       </c>
@@ -17067,7 +17909,11 @@
           <t>Клапан угловой с присоединением под дюрит Ду50Ру4</t>
         </is>
       </c>
-      <c r="H82" s="8" t="inlineStr"/>
+      <c r="H82" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I82" s="8" t="n">
         <v>4</v>
       </c>
@@ -17141,7 +17987,11 @@
           <t>Клапан невозв-запорн.с присоед.под дюрит прох. Ду 50 Ру6</t>
         </is>
       </c>
-      <c r="H83" s="8" t="inlineStr"/>
+      <c r="H83" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I83" s="8" t="n">
         <v>1</v>
       </c>
@@ -17215,7 +18065,11 @@
           <t>Клапан предохранит. фланцевый угловой Ду32Ру4 (524-03.090)</t>
         </is>
       </c>
-      <c r="H84" s="8" t="inlineStr"/>
+      <c r="H84" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I84" s="8" t="n">
         <v>1</v>
       </c>
@@ -17289,7 +18143,11 @@
           <t>Клапан проходной фланцевый Ду40 - БРАК</t>
         </is>
       </c>
-      <c r="H85" s="8" t="inlineStr"/>
+      <c r="H85" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I85" s="8" t="n">
         <v>13</v>
       </c>
@@ -17363,7 +18221,11 @@
           <t>Клапан для колонки указательной Ду10 Ру16</t>
         </is>
       </c>
-      <c r="H86" s="8" t="inlineStr"/>
+      <c r="H86" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I86" s="8" t="n">
         <v>6</v>
       </c>
@@ -17437,7 +18299,11 @@
           <t>Клапан муфтовый проходной запорный Ду20Ру16</t>
         </is>
       </c>
-      <c r="H87" s="8" t="inlineStr"/>
+      <c r="H87" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I87" s="8" t="n">
         <v>1</v>
       </c>
@@ -17511,7 +18377,11 @@
           <t>Клапан муфтовый проходной запорный Ду25Ру16</t>
         </is>
       </c>
-      <c r="H88" s="8" t="inlineStr"/>
+      <c r="H88" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I88" s="8" t="n">
         <v>2</v>
       </c>
@@ -17585,7 +18455,11 @@
           <t>Клапан муфтовый проходной запорный Ду32Ру10</t>
         </is>
       </c>
-      <c r="H89" s="8" t="inlineStr"/>
+      <c r="H89" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I89" s="8" t="n">
         <v>1</v>
       </c>
@@ -17659,7 +18533,11 @@
           <t>Клапан штуцерный проходной бессальниковый Ду15/1</t>
         </is>
       </c>
-      <c r="H90" s="8" t="inlineStr"/>
+      <c r="H90" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I90" s="8" t="n">
         <v>3</v>
       </c>
@@ -17729,7 +18607,11 @@
           <t>(Кнопка)Клапан самозакрывающий проходной муфтовый Ду15Ру3</t>
         </is>
       </c>
-      <c r="H91" s="8" t="inlineStr"/>
+      <c r="H91" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I91" s="8" t="n">
         <v>1</v>
       </c>
@@ -17795,7 +18677,11 @@
           <t>Клапан дроссельный угловой штуцерный</t>
         </is>
       </c>
-      <c r="H92" s="8" t="inlineStr"/>
+      <c r="H92" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I92" s="8" t="n">
         <v>1</v>
       </c>
@@ -17865,7 +18751,11 @@
           <t>Клапан штуцерный угловой Ду10 Ру100</t>
         </is>
       </c>
-      <c r="H93" s="8" t="inlineStr"/>
+      <c r="H93" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I93" s="8" t="n">
         <v>1</v>
       </c>
@@ -17931,7 +18821,11 @@
           <t>Клапан штуцерный угловой Ду НЕРЖ</t>
         </is>
       </c>
-      <c r="H94" s="8" t="inlineStr"/>
+      <c r="H94" s="8" t="inlineStr">
+        <is>
+          <t>нержавейка</t>
+        </is>
+      </c>
       <c r="I94" s="8" t="n">
         <v>1</v>
       </c>
@@ -18001,7 +18895,11 @@
           <t>Клапан редукционный штуц.проход.односедельный Ду20Ру400 у входа</t>
         </is>
       </c>
-      <c r="H95" s="8" t="inlineStr"/>
+      <c r="H95" s="8" t="inlineStr">
+        <is>
+          <t>сталь</t>
+        </is>
+      </c>
       <c r="I95" s="8" t="n">
         <v>9</v>
       </c>
@@ -18071,7 +18969,11 @@
           <t>Клапан с электромагнитным ручным управлением Ду20/10 перем. 220В</t>
         </is>
       </c>
-      <c r="H96" s="8" t="inlineStr"/>
+      <c r="H96" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I96" s="8" t="n">
         <v>1</v>
       </c>
@@ -18141,7 +19043,11 @@
           <t>Клапан пусковой Ду20Ру125</t>
         </is>
       </c>
-      <c r="H97" s="8" t="inlineStr"/>
+      <c r="H97" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I97" s="8" t="n">
         <v>7</v>
       </c>
@@ -18211,7 +19117,11 @@
           <t>Клапан пусковой Ду32Ру125</t>
         </is>
       </c>
-      <c r="H98" s="8" t="inlineStr"/>
+      <c r="H98" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I98" s="8" t="n">
         <v>8</v>
       </c>
@@ -18281,7 +19191,11 @@
           <t>Клапан фланц. концевой пожарный угловой Ду32 Ру10</t>
         </is>
       </c>
-      <c r="H99" s="8" t="inlineStr"/>
+      <c r="H99" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I99" s="8" t="n">
         <v>1</v>
       </c>
@@ -18351,7 +19265,11 @@
           <t>Клапан фланц. концевой пожарный угловой Ду32 Ру16</t>
         </is>
       </c>
-      <c r="H100" s="8" t="inlineStr"/>
+      <c r="H100" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I100" s="8" t="n">
         <v>2</v>
       </c>
@@ -18421,7 +19339,11 @@
           <t>Клапан невозв-запорн.с присоед.под дюрит прох. Ду 50</t>
         </is>
       </c>
-      <c r="H101" s="8" t="inlineStr"/>
+      <c r="H101" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I101" s="8" t="n">
         <v>10</v>
       </c>
@@ -18491,7 +19413,11 @@
           <t>Клапан запорн.с присоед.под дюрит прох. Ду65</t>
         </is>
       </c>
-      <c r="H102" s="8" t="inlineStr"/>
+      <c r="H102" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I102" s="8" t="n">
         <v>20</v>
       </c>
@@ -18714,7 +19640,11 @@
           <t>Коробка 3-х клап.фланцевая невозврат.Ду80 Ру6</t>
         </is>
       </c>
-      <c r="H4" s="8" t="inlineStr"/>
+      <c r="H4" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I4" s="8" t="n">
         <v>6</v>
       </c>
@@ -18788,7 +19718,11 @@
           <t>Коробка 2-х клапановая фланцевая Ду50</t>
         </is>
       </c>
-      <c r="H5" s="8" t="inlineStr"/>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I5" s="8" t="n">
         <v>4</v>
       </c>
@@ -18862,7 +19796,11 @@
           <t>Коробка 2-х клапановая фланцевая Ду80</t>
         </is>
       </c>
-      <c r="H6" s="8" t="inlineStr"/>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I6" s="8" t="n">
         <v>2</v>
       </c>
@@ -19014,7 +19952,11 @@
           <t>Коробка 2-х клапановая фланцевая Ду80</t>
         </is>
       </c>
-      <c r="H8" s="8" t="inlineStr"/>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I8" s="8" t="n">
         <v>2</v>
       </c>
@@ -19088,7 +20030,11 @@
           <t>Коробка 2-х клапановая фланцевая Ду80</t>
         </is>
       </c>
-      <c r="H9" s="8" t="inlineStr"/>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I9" s="8" t="n">
         <v>15</v>
       </c>
@@ -19544,7 +20490,11 @@
           <t>Коробка 2-х клапанная корпус</t>
         </is>
       </c>
-      <c r="H15" s="8" t="inlineStr"/>
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I15" s="8" t="n">
         <v>1</v>
       </c>
@@ -19696,7 +20646,11 @@
           <t>Коробка 3-х клап.фланцевая Ду50</t>
         </is>
       </c>
-      <c r="H17" s="8" t="inlineStr"/>
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I17" s="8" t="n">
         <v>3</v>
       </c>
@@ -19766,7 +20720,11 @@
           <t>Коробка 3-х клап.фланцевая Ду80</t>
         </is>
       </c>
-      <c r="H18" s="8" t="inlineStr"/>
+      <c r="H18" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I18" s="8" t="n">
         <v>8</v>
       </c>
@@ -19836,7 +20794,11 @@
           <t>Коробка 3-х клап.фланцевая Ду100</t>
         </is>
       </c>
-      <c r="H19" s="8" t="inlineStr"/>
+      <c r="H19" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I19" s="8" t="n">
         <v>1</v>
       </c>
@@ -19906,7 +20868,11 @@
           <t>Коробка 2-х клапановая фланцевая Ду50</t>
         </is>
       </c>
-      <c r="H20" s="8" t="inlineStr"/>
+      <c r="H20" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I20" s="8" t="n">
         <v>2</v>
       </c>
@@ -19976,7 +20942,11 @@
           <t>Коробка 2-х клапановая фланцевая Ду80</t>
         </is>
       </c>
-      <c r="H21" s="8" t="inlineStr"/>
+      <c r="H21" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I21" s="8" t="n">
         <v>13</v>
       </c>
@@ -20046,7 +21016,11 @@
           <t>Коробка 3-х клап.фланцевая запорная Ду50 Ру6</t>
         </is>
       </c>
-      <c r="H22" s="8" t="inlineStr"/>
+      <c r="H22" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I22" s="8" t="n">
         <v>1</v>
       </c>
@@ -20116,7 +21090,11 @@
           <t>Коробка 3-х клап.фланцевая запорная Ду50 Ру6</t>
         </is>
       </c>
-      <c r="H23" s="8" t="inlineStr"/>
+      <c r="H23" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I23" s="8" t="n">
         <v>2</v>
       </c>
@@ -20186,7 +21164,11 @@
           <t>Коробка 3-х клап.фланцевая невозврат.Ду80 Ру6</t>
         </is>
       </c>
-      <c r="H24" s="8" t="inlineStr"/>
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I24" s="8" t="n">
         <v>2</v>
       </c>
@@ -20256,7 +21238,11 @@
           <t>Коробка 3-х клап.фланцевая Ду80</t>
         </is>
       </c>
-      <c r="H25" s="8" t="inlineStr"/>
+      <c r="H25" s="8" t="inlineStr">
+        <is>
+          <t>бронза/латунь</t>
+        </is>
+      </c>
       <c r="I25" s="8" t="n">
         <v>3</v>
       </c>
@@ -20913,7 +21899,7 @@
         </is>
       </c>
       <c r="D20" s="12" t="n">
-        <v>2095</v>
+        <v>2172</v>
       </c>
     </row>
     <row r="21">
@@ -20933,7 +21919,7 @@
         </is>
       </c>
       <c r="D21" s="12" t="n">
-        <v>9893</v>
+        <v>9848</v>
       </c>
     </row>
     <row r="22">
@@ -20953,7 +21939,7 @@
         </is>
       </c>
       <c r="D22" s="12" t="n">
-        <v>1652</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="23" ht="28" customHeight="1">
@@ -20966,7 +21952,7 @@
     <row r="24" ht="28" customHeight="1">
       <c r="A24" s="19" t="inlineStr">
         <is>
-          <t>Фильтры (1652 кг) стоят на ящиках, значит ящики должны быть каркасные: брус по углам и по верху. Фильтр Ду200 весит 120 кг, Ду300 — 230 кг, тонкая обрешетка под ним сложится. Крупные фильтры ставим над углами ящиков, а не над серединой крышки.</t>
+          <t>Фильтры (1620 кг) стоят на ящиках, значит ящики должны быть каркасные: брус по углам и по верху. Фильтр Ду200 весит 120 кг, Ду300 — 230 кг, тонкая обрешетка под ним сложится. Крупные фильтры ставим над углами ящиков, а не над серединой крышки.</t>
         </is>
       </c>
     </row>
@@ -21045,13 +22031,13 @@
         </is>
       </c>
       <c r="B32" s="8" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C32" s="8" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="D32" s="12" t="n">
-        <v>3955</v>
+        <v>3987</v>
       </c>
     </row>
     <row r="33">
@@ -21061,13 +22047,13 @@
         </is>
       </c>
       <c r="B33" s="8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C33" s="8" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D33" s="12" t="n">
-        <v>1542</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="34">

--- a/outputs/marine_equipment/Отгрузка_Питер.xlsx
+++ b/outputs/marine_equipment/Отгрузка_Питер.xlsx
@@ -15,8 +15,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Едет'!$A$3:$R$148</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Не влезло'!$A$3:$R$102</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Не грузим сейчас'!$A$3:$R$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Не влезло'!$A$3:$R$101</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Не грузим сейчас'!$A$3:$R$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -644,12 +644,12 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>99 позиций</t>
+          <t>98 позиций</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>4.0 т, 14.1 млн руб</t>
+          <t>3.5 т, 14.1 млн руб</t>
         </is>
       </c>
     </row>
@@ -661,12 +661,12 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>26 позиций</t>
+          <t>27 позиций</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3.6 т, 1.9 млн руб</t>
+          <t>4.1 т, 1.9 млн руб</t>
         </is>
       </c>
     </row>
@@ -11689,7 +11689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R103"/>
+  <dimension ref="A1:R102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -11827,18 +11827,22 @@
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>Ярус 3, ящики</t>
+          <t>Ярус 2, рядом на полу</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>клинкет (задвижка)</t>
-        </is>
-      </c>
-      <c r="F4" s="8" t="inlineStr"/>
+          <t>блины к клинкету</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>Ду100</t>
+        </is>
+      </c>
       <c r="G4" s="10" t="inlineStr">
         <is>
-          <t>Задвижки (желтая) ок. крышек</t>
+          <t>Блины к клинкету Ду100</t>
         </is>
       </c>
       <c r="H4" s="8" t="inlineStr">
@@ -11847,24 +11851,24 @@
         </is>
       </c>
       <c r="I4" s="8" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J4" s="12" t="n">
-        <v>520</v>
+        <v>495</v>
       </c>
       <c r="K4" s="13" t="n">
-        <v>0.13</v>
+        <v>0.495</v>
       </c>
       <c r="L4" s="12" t="n"/>
       <c r="M4" s="12" t="n"/>
       <c r="N4" s="10" t="inlineStr">
         <is>
-          <t>Ящик сплошной, с перегородками</t>
+          <t>Поддон, прокладки между рядами</t>
         </is>
       </c>
       <c r="O4" s="8" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад электрики</t>
         </is>
       </c>
       <c r="P4" s="8" t="inlineStr">
@@ -11878,7 +11882,7 @@
         </is>
       </c>
       <c r="R4" s="12" t="n">
-        <v>42325</v>
+        <v>40290</v>
       </c>
     </row>
     <row r="5">
@@ -11892,27 +11896,27 @@
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>4. Прочее, по цене за килограмм</t>
+          <t>5. Мелочь — ей добиваем контейнер до 25 тонн</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>Ярус 2, рядом на полу</t>
+          <t>Ярус 3, ящики</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>блины к клинкету</t>
+          <t>клапан штуцерный</t>
         </is>
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>Ду100</t>
+          <t>Ду10</t>
         </is>
       </c>
       <c r="G5" s="10" t="inlineStr">
         <is>
-          <t>Блины к клинкету Ду100</t>
+          <t>Клапан штуцерный проходной Ду 10 Ру40 (СУНДУК)</t>
         </is>
       </c>
       <c r="H5" s="8" t="inlineStr">
@@ -11921,24 +11925,28 @@
         </is>
       </c>
       <c r="I5" s="8" t="n">
-        <v>11</v>
+        <v>798</v>
       </c>
       <c r="J5" s="12" t="n">
-        <v>495</v>
+        <v>479</v>
       </c>
       <c r="K5" s="13" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="L5" s="12" t="n"/>
-      <c r="M5" s="12" t="n"/>
+        <v>0.798</v>
+      </c>
+      <c r="L5" s="12" t="n">
+        <v>7182000</v>
+      </c>
+      <c r="M5" s="12" t="n">
+        <v>15000</v>
+      </c>
       <c r="N5" s="10" t="inlineStr">
         <is>
-          <t>Поддон, прокладки между рядами</t>
+          <t>Ящик сплошной, с перегородками</t>
         </is>
       </c>
       <c r="O5" s="8" t="inlineStr">
         <is>
-          <t>Склад электрики</t>
+          <t>Менеджерская</t>
         </is>
       </c>
       <c r="P5" s="8" t="inlineStr">
@@ -11948,11 +11956,11 @@
       </c>
       <c r="Q5" s="8" t="inlineStr">
         <is>
-          <t>ждет контейнера, цены нет</t>
+          <t>транспортной компанией</t>
         </is>
       </c>
       <c r="R5" s="12" t="n">
-        <v>40290</v>
+        <v>38972</v>
       </c>
     </row>
     <row r="6">
@@ -11986,7 +11994,7 @@
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 10 Ру40 (СУНДУК)</t>
+          <t>Клапан штуцерный проходной Ду 10</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
@@ -11995,19 +12003,19 @@
         </is>
       </c>
       <c r="I6" s="8" t="n">
-        <v>798</v>
+        <v>83</v>
       </c>
       <c r="J6" s="12" t="n">
-        <v>479</v>
+        <v>50</v>
       </c>
       <c r="K6" s="13" t="n">
-        <v>0.798</v>
+        <v>0.083</v>
       </c>
       <c r="L6" s="12" t="n">
-        <v>7182000</v>
+        <v>290500</v>
       </c>
       <c r="M6" s="12" t="n">
-        <v>15000</v>
+        <v>5833</v>
       </c>
       <c r="N6" s="10" t="inlineStr">
         <is>
@@ -12016,7 +12024,7 @@
       </c>
       <c r="O6" s="8" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>Склад 3</t>
         </is>
       </c>
       <c r="P6" s="8" t="inlineStr">
@@ -12030,7 +12038,7 @@
         </is>
       </c>
       <c r="R6" s="12" t="n">
-        <v>38972</v>
+        <v>4053</v>
       </c>
     </row>
     <row r="7">
@@ -12054,17 +12062,17 @@
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
+          <t>клапан педальный</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>Ду10</t>
+          <t>Ду25</t>
         </is>
       </c>
       <c r="G7" s="10" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 10</t>
+          <t>Клапан педальный Ду25 Китай</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
@@ -12073,19 +12081,19 @@
         </is>
       </c>
       <c r="I7" s="8" t="n">
-        <v>83</v>
+        <v>62</v>
       </c>
       <c r="J7" s="12" t="n">
-        <v>50</v>
+        <v>155</v>
       </c>
       <c r="K7" s="13" t="n">
-        <v>0.083</v>
+        <v>0.186</v>
       </c>
       <c r="L7" s="12" t="n">
-        <v>290500</v>
+        <v>775000</v>
       </c>
       <c r="M7" s="12" t="n">
-        <v>5833</v>
+        <v>5000</v>
       </c>
       <c r="N7" s="10" t="inlineStr">
         <is>
@@ -12094,7 +12102,7 @@
       </c>
       <c r="O7" s="8" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад 2</t>
         </is>
       </c>
       <c r="P7" s="8" t="inlineStr">
@@ -12108,7 +12116,7 @@
         </is>
       </c>
       <c r="R7" s="12" t="n">
-        <v>4053</v>
+        <v>12616</v>
       </c>
     </row>
     <row r="8">
@@ -12132,17 +12140,17 @@
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>клапан педальный</t>
+          <t>клапан штуцерный</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>Ду25</t>
+          <t>Ду20</t>
         </is>
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
-          <t>Клапан педальный Ду25 Китай</t>
+          <t>Клапан штуцерный проходной Ду 20</t>
         </is>
       </c>
       <c r="H8" s="8" t="inlineStr">
@@ -12151,16 +12159,16 @@
         </is>
       </c>
       <c r="I8" s="8" t="n">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="J8" s="12" t="n">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="K8" s="13" t="n">
-        <v>0.186</v>
+        <v>0.2</v>
       </c>
       <c r="L8" s="12" t="n">
-        <v>775000</v>
+        <v>750000</v>
       </c>
       <c r="M8" s="12" t="n">
         <v>5000</v>
@@ -12172,7 +12180,7 @@
       </c>
       <c r="O8" s="8" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 3</t>
         </is>
       </c>
       <c r="P8" s="8" t="inlineStr">
@@ -12186,7 +12194,7 @@
         </is>
       </c>
       <c r="R8" s="12" t="n">
-        <v>12616</v>
+        <v>12209</v>
       </c>
     </row>
     <row r="9">
@@ -12215,12 +12223,12 @@
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>Ду20</t>
+          <t>Ду25</t>
         </is>
       </c>
       <c r="G9" s="10" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 20</t>
+          <t>Клапан штуцерный проходной Ду 25 (Китай)</t>
         </is>
       </c>
       <c r="H9" s="8" t="inlineStr">
@@ -12229,19 +12237,19 @@
         </is>
       </c>
       <c r="I9" s="8" t="n">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="J9" s="12" t="n">
-        <v>150</v>
+        <v>198</v>
       </c>
       <c r="K9" s="13" t="n">
-        <v>0.2</v>
+        <v>0.237</v>
       </c>
       <c r="L9" s="12" t="n">
-        <v>750000</v>
+        <v>790000</v>
       </c>
       <c r="M9" s="12" t="n">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="N9" s="10" t="inlineStr">
         <is>
@@ -12264,7 +12272,7 @@
         </is>
       </c>
       <c r="R9" s="12" t="n">
-        <v>12209</v>
+        <v>16075</v>
       </c>
     </row>
     <row r="10">
@@ -12293,12 +12301,12 @@
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>Ду25</t>
+          <t>Ду20</t>
         </is>
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 25 (Китай)</t>
+          <t>Клапан штуцерный проходной Ду 20 Ру10</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr">
@@ -12307,16 +12315,16 @@
         </is>
       </c>
       <c r="I10" s="8" t="n">
-        <v>79</v>
+        <v>5</v>
       </c>
       <c r="J10" s="12" t="n">
-        <v>198</v>
+        <v>8</v>
       </c>
       <c r="K10" s="13" t="n">
-        <v>0.237</v>
+        <v>0.01</v>
       </c>
       <c r="L10" s="12" t="n">
-        <v>790000</v>
+        <v>30000</v>
       </c>
       <c r="M10" s="12" t="n">
         <v>4000</v>
@@ -12328,7 +12336,7 @@
       </c>
       <c r="O10" s="8" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Менеджерская</t>
         </is>
       </c>
       <c r="P10" s="8" t="inlineStr">
@@ -12342,7 +12350,7 @@
         </is>
       </c>
       <c r="R10" s="12" t="n">
-        <v>16075</v>
+        <v>610</v>
       </c>
     </row>
     <row r="11">
@@ -12376,7 +12384,7 @@
       </c>
       <c r="G11" s="10" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 20 Ру10</t>
+          <t>Клапан штуцерный проходной Ду 20 Ру 40</t>
         </is>
       </c>
       <c r="H11" s="8" t="inlineStr">
@@ -12385,16 +12393,16 @@
         </is>
       </c>
       <c r="I11" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K11" s="13" t="n">
-        <v>0.01</v>
+        <v>0.008</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>30000</v>
+        <v>24000</v>
       </c>
       <c r="M11" s="12" t="n">
         <v>4000</v>
@@ -12420,7 +12428,7 @@
         </is>
       </c>
       <c r="R11" s="12" t="n">
-        <v>610</v>
+        <v>488</v>
       </c>
     </row>
     <row r="12">
@@ -12463,16 +12471,16 @@
         </is>
       </c>
       <c r="I12" s="8" t="n">
-        <v>4</v>
+        <v>72</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>6</v>
+        <v>108</v>
       </c>
       <c r="K12" s="13" t="n">
-        <v>0.008</v>
+        <v>0.144</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>24000</v>
+        <v>432000</v>
       </c>
       <c r="M12" s="12" t="n">
         <v>4000</v>
@@ -12498,7 +12506,7 @@
         </is>
       </c>
       <c r="R12" s="12" t="n">
-        <v>488</v>
+        <v>8791</v>
       </c>
     </row>
     <row r="13">
@@ -12541,16 +12549,16 @@
         </is>
       </c>
       <c r="I13" s="8" t="n">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>108</v>
+        <v>16</v>
       </c>
       <c r="K13" s="13" t="n">
-        <v>0.144</v>
+        <v>0.022</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>432000</v>
+        <v>66000</v>
       </c>
       <c r="M13" s="12" t="n">
         <v>4000</v>
@@ -12576,7 +12584,7 @@
         </is>
       </c>
       <c r="R13" s="12" t="n">
-        <v>8791</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="14">
@@ -12697,16 +12705,16 @@
         </is>
       </c>
       <c r="I15" s="8" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="K15" s="13" t="n">
-        <v>0.022</v>
+        <v>0.046</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>66000</v>
+        <v>138000</v>
       </c>
       <c r="M15" s="12" t="n">
         <v>4000</v>
@@ -12732,7 +12740,7 @@
         </is>
       </c>
       <c r="R15" s="12" t="n">
-        <v>1343</v>
+        <v>2808</v>
       </c>
     </row>
     <row r="16">
@@ -12775,16 +12783,16 @@
         </is>
       </c>
       <c r="I16" s="8" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="K16" s="13" t="n">
-        <v>0.046</v>
+        <v>0.006</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>138000</v>
+        <v>18000</v>
       </c>
       <c r="M16" s="12" t="n">
         <v>4000</v>
@@ -12810,7 +12818,7 @@
         </is>
       </c>
       <c r="R16" s="12" t="n">
-        <v>2808</v>
+        <v>366</v>
       </c>
     </row>
     <row r="17">
@@ -12844,7 +12852,7 @@
       </c>
       <c r="G17" s="10" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 20 Ру 40</t>
+          <t>Клапан штуцерный проходной Ду 20 Ру 64</t>
         </is>
       </c>
       <c r="H17" s="8" t="inlineStr">
@@ -12853,16 +12861,16 @@
         </is>
       </c>
       <c r="I17" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K17" s="13" t="n">
-        <v>0.006</v>
+        <v>0.002</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>18000</v>
+        <v>6000</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>4000</v>
@@ -12888,7 +12896,7 @@
         </is>
       </c>
       <c r="R17" s="12" t="n">
-        <v>366</v>
+        <v>122</v>
       </c>
     </row>
     <row r="18">
@@ -12922,7 +12930,7 @@
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 20 Ру 64</t>
+          <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
@@ -13009,16 +13017,16 @@
         </is>
       </c>
       <c r="I19" s="8" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="K19" s="13" t="n">
-        <v>0.002</v>
+        <v>0.026</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>6000</v>
+        <v>78000</v>
       </c>
       <c r="M19" s="12" t="n">
         <v>4000</v>
@@ -13044,7 +13052,7 @@
         </is>
       </c>
       <c r="R19" s="12" t="n">
-        <v>122</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="20">
@@ -13087,16 +13095,16 @@
         </is>
       </c>
       <c r="I20" s="8" t="n">
-        <v>13</v>
+        <v>102</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>20</v>
+        <v>153</v>
       </c>
       <c r="K20" s="13" t="n">
-        <v>0.026</v>
+        <v>0.204</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>78000</v>
+        <v>612000</v>
       </c>
       <c r="M20" s="12" t="n">
         <v>4000</v>
@@ -13122,7 +13130,7 @@
         </is>
       </c>
       <c r="R20" s="12" t="n">
-        <v>1587</v>
+        <v>12453</v>
       </c>
     </row>
     <row r="21">
@@ -13165,16 +13173,16 @@
         </is>
       </c>
       <c r="I21" s="8" t="n">
-        <v>102</v>
+        <v>1</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>153</v>
+        <v>2</v>
       </c>
       <c r="K21" s="13" t="n">
-        <v>0.204</v>
+        <v>0.002</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>612000</v>
+        <v>6000</v>
       </c>
       <c r="M21" s="12" t="n">
         <v>4000</v>
@@ -13200,7 +13208,7 @@
         </is>
       </c>
       <c r="R21" s="12" t="n">
-        <v>12453</v>
+        <v>122</v>
       </c>
     </row>
     <row r="22">
@@ -13243,16 +13251,16 @@
         </is>
       </c>
       <c r="I22" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K22" s="13" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>6000</v>
+        <v>12000</v>
       </c>
       <c r="M22" s="12" t="n">
         <v>4000</v>
@@ -13278,7 +13286,7 @@
         </is>
       </c>
       <c r="R22" s="12" t="n">
-        <v>122</v>
+        <v>244</v>
       </c>
     </row>
     <row r="23">
@@ -13399,16 +13407,16 @@
         </is>
       </c>
       <c r="I24" s="8" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="K24" s="13" t="n">
-        <v>0.004</v>
+        <v>0.042</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>12000</v>
+        <v>126000</v>
       </c>
       <c r="M24" s="12" t="n">
         <v>4000</v>
@@ -13434,7 +13442,7 @@
         </is>
       </c>
       <c r="R24" s="12" t="n">
-        <v>244</v>
+        <v>2564</v>
       </c>
     </row>
     <row r="25">
@@ -13477,16 +13485,16 @@
         </is>
       </c>
       <c r="I25" s="8" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="K25" s="13" t="n">
-        <v>0.042</v>
+        <v>0.032</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>126000</v>
+        <v>96000</v>
       </c>
       <c r="M25" s="12" t="n">
         <v>4000</v>
@@ -13512,7 +13520,7 @@
         </is>
       </c>
       <c r="R25" s="12" t="n">
-        <v>2564</v>
+        <v>1953</v>
       </c>
     </row>
     <row r="26">
@@ -13555,16 +13563,16 @@
         </is>
       </c>
       <c r="I26" s="8" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="K26" s="13" t="n">
-        <v>0.032</v>
+        <v>0.004</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>96000</v>
+        <v>12000</v>
       </c>
       <c r="M26" s="12" t="n">
         <v>4000</v>
@@ -13590,7 +13598,7 @@
         </is>
       </c>
       <c r="R26" s="12" t="n">
-        <v>1953</v>
+        <v>244</v>
       </c>
     </row>
     <row r="27">
@@ -13633,16 +13641,16 @@
         </is>
       </c>
       <c r="I27" s="8" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="K27" s="13" t="n">
-        <v>0.004</v>
+        <v>0.014</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>12000</v>
+        <v>42000</v>
       </c>
       <c r="M27" s="12" t="n">
         <v>4000</v>
@@ -13668,7 +13676,7 @@
         </is>
       </c>
       <c r="R27" s="12" t="n">
-        <v>244</v>
+        <v>855</v>
       </c>
     </row>
     <row r="28">
@@ -13711,16 +13719,16 @@
         </is>
       </c>
       <c r="I28" s="8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K28" s="13" t="n">
-        <v>0.014</v>
+        <v>0.018</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>42000</v>
+        <v>54000</v>
       </c>
       <c r="M28" s="12" t="n">
         <v>4000</v>
@@ -13746,7 +13754,7 @@
         </is>
       </c>
       <c r="R28" s="12" t="n">
-        <v>855</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="29">
@@ -13789,16 +13797,16 @@
         </is>
       </c>
       <c r="I29" s="8" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="K29" s="13" t="n">
-        <v>0.018</v>
+        <v>0.002</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>54000</v>
+        <v>6000</v>
       </c>
       <c r="M29" s="12" t="n">
         <v>4000</v>
@@ -13824,7 +13832,7 @@
         </is>
       </c>
       <c r="R29" s="12" t="n">
-        <v>1099</v>
+        <v>122</v>
       </c>
     </row>
     <row r="30">
@@ -13945,16 +13953,16 @@
         </is>
       </c>
       <c r="I31" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K31" s="13" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>6000</v>
+        <v>18000</v>
       </c>
       <c r="M31" s="12" t="n">
         <v>4000</v>
@@ -13980,7 +13988,7 @@
         </is>
       </c>
       <c r="R31" s="12" t="n">
-        <v>122</v>
+        <v>366</v>
       </c>
     </row>
     <row r="32">
@@ -14009,12 +14017,12 @@
       </c>
       <c r="F32" s="8" t="inlineStr">
         <is>
-          <t>Ду20</t>
+          <t>Ду32</t>
         </is>
       </c>
       <c r="G32" s="10" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
+          <t>Клапан штуцерный проходной Ду 32 Ру 40</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr">
@@ -14026,16 +14034,16 @@
         <v>3</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="K32" s="13" t="n">
-        <v>0.006</v>
+        <v>0.015</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>18000</v>
+        <v>37500</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>4000</v>
+        <v>3571</v>
       </c>
       <c r="N32" s="10" t="inlineStr">
         <is>
@@ -14058,7 +14066,7 @@
         </is>
       </c>
       <c r="R32" s="12" t="n">
-        <v>366</v>
+        <v>855</v>
       </c>
     </row>
     <row r="33">
@@ -14087,12 +14095,12 @@
       </c>
       <c r="F33" s="8" t="inlineStr">
         <is>
-          <t>Ду32</t>
+          <t>Ду10</t>
         </is>
       </c>
       <c r="G33" s="10" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 32 Ру 40</t>
+          <t>Клапан штуцерный угловой Ду10 Ру100</t>
         </is>
       </c>
       <c r="H33" s="8" t="inlineStr">
@@ -14101,19 +14109,19 @@
         </is>
       </c>
       <c r="I33" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="K33" s="13" t="n">
-        <v>0.015</v>
+        <v>0.001</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>37500</v>
+        <v>2000</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>3571</v>
+        <v>3333</v>
       </c>
       <c r="N33" s="10" t="inlineStr">
         <is>
@@ -14122,7 +14130,7 @@
       </c>
       <c r="O33" s="8" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>Склад 2</t>
         </is>
       </c>
       <c r="P33" s="8" t="inlineStr">
@@ -14136,7 +14144,7 @@
         </is>
       </c>
       <c r="R33" s="12" t="n">
-        <v>855</v>
+        <v>49</v>
       </c>
     </row>
     <row r="34">
@@ -14248,7 +14256,7 @@
       </c>
       <c r="G35" s="10" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду10 Ру100</t>
+          <t>Клапан штуцерный проходной Ду 10 Ру 40</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">
@@ -14257,16 +14265,16 @@
         </is>
       </c>
       <c r="I35" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K35" s="13" t="n">
-        <v>0.001</v>
+        <v>0.004</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>2000</v>
+        <v>8000</v>
       </c>
       <c r="M35" s="12" t="n">
         <v>3333</v>
@@ -14278,7 +14286,7 @@
       </c>
       <c r="O35" s="8" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Менеджерская</t>
         </is>
       </c>
       <c r="P35" s="8" t="inlineStr">
@@ -14292,7 +14300,7 @@
         </is>
       </c>
       <c r="R35" s="12" t="n">
-        <v>49</v>
+        <v>195</v>
       </c>
     </row>
     <row r="36">
@@ -14335,16 +14343,16 @@
         </is>
       </c>
       <c r="I36" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K36" s="13" t="n">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>8000</v>
+        <v>2000</v>
       </c>
       <c r="M36" s="12" t="n">
         <v>3333</v>
@@ -14370,7 +14378,7 @@
         </is>
       </c>
       <c r="R36" s="12" t="n">
-        <v>195</v>
+        <v>49</v>
       </c>
     </row>
     <row r="37">
@@ -14404,7 +14412,7 @@
       </c>
       <c r="G37" s="10" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 10 Ру 40</t>
+          <t>Клапан штуцерный проходной Ду 10 Ру100</t>
         </is>
       </c>
       <c r="H37" s="8" t="inlineStr">
@@ -14413,16 +14421,16 @@
         </is>
       </c>
       <c r="I37" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K37" s="13" t="n">
-        <v>0.001</v>
+        <v>0.005</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>2000</v>
+        <v>10000</v>
       </c>
       <c r="M37" s="12" t="n">
         <v>3333</v>
@@ -14448,7 +14456,7 @@
         </is>
       </c>
       <c r="R37" s="12" t="n">
-        <v>49</v>
+        <v>244</v>
       </c>
     </row>
     <row r="38">
@@ -14491,16 +14499,16 @@
         </is>
       </c>
       <c r="I38" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K38" s="13" t="n">
-        <v>0.005</v>
+        <v>0.003</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="M38" s="12" t="n">
         <v>3333</v>
@@ -14526,7 +14534,7 @@
         </is>
       </c>
       <c r="R38" s="12" t="n">
-        <v>244</v>
+        <v>147</v>
       </c>
     </row>
     <row r="39">
@@ -14647,16 +14655,16 @@
         </is>
       </c>
       <c r="I40" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K40" s="13" t="n">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>6000</v>
+        <v>2000</v>
       </c>
       <c r="M40" s="12" t="n">
         <v>3333</v>
@@ -14682,7 +14690,7 @@
         </is>
       </c>
       <c r="R40" s="12" t="n">
-        <v>147</v>
+        <v>49</v>
       </c>
     </row>
     <row r="41">
@@ -14725,16 +14733,16 @@
         </is>
       </c>
       <c r="I41" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J41" s="12" t="n">
         <v>1</v>
       </c>
       <c r="K41" s="13" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="M41" s="12" t="n">
         <v>3333</v>
@@ -14760,7 +14768,7 @@
         </is>
       </c>
       <c r="R41" s="12" t="n">
-        <v>49</v>
+        <v>98</v>
       </c>
     </row>
     <row r="42">
@@ -14803,16 +14811,16 @@
         </is>
       </c>
       <c r="I42" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J42" s="12" t="n">
         <v>1</v>
       </c>
       <c r="K42" s="13" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>4000</v>
+        <v>2000</v>
       </c>
       <c r="M42" s="12" t="n">
         <v>3333</v>
@@ -14838,7 +14846,7 @@
         </is>
       </c>
       <c r="R42" s="12" t="n">
-        <v>98</v>
+        <v>49</v>
       </c>
     </row>
     <row r="43">
@@ -14872,7 +14880,7 @@
       </c>
       <c r="G43" s="10" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 10 Ру100</t>
+          <t>Клапан штуцерный проходной Ду 10</t>
         </is>
       </c>
       <c r="H43" s="8" t="inlineStr">
@@ -14881,16 +14889,16 @@
         </is>
       </c>
       <c r="I43" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K43" s="13" t="n">
-        <v>0.001</v>
+        <v>0.004</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>2000</v>
+        <v>8000</v>
       </c>
       <c r="M43" s="12" t="n">
         <v>3333</v>
@@ -14916,7 +14924,7 @@
         </is>
       </c>
       <c r="R43" s="12" t="n">
-        <v>49</v>
+        <v>195</v>
       </c>
     </row>
     <row r="44">
@@ -14945,12 +14953,12 @@
       </c>
       <c r="F44" s="8" t="inlineStr">
         <is>
-          <t>Ду10</t>
+          <t>Ду20</t>
         </is>
       </c>
       <c r="G44" s="10" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 10</t>
+          <t>Клапан невозв-запор.цапковый угловой под дюрит Ду20Ру6</t>
         </is>
       </c>
       <c r="H44" s="8" t="inlineStr">
@@ -14959,19 +14967,19 @@
         </is>
       </c>
       <c r="I44" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K44" s="13" t="n">
         <v>0.004</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>8000</v>
+        <v>9600</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>3333</v>
+        <v>3200</v>
       </c>
       <c r="N44" s="10" t="inlineStr">
         <is>
@@ -14980,7 +14988,7 @@
       </c>
       <c r="O44" s="8" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>Склад 2</t>
         </is>
       </c>
       <c r="P44" s="8" t="inlineStr">
@@ -14994,7 +15002,7 @@
         </is>
       </c>
       <c r="R44" s="12" t="n">
-        <v>195</v>
+        <v>244</v>
       </c>
     </row>
     <row r="45">
@@ -15023,12 +15031,12 @@
       </c>
       <c r="F45" s="8" t="inlineStr">
         <is>
-          <t>Ду20</t>
+          <t>Ду25</t>
         </is>
       </c>
       <c r="G45" s="10" t="inlineStr">
         <is>
-          <t>Клапан невозв-запор.цапковый угловой под дюрит Ду20Ру6</t>
+          <t>Клапан штуцерный угловой Ду25</t>
         </is>
       </c>
       <c r="H45" s="8" t="inlineStr">
@@ -15037,19 +15045,19 @@
         </is>
       </c>
       <c r="I45" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J45" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="J45" s="12" t="n">
-        <v>3</v>
-      </c>
       <c r="K45" s="13" t="n">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>9600</v>
+        <v>7500</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>3200</v>
+        <v>3000</v>
       </c>
       <c r="N45" s="10" t="inlineStr">
         <is>
@@ -15072,7 +15080,7 @@
         </is>
       </c>
       <c r="R45" s="12" t="n">
-        <v>244</v>
+        <v>203</v>
       </c>
     </row>
     <row r="46">
@@ -15193,16 +15201,16 @@
         </is>
       </c>
       <c r="I47" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="K47" s="13" t="n">
-        <v>0.003</v>
+        <v>0.018</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>7500</v>
+        <v>45000</v>
       </c>
       <c r="M47" s="12" t="n">
         <v>3000</v>
@@ -15214,7 +15222,7 @@
       </c>
       <c r="O47" s="8" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 3</t>
         </is>
       </c>
       <c r="P47" s="8" t="inlineStr">
@@ -15228,7 +15236,7 @@
         </is>
       </c>
       <c r="R47" s="12" t="n">
-        <v>203</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="48">
@@ -15255,14 +15263,10 @@
           <t>клапан штуцерный</t>
         </is>
       </c>
-      <c r="F48" s="8" t="inlineStr">
-        <is>
-          <t>Ду25</t>
-        </is>
-      </c>
+      <c r="F48" s="8" t="inlineStr"/>
       <c r="G48" s="10" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду25</t>
+          <t>Клапан для манометра штуцерный сальниковый</t>
         </is>
       </c>
       <c r="H48" s="8" t="inlineStr">
@@ -15271,16 +15275,16 @@
         </is>
       </c>
       <c r="I48" s="8" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="J48" s="12" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="K48" s="13" t="n">
-        <v>0.018</v>
+        <v>0.18</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>45000</v>
+        <v>108000</v>
       </c>
       <c r="M48" s="12" t="n">
         <v>3000</v>
@@ -15292,7 +15296,7 @@
       </c>
       <c r="O48" s="8" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Менеджерская</t>
         </is>
       </c>
       <c r="P48" s="8" t="inlineStr">
@@ -15306,7 +15310,7 @@
         </is>
       </c>
       <c r="R48" s="12" t="n">
-        <v>1221</v>
+        <v>2930</v>
       </c>
     </row>
     <row r="49">
@@ -15333,10 +15337,14 @@
           <t>клапан штуцерный</t>
         </is>
       </c>
-      <c r="F49" s="8" t="inlineStr"/>
+      <c r="F49" s="8" t="inlineStr">
+        <is>
+          <t>Ду20</t>
+        </is>
+      </c>
       <c r="G49" s="10" t="inlineStr">
         <is>
-          <t>Клапан для манометра штуцерный сальниковый</t>
+          <t>Клапан штуцерный угловой Ду20 ру 40</t>
         </is>
       </c>
       <c r="H49" s="8" t="inlineStr">
@@ -15345,16 +15353,16 @@
         </is>
       </c>
       <c r="I49" s="8" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="J49" s="12" t="n">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="K49" s="13" t="n">
-        <v>0.18</v>
+        <v>0.002</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>108000</v>
+        <v>4500</v>
       </c>
       <c r="M49" s="12" t="n">
         <v>3000</v>
@@ -15380,7 +15388,7 @@
         </is>
       </c>
       <c r="R49" s="12" t="n">
-        <v>2930</v>
+        <v>122</v>
       </c>
     </row>
     <row r="50">
@@ -15423,16 +15431,16 @@
         </is>
       </c>
       <c r="I50" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J50" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K50" s="13" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>4500</v>
+        <v>9000</v>
       </c>
       <c r="M50" s="12" t="n">
         <v>3000</v>
@@ -15458,7 +15466,7 @@
         </is>
       </c>
       <c r="R50" s="12" t="n">
-        <v>122</v>
+        <v>244</v>
       </c>
     </row>
     <row r="51">
@@ -15501,16 +15509,16 @@
         </is>
       </c>
       <c r="I51" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J51" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="J51" s="12" t="n">
-        <v>3</v>
-      </c>
       <c r="K51" s="13" t="n">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>9000</v>
+        <v>4500</v>
       </c>
       <c r="M51" s="12" t="n">
         <v>3000</v>
@@ -15536,7 +15544,7 @@
         </is>
       </c>
       <c r="R51" s="12" t="n">
-        <v>244</v>
+        <v>122</v>
       </c>
     </row>
     <row r="52">
@@ -15570,7 +15578,7 @@
       </c>
       <c r="G52" s="10" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду20 ру 40</t>
+          <t>Клапан штуцерный угловой Ду20 Ру160</t>
         </is>
       </c>
       <c r="H52" s="8" t="inlineStr">
@@ -15579,16 +15587,16 @@
         </is>
       </c>
       <c r="I52" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J52" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K52" s="13" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>4500</v>
+        <v>13500</v>
       </c>
       <c r="M52" s="12" t="n">
         <v>3000</v>
@@ -15614,7 +15622,7 @@
         </is>
       </c>
       <c r="R52" s="12" t="n">
-        <v>122</v>
+        <v>366</v>
       </c>
     </row>
     <row r="53">
@@ -15643,12 +15651,12 @@
       </c>
       <c r="F53" s="8" t="inlineStr">
         <is>
-          <t>Ду20</t>
+          <t>Ду25</t>
         </is>
       </c>
       <c r="G53" s="10" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду20 Ру160</t>
+          <t>Клапан штуцерный угловой Ду25 Ру100</t>
         </is>
       </c>
       <c r="H53" s="8" t="inlineStr">
@@ -15657,16 +15665,16 @@
         </is>
       </c>
       <c r="I53" s="8" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J53" s="12" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="K53" s="13" t="n">
-        <v>0.006</v>
+        <v>0.024</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>13500</v>
+        <v>60000</v>
       </c>
       <c r="M53" s="12" t="n">
         <v>3000</v>
@@ -15692,7 +15700,7 @@
         </is>
       </c>
       <c r="R53" s="12" t="n">
-        <v>366</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="54">
@@ -15735,16 +15743,16 @@
         </is>
       </c>
       <c r="I54" s="8" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J54" s="12" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="K54" s="13" t="n">
-        <v>0.024</v>
+        <v>0.003</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>60000</v>
+        <v>7500</v>
       </c>
       <c r="M54" s="12" t="n">
         <v>3000</v>
@@ -15770,7 +15778,7 @@
         </is>
       </c>
       <c r="R54" s="12" t="n">
-        <v>1628</v>
+        <v>203</v>
       </c>
     </row>
     <row r="55">
@@ -15813,16 +15821,16 @@
         </is>
       </c>
       <c r="I55" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J55" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K55" s="13" t="n">
-        <v>0.003</v>
+        <v>0.006</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>7500</v>
+        <v>15000</v>
       </c>
       <c r="M55" s="12" t="n">
         <v>3000</v>
@@ -15848,7 +15856,7 @@
         </is>
       </c>
       <c r="R55" s="12" t="n">
-        <v>203</v>
+        <v>407</v>
       </c>
     </row>
     <row r="56">
@@ -15877,12 +15885,12 @@
       </c>
       <c r="F56" s="8" t="inlineStr">
         <is>
-          <t>Ду25</t>
+          <t>Ду32</t>
         </is>
       </c>
       <c r="G56" s="10" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду25 Ру100</t>
+          <t>Клапан штуцерный угловой Ду32Ру100 (Яшик мет.)</t>
         </is>
       </c>
       <c r="H56" s="8" t="inlineStr">
@@ -15891,19 +15899,19 @@
         </is>
       </c>
       <c r="I56" s="8" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="J56" s="12" t="n">
-        <v>5</v>
+        <v>108</v>
       </c>
       <c r="K56" s="13" t="n">
-        <v>0.006</v>
+        <v>0.155</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>15000</v>
+        <v>297600</v>
       </c>
       <c r="M56" s="12" t="n">
-        <v>3000</v>
+        <v>2743</v>
       </c>
       <c r="N56" s="10" t="inlineStr">
         <is>
@@ -15912,7 +15920,7 @@
       </c>
       <c r="O56" s="8" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>Склад 2</t>
         </is>
       </c>
       <c r="P56" s="8" t="inlineStr">
@@ -15926,7 +15934,7 @@
         </is>
       </c>
       <c r="R56" s="12" t="n">
-        <v>407</v>
+        <v>8831</v>
       </c>
     </row>
     <row r="57">
@@ -15969,16 +15977,16 @@
         </is>
       </c>
       <c r="I57" s="8" t="n">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="J57" s="12" t="n">
-        <v>108</v>
+        <v>49</v>
       </c>
       <c r="K57" s="13" t="n">
-        <v>0.155</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L57" s="12" t="n">
-        <v>297600</v>
+        <v>134400</v>
       </c>
       <c r="M57" s="12" t="n">
         <v>2743</v>
@@ -16004,7 +16012,7 @@
         </is>
       </c>
       <c r="R57" s="12" t="n">
-        <v>8831</v>
+        <v>3988</v>
       </c>
     </row>
     <row r="58">
@@ -16047,16 +16055,16 @@
         </is>
       </c>
       <c r="I58" s="8" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="J58" s="12" t="n">
-        <v>49</v>
+        <v>4</v>
       </c>
       <c r="K58" s="13" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.005</v>
       </c>
       <c r="L58" s="12" t="n">
-        <v>134400</v>
+        <v>9600</v>
       </c>
       <c r="M58" s="12" t="n">
         <v>2743</v>
@@ -16082,7 +16090,7 @@
         </is>
       </c>
       <c r="R58" s="12" t="n">
-        <v>3988</v>
+        <v>285</v>
       </c>
     </row>
     <row r="59">
@@ -16194,7 +16202,7 @@
       </c>
       <c r="G60" s="10" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду32Ру100 (Яшик мет.)</t>
+          <t>Клапан штуцерный угловой Ду32</t>
         </is>
       </c>
       <c r="H60" s="8" t="inlineStr">
@@ -16203,16 +16211,16 @@
         </is>
       </c>
       <c r="I60" s="8" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J60" s="12" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="K60" s="13" t="n">
-        <v>0.005</v>
+        <v>0.04</v>
       </c>
       <c r="L60" s="12" t="n">
-        <v>9600</v>
+        <v>76800</v>
       </c>
       <c r="M60" s="12" t="n">
         <v>2743</v>
@@ -16224,7 +16232,7 @@
       </c>
       <c r="O60" s="8" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 3</t>
         </is>
       </c>
       <c r="P60" s="8" t="inlineStr">
@@ -16238,7 +16246,7 @@
         </is>
       </c>
       <c r="R60" s="12" t="n">
-        <v>285</v>
+        <v>2279</v>
       </c>
     </row>
     <row r="61">
@@ -16272,7 +16280,7 @@
       </c>
       <c r="G61" s="10" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду32</t>
+          <t>Клапан штуцерный угловой Ду32 Ру100</t>
         </is>
       </c>
       <c r="H61" s="8" t="inlineStr">
@@ -16281,16 +16289,16 @@
         </is>
       </c>
       <c r="I61" s="8" t="n">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="J61" s="12" t="n">
-        <v>28</v>
+        <v>136</v>
       </c>
       <c r="K61" s="13" t="n">
-        <v>0.04</v>
+        <v>0.195</v>
       </c>
       <c r="L61" s="12" t="n">
-        <v>76800</v>
+        <v>374400</v>
       </c>
       <c r="M61" s="12" t="n">
         <v>2743</v>
@@ -16302,7 +16310,7 @@
       </c>
       <c r="O61" s="8" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Менеджерская</t>
         </is>
       </c>
       <c r="P61" s="8" t="inlineStr">
@@ -16316,7 +16324,7 @@
         </is>
       </c>
       <c r="R61" s="12" t="n">
-        <v>2279</v>
+        <v>11110</v>
       </c>
     </row>
     <row r="62">
@@ -16359,16 +16367,16 @@
         </is>
       </c>
       <c r="I62" s="8" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="J62" s="12" t="n">
-        <v>136</v>
+        <v>7</v>
       </c>
       <c r="K62" s="13" t="n">
-        <v>0.195</v>
+        <v>0.01</v>
       </c>
       <c r="L62" s="12" t="n">
-        <v>374400</v>
+        <v>19200</v>
       </c>
       <c r="M62" s="12" t="n">
         <v>2743</v>
@@ -16394,7 +16402,7 @@
         </is>
       </c>
       <c r="R62" s="12" t="n">
-        <v>11110</v>
+        <v>570</v>
       </c>
     </row>
     <row r="63">
@@ -16437,16 +16445,16 @@
         </is>
       </c>
       <c r="I63" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J63" s="12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K63" s="13" t="n">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="L63" s="12" t="n">
-        <v>19200</v>
+        <v>9600</v>
       </c>
       <c r="M63" s="12" t="n">
         <v>2743</v>
@@ -16472,7 +16480,7 @@
         </is>
       </c>
       <c r="R63" s="12" t="n">
-        <v>570</v>
+        <v>285</v>
       </c>
     </row>
     <row r="64">
@@ -16506,7 +16514,7 @@
       </c>
       <c r="G64" s="10" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду32 Ру100</t>
+          <t>Клапан штуцерный угловой Ду32 Ру160</t>
         </is>
       </c>
       <c r="H64" s="8" t="inlineStr">
@@ -16515,16 +16523,16 @@
         </is>
       </c>
       <c r="I64" s="8" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J64" s="12" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="K64" s="13" t="n">
-        <v>0.005</v>
+        <v>0.04</v>
       </c>
       <c r="L64" s="12" t="n">
-        <v>9600</v>
+        <v>76800</v>
       </c>
       <c r="M64" s="12" t="n">
         <v>2743</v>
@@ -16550,7 +16558,7 @@
         </is>
       </c>
       <c r="R64" s="12" t="n">
-        <v>285</v>
+        <v>2279</v>
       </c>
     </row>
     <row r="65">
@@ -16593,16 +16601,16 @@
         </is>
       </c>
       <c r="I65" s="8" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="J65" s="12" t="n">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="K65" s="13" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="L65" s="12" t="n">
-        <v>76800</v>
+        <v>153600</v>
       </c>
       <c r="M65" s="12" t="n">
         <v>2743</v>
@@ -16628,7 +16636,7 @@
         </is>
       </c>
       <c r="R65" s="12" t="n">
-        <v>2279</v>
+        <v>4558</v>
       </c>
     </row>
     <row r="66">
@@ -16657,12 +16665,12 @@
       </c>
       <c r="F66" s="8" t="inlineStr">
         <is>
-          <t>Ду32</t>
+          <t>Ду20</t>
         </is>
       </c>
       <c r="G66" s="10" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду32 Ру160</t>
+          <t>Клапан невозвратный штуцерный проходной Ду20 Ру40</t>
         </is>
       </c>
       <c r="H66" s="8" t="inlineStr">
@@ -16671,19 +16679,19 @@
         </is>
       </c>
       <c r="I66" s="8" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="J66" s="12" t="n">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="K66" s="13" t="n">
-        <v>0.08</v>
+        <v>0.002</v>
       </c>
       <c r="L66" s="12" t="n">
-        <v>153600</v>
+        <v>4000</v>
       </c>
       <c r="M66" s="12" t="n">
-        <v>2743</v>
+        <v>2667</v>
       </c>
       <c r="N66" s="10" t="inlineStr">
         <is>
@@ -16692,7 +16700,7 @@
       </c>
       <c r="O66" s="8" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>Склад 2</t>
         </is>
       </c>
       <c r="P66" s="8" t="inlineStr">
@@ -16706,7 +16714,7 @@
         </is>
       </c>
       <c r="R66" s="12" t="n">
-        <v>4558</v>
+        <v>122</v>
       </c>
     </row>
     <row r="67">
@@ -16730,7 +16738,7 @@
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
+          <t>кран</t>
         </is>
       </c>
       <c r="F67" s="8" t="inlineStr">
@@ -16740,7 +16748,7 @@
       </c>
       <c r="G67" s="10" t="inlineStr">
         <is>
-          <t>Клапан невозвратный штуцерный проходной Ду20 Ру40</t>
+          <t>Кран двухходовой штуцерный Ду20 Ру16</t>
         </is>
       </c>
       <c r="H67" s="8" t="inlineStr">
@@ -16749,16 +16757,16 @@
         </is>
       </c>
       <c r="I67" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J67" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K67" s="13" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="L67" s="12" t="n">
-        <v>4000</v>
+        <v>12000</v>
       </c>
       <c r="M67" s="12" t="n">
         <v>2667</v>
@@ -16784,7 +16792,7 @@
         </is>
       </c>
       <c r="R67" s="12" t="n">
-        <v>122</v>
+        <v>366</v>
       </c>
     </row>
     <row r="68">
@@ -16808,17 +16816,17 @@
       </c>
       <c r="E68" s="8" t="inlineStr">
         <is>
-          <t>кран</t>
+          <t>клапан быстрозапорный</t>
         </is>
       </c>
       <c r="F68" s="8" t="inlineStr">
         <is>
-          <t>Ду20</t>
+          <t>Ду40</t>
         </is>
       </c>
       <c r="G68" s="10" t="inlineStr">
         <is>
-          <t>Кран двухходовой штуцерный Ду20 Ру16</t>
+          <t>Клапан быстрозапор. фланц. проход. с тросиков. приводом Ду40Ру6,3</t>
         </is>
       </c>
       <c r="H68" s="8" t="inlineStr">
@@ -16827,19 +16835,19 @@
         </is>
       </c>
       <c r="I68" s="8" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J68" s="12" t="n">
-        <v>4</v>
+        <v>70</v>
       </c>
       <c r="K68" s="13" t="n">
-        <v>0.006</v>
+        <v>0.056</v>
       </c>
       <c r="L68" s="12" t="n">
-        <v>12000</v>
+        <v>182000</v>
       </c>
       <c r="M68" s="12" t="n">
-        <v>2667</v>
+        <v>2600</v>
       </c>
       <c r="N68" s="10" t="inlineStr">
         <is>
@@ -16848,7 +16856,7 @@
       </c>
       <c r="O68" s="8" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 3</t>
         </is>
       </c>
       <c r="P68" s="8" t="inlineStr">
@@ -16862,7 +16870,7 @@
         </is>
       </c>
       <c r="R68" s="12" t="n">
-        <v>366</v>
+        <v>5698</v>
       </c>
     </row>
     <row r="69">
@@ -16886,17 +16894,17 @@
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>клапан быстрозапорный</t>
+          <t>клапан фланцевый</t>
         </is>
       </c>
       <c r="F69" s="8" t="inlineStr">
         <is>
-          <t>Ду40</t>
+          <t>Ду20</t>
         </is>
       </c>
       <c r="G69" s="10" t="inlineStr">
         <is>
-          <t>Клапан быстрозапор. фланц. проход. с тросиков. приводом Ду40Ру6,3</t>
+          <t>Клапан фланцевый проходной ДУ20 Ру25</t>
         </is>
       </c>
       <c r="H69" s="8" t="inlineStr">
@@ -16905,19 +16913,19 @@
         </is>
       </c>
       <c r="I69" s="8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J69" s="12" t="n">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="K69" s="13" t="n">
-        <v>0.056</v>
+        <v>0.016</v>
       </c>
       <c r="L69" s="12" t="n">
-        <v>182000</v>
+        <v>80000</v>
       </c>
       <c r="M69" s="12" t="n">
-        <v>2600</v>
+        <v>2500</v>
       </c>
       <c r="N69" s="10" t="inlineStr">
         <is>
@@ -16940,7 +16948,7 @@
         </is>
       </c>
       <c r="R69" s="12" t="n">
-        <v>5698</v>
+        <v>2605</v>
       </c>
     </row>
     <row r="70">
@@ -16964,17 +16972,17 @@
       </c>
       <c r="E70" s="8" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>кран</t>
         </is>
       </c>
       <c r="F70" s="8" t="inlineStr">
         <is>
-          <t>Ду20</t>
+          <t>Ду32</t>
         </is>
       </c>
       <c r="G70" s="10" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной ДУ20 Ру25</t>
+          <t>Кран двухходовой фланцевый Ду32 Ру6</t>
         </is>
       </c>
       <c r="H70" s="8" t="inlineStr">
@@ -16983,19 +16991,19 @@
         </is>
       </c>
       <c r="I70" s="8" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J70" s="12" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="K70" s="13" t="n">
-        <v>0.016</v>
+        <v>0.005</v>
       </c>
       <c r="L70" s="12" t="n">
-        <v>80000</v>
+        <v>9600</v>
       </c>
       <c r="M70" s="12" t="n">
-        <v>2500</v>
+        <v>2400</v>
       </c>
       <c r="N70" s="10" t="inlineStr">
         <is>
@@ -17004,7 +17012,7 @@
       </c>
       <c r="O70" s="8" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад 2</t>
         </is>
       </c>
       <c r="P70" s="8" t="inlineStr">
@@ -17018,7 +17026,7 @@
         </is>
       </c>
       <c r="R70" s="12" t="n">
-        <v>2605</v>
+        <v>326</v>
       </c>
     </row>
     <row r="71">
@@ -17042,17 +17050,17 @@
       </c>
       <c r="E71" s="8" t="inlineStr">
         <is>
-          <t>кран</t>
+          <t>клапан фланцевый</t>
         </is>
       </c>
       <c r="F71" s="8" t="inlineStr">
         <is>
-          <t>Ду32</t>
+          <t>Ду25</t>
         </is>
       </c>
       <c r="G71" s="10" t="inlineStr">
         <is>
-          <t>Кран двухходовой фланцевый Ду32 Ру6</t>
+          <t>Клапан фланцевый проходной ДУ25 ???</t>
         </is>
       </c>
       <c r="H71" s="8" t="inlineStr">
@@ -17064,13 +17072,13 @@
         <v>1</v>
       </c>
       <c r="J71" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K71" s="13" t="n">
-        <v>0.005</v>
+        <v>0.003</v>
       </c>
       <c r="L71" s="12" t="n">
-        <v>9600</v>
+        <v>12000</v>
       </c>
       <c r="M71" s="12" t="n">
         <v>2400</v>
@@ -17082,7 +17090,7 @@
       </c>
       <c r="O71" s="8" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 3</t>
         </is>
       </c>
       <c r="P71" s="8" t="inlineStr">
@@ -17096,7 +17104,7 @@
         </is>
       </c>
       <c r="R71" s="12" t="n">
-        <v>326</v>
+        <v>407</v>
       </c>
     </row>
     <row r="72">
@@ -17120,17 +17128,17 @@
       </c>
       <c r="E72" s="8" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>клапан штуцерный</t>
         </is>
       </c>
       <c r="F72" s="8" t="inlineStr">
         <is>
-          <t>Ду25</t>
+          <t>Ду20</t>
         </is>
       </c>
       <c r="G72" s="10" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной ДУ25 ???</t>
+          <t>Клапан штуцерный угловой Ду20 Ру100</t>
         </is>
       </c>
       <c r="H72" s="8" t="inlineStr">
@@ -17139,19 +17147,19 @@
         </is>
       </c>
       <c r="I72" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J72" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K72" s="13" t="n">
-        <v>0.003</v>
+        <v>0.01</v>
       </c>
       <c r="L72" s="12" t="n">
-        <v>12000</v>
+        <v>15000</v>
       </c>
       <c r="M72" s="12" t="n">
-        <v>2400</v>
+        <v>2000</v>
       </c>
       <c r="N72" s="10" t="inlineStr">
         <is>
@@ -17160,7 +17168,7 @@
       </c>
       <c r="O72" s="8" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад 2</t>
         </is>
       </c>
       <c r="P72" s="8" t="inlineStr">
@@ -17174,7 +17182,7 @@
         </is>
       </c>
       <c r="R72" s="12" t="n">
-        <v>407</v>
+        <v>610</v>
       </c>
     </row>
     <row r="73">
@@ -17201,14 +17209,10 @@
           <t>клапан штуцерный</t>
         </is>
       </c>
-      <c r="F73" s="8" t="inlineStr">
-        <is>
-          <t>Ду20</t>
-        </is>
-      </c>
+      <c r="F73" s="8" t="inlineStr"/>
       <c r="G73" s="10" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду20 Ру100</t>
+          <t>Клапан штуцерный угловой Рр150/10</t>
         </is>
       </c>
       <c r="H73" s="8" t="inlineStr">
@@ -17217,16 +17221,16 @@
         </is>
       </c>
       <c r="I73" s="8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J73" s="12" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="K73" s="13" t="n">
-        <v>0.01</v>
+        <v>0.08</v>
       </c>
       <c r="L73" s="12" t="n">
-        <v>15000</v>
+        <v>32000</v>
       </c>
       <c r="M73" s="12" t="n">
         <v>2000</v>
@@ -17252,7 +17256,7 @@
         </is>
       </c>
       <c r="R73" s="12" t="n">
-        <v>610</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="74">
@@ -17276,13 +17280,17 @@
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
-        </is>
-      </c>
-      <c r="F74" s="8" t="inlineStr"/>
+          <t>сетка к фильтру</t>
+        </is>
+      </c>
+      <c r="F74" s="8" t="inlineStr">
+        <is>
+          <t>Ду20</t>
+        </is>
+      </c>
       <c r="G74" s="10" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Рр150/10</t>
+          <t>Сетка на фильтр Ду20 маленькая</t>
         </is>
       </c>
       <c r="H74" s="8" t="inlineStr">
@@ -17291,16 +17299,16 @@
         </is>
       </c>
       <c r="I74" s="8" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J74" s="12" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="K74" s="13" t="n">
-        <v>0.08</v>
+        <v>0.002</v>
       </c>
       <c r="L74" s="12" t="n">
-        <v>32000</v>
+        <v>3000</v>
       </c>
       <c r="M74" s="12" t="n">
         <v>2000</v>
@@ -17326,7 +17334,7 @@
         </is>
       </c>
       <c r="R74" s="12" t="n">
-        <v>1302</v>
+        <v>122</v>
       </c>
     </row>
     <row r="75">
@@ -17350,17 +17358,17 @@
       </c>
       <c r="E75" s="8" t="inlineStr">
         <is>
-          <t>сетка к фильтру</t>
+          <t>клапан фланцевый</t>
         </is>
       </c>
       <c r="F75" s="8" t="inlineStr">
         <is>
-          <t>Ду20</t>
+          <t>Ду32</t>
         </is>
       </c>
       <c r="G75" s="10" t="inlineStr">
         <is>
-          <t>Сетка на фильтр Ду20 маленькая</t>
+          <t>Клапан фланцевый проходной ДУ32 Ру25</t>
         </is>
       </c>
       <c r="H75" s="8" t="inlineStr">
@@ -17369,16 +17377,16 @@
         </is>
       </c>
       <c r="I75" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J75" s="12" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="K75" s="13" t="n">
-        <v>0.002</v>
+        <v>0.01</v>
       </c>
       <c r="L75" s="12" t="n">
-        <v>3000</v>
+        <v>28000</v>
       </c>
       <c r="M75" s="12" t="n">
         <v>2000</v>
@@ -17390,7 +17398,7 @@
       </c>
       <c r="O75" s="8" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 3</t>
         </is>
       </c>
       <c r="P75" s="8" t="inlineStr">
@@ -17404,7 +17412,7 @@
         </is>
       </c>
       <c r="R75" s="12" t="n">
-        <v>122</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="76">
@@ -17447,16 +17455,16 @@
         </is>
       </c>
       <c r="I76" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J76" s="12" t="n">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="K76" s="13" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="L76" s="12" t="n">
-        <v>28000</v>
+        <v>84000</v>
       </c>
       <c r="M76" s="12" t="n">
         <v>2000</v>
@@ -17482,7 +17490,7 @@
         </is>
       </c>
       <c r="R76" s="12" t="n">
-        <v>1140</v>
+        <v>3419</v>
       </c>
     </row>
     <row r="77">
@@ -17506,7 +17514,7 @@
       </c>
       <c r="E77" s="8" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>клапан пожарный</t>
         </is>
       </c>
       <c r="F77" s="8" t="inlineStr">
@@ -17516,7 +17524,7 @@
       </c>
       <c r="G77" s="10" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной ДУ32 Ру25</t>
+          <t>Клапан Пожарный фланцевый угловой Ду32</t>
         </is>
       </c>
       <c r="H77" s="8" t="inlineStr">
@@ -17525,19 +17533,19 @@
         </is>
       </c>
       <c r="I77" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J77" s="12" t="n">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="K77" s="13" t="n">
-        <v>0.03</v>
+        <v>0.005</v>
       </c>
       <c r="L77" s="12" t="n">
-        <v>84000</v>
+        <v>12800</v>
       </c>
       <c r="M77" s="12" t="n">
-        <v>2000</v>
+        <v>1829</v>
       </c>
       <c r="N77" s="10" t="inlineStr">
         <is>
@@ -17546,7 +17554,7 @@
       </c>
       <c r="O77" s="8" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Менеджерская</t>
         </is>
       </c>
       <c r="P77" s="8" t="inlineStr">
@@ -17560,7 +17568,7 @@
         </is>
       </c>
       <c r="R77" s="12" t="n">
-        <v>3419</v>
+        <v>570</v>
       </c>
     </row>
     <row r="78">
@@ -17584,17 +17592,17 @@
       </c>
       <c r="E78" s="8" t="inlineStr">
         <is>
-          <t>клапан пожарный</t>
+          <t>клапан фланцевый</t>
         </is>
       </c>
       <c r="F78" s="8" t="inlineStr">
         <is>
-          <t>Ду32</t>
+          <t>Ду40</t>
         </is>
       </c>
       <c r="G78" s="10" t="inlineStr">
         <is>
-          <t>Клапан Пожарный фланцевый угловой Ду32</t>
+          <t>Клапан угловой фланцевый Ду 40 - БРАК</t>
         </is>
       </c>
       <c r="H78" s="8" t="inlineStr">
@@ -17603,19 +17611,19 @@
         </is>
       </c>
       <c r="I78" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J78" s="12" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="K78" s="13" t="n">
-        <v>0.005</v>
+        <v>0.024</v>
       </c>
       <c r="L78" s="12" t="n">
-        <v>12800</v>
+        <v>54000</v>
       </c>
       <c r="M78" s="12" t="n">
-        <v>1829</v>
+        <v>1800</v>
       </c>
       <c r="N78" s="10" t="inlineStr">
         <is>
@@ -17624,7 +17632,7 @@
       </c>
       <c r="O78" s="8" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
       <c r="P78" s="8" t="inlineStr">
@@ -17638,7 +17646,7 @@
         </is>
       </c>
       <c r="R78" s="12" t="n">
-        <v>570</v>
+        <v>2442</v>
       </c>
     </row>
     <row r="79">
@@ -17662,17 +17670,17 @@
       </c>
       <c r="E79" s="8" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>клапан без описания — уточнить</t>
         </is>
       </c>
       <c r="F79" s="8" t="inlineStr">
         <is>
-          <t>Ду40</t>
+          <t>Ду20</t>
         </is>
       </c>
       <c r="G79" s="10" t="inlineStr">
         <is>
-          <t>Клапан угловой фланцевый Ду 40 - БРАК</t>
+          <t>Клапан Ду20/10</t>
         </is>
       </c>
       <c r="H79" s="8" t="inlineStr">
@@ -17684,13 +17692,13 @@
         <v>3</v>
       </c>
       <c r="J79" s="12" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="K79" s="13" t="n">
-        <v>0.024</v>
+        <v>0.006</v>
       </c>
       <c r="L79" s="12" t="n">
-        <v>54000</v>
+        <v>27000</v>
       </c>
       <c r="M79" s="12" t="n">
         <v>1800</v>
@@ -17702,7 +17710,7 @@
       </c>
       <c r="O79" s="8" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Склад 2</t>
         </is>
       </c>
       <c r="P79" s="8" t="inlineStr">
@@ -17716,7 +17724,7 @@
         </is>
       </c>
       <c r="R79" s="12" t="n">
-        <v>2442</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="80">
@@ -17740,17 +17748,17 @@
       </c>
       <c r="E80" s="8" t="inlineStr">
         <is>
-          <t>клапан без описания — уточнить</t>
+          <t>клапан фланцевый</t>
         </is>
       </c>
       <c r="F80" s="8" t="inlineStr">
         <is>
-          <t>Ду20</t>
+          <t>Ду32</t>
         </is>
       </c>
       <c r="G80" s="10" t="inlineStr">
         <is>
-          <t>Клапан Ду20/10</t>
+          <t>Клапан проходной фланцевый Ду32 - БРАК</t>
         </is>
       </c>
       <c r="H80" s="8" t="inlineStr">
@@ -17759,19 +17767,19 @@
         </is>
       </c>
       <c r="I80" s="8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J80" s="12" t="n">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="K80" s="13" t="n">
-        <v>0.006</v>
+        <v>0.03</v>
       </c>
       <c r="L80" s="12" t="n">
-        <v>27000</v>
+        <v>60000</v>
       </c>
       <c r="M80" s="12" t="n">
-        <v>1800</v>
+        <v>1429</v>
       </c>
       <c r="N80" s="10" t="inlineStr">
         <is>
@@ -17780,7 +17788,7 @@
       </c>
       <c r="O80" s="8" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
       <c r="P80" s="8" t="inlineStr">
@@ -17794,7 +17802,7 @@
         </is>
       </c>
       <c r="R80" s="12" t="n">
-        <v>1221</v>
+        <v>3419</v>
       </c>
     </row>
     <row r="81">
@@ -17818,17 +17826,17 @@
       </c>
       <c r="E81" s="8" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>клапан штуцерный</t>
         </is>
       </c>
       <c r="F81" s="8" t="inlineStr">
         <is>
-          <t>Ду32</t>
+          <t>Ду50</t>
         </is>
       </c>
       <c r="G81" s="10" t="inlineStr">
         <is>
-          <t>Клапан проходной фланцевый Ду32 - БРАК</t>
+          <t>Клапан угловой с присоединением под дюрит Ду50Ру4</t>
         </is>
       </c>
       <c r="H81" s="8" t="inlineStr">
@@ -17837,28 +17845,28 @@
         </is>
       </c>
       <c r="I81" s="8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J81" s="12" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="K81" s="13" t="n">
-        <v>0.03</v>
+        <v>0.048</v>
       </c>
       <c r="L81" s="12" t="n">
-        <v>60000</v>
+        <v>40000</v>
       </c>
       <c r="M81" s="12" t="n">
         <v>1429</v>
       </c>
       <c r="N81" s="10" t="inlineStr">
         <is>
-          <t>Ящик сплошной, с перегородками</t>
+          <t>Обрешетка на поддоне</t>
         </is>
       </c>
       <c r="O81" s="8" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Склад 2</t>
         </is>
       </c>
       <c r="P81" s="8" t="inlineStr">
@@ -17872,7 +17880,7 @@
         </is>
       </c>
       <c r="R81" s="12" t="n">
-        <v>3419</v>
+        <v>2279</v>
       </c>
     </row>
     <row r="82">
@@ -17906,7 +17914,7 @@
       </c>
       <c r="G82" s="10" t="inlineStr">
         <is>
-          <t>Клапан угловой с присоединением под дюрит Ду50Ру4</t>
+          <t>Клапан невозв-запорн.с присоед.под дюрит прох. Ду 50 Ру6</t>
         </is>
       </c>
       <c r="H82" s="8" t="inlineStr">
@@ -17915,16 +17923,16 @@
         </is>
       </c>
       <c r="I82" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J82" s="12" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="K82" s="13" t="n">
-        <v>0.048</v>
+        <v>0.012</v>
       </c>
       <c r="L82" s="12" t="n">
-        <v>40000</v>
+        <v>10000</v>
       </c>
       <c r="M82" s="12" t="n">
         <v>1429</v>
@@ -17950,7 +17958,7 @@
         </is>
       </c>
       <c r="R82" s="12" t="n">
-        <v>2279</v>
+        <v>570</v>
       </c>
     </row>
     <row r="83">
@@ -17974,17 +17982,17 @@
       </c>
       <c r="E83" s="8" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
+          <t>клапан фланцевый</t>
         </is>
       </c>
       <c r="F83" s="8" t="inlineStr">
         <is>
-          <t>Ду50</t>
+          <t>Ду32</t>
         </is>
       </c>
       <c r="G83" s="10" t="inlineStr">
         <is>
-          <t>Клапан невозв-запорн.с присоед.под дюрит прох. Ду 50 Ру6</t>
+          <t>Клапан предохранит. фланцевый угловой Ду32Ру4 (524-03.090)</t>
         </is>
       </c>
       <c r="H83" s="8" t="inlineStr">
@@ -17999,22 +18007,22 @@
         <v>7</v>
       </c>
       <c r="K83" s="13" t="n">
-        <v>0.012</v>
+        <v>0.005</v>
       </c>
       <c r="L83" s="12" t="n">
-        <v>10000</v>
+        <v>9600</v>
       </c>
       <c r="M83" s="12" t="n">
-        <v>1429</v>
+        <v>1371</v>
       </c>
       <c r="N83" s="10" t="inlineStr">
         <is>
-          <t>Обрешетка на поддоне</t>
+          <t>Ящик сплошной, с перегородками</t>
         </is>
       </c>
       <c r="O83" s="8" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
       <c r="P83" s="8" t="inlineStr">
@@ -18057,12 +18065,12 @@
       </c>
       <c r="F84" s="8" t="inlineStr">
         <is>
-          <t>Ду32</t>
+          <t>Ду40</t>
         </is>
       </c>
       <c r="G84" s="10" t="inlineStr">
         <is>
-          <t>Клапан предохранит. фланцевый угловой Ду32Ру4 (524-03.090)</t>
+          <t>Клапан проходной фланцевый Ду40 - БРАК</t>
         </is>
       </c>
       <c r="H84" s="8" t="inlineStr">
@@ -18071,19 +18079,19 @@
         </is>
       </c>
       <c r="I84" s="8" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="J84" s="12" t="n">
-        <v>7</v>
+        <v>130</v>
       </c>
       <c r="K84" s="13" t="n">
-        <v>0.005</v>
+        <v>0.104</v>
       </c>
       <c r="L84" s="12" t="n">
-        <v>9600</v>
+        <v>156000</v>
       </c>
       <c r="M84" s="12" t="n">
-        <v>1371</v>
+        <v>1200</v>
       </c>
       <c r="N84" s="10" t="inlineStr">
         <is>
@@ -18106,7 +18114,7 @@
         </is>
       </c>
       <c r="R84" s="12" t="n">
-        <v>570</v>
+        <v>10581</v>
       </c>
     </row>
     <row r="85">
@@ -18130,17 +18138,17 @@
       </c>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>колонка указательная</t>
         </is>
       </c>
       <c r="F85" s="8" t="inlineStr">
         <is>
-          <t>Ду40</t>
+          <t>Ду10</t>
         </is>
       </c>
       <c r="G85" s="10" t="inlineStr">
         <is>
-          <t>Клапан проходной фланцевый Ду40 - БРАК</t>
+          <t>Клапан для колонки указательной Ду10 Ру16</t>
         </is>
       </c>
       <c r="H85" s="8" t="inlineStr">
@@ -18149,16 +18157,16 @@
         </is>
       </c>
       <c r="I85" s="8" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="J85" s="12" t="n">
-        <v>130</v>
+        <v>30</v>
       </c>
       <c r="K85" s="13" t="n">
-        <v>0.104</v>
+        <v>0.006</v>
       </c>
       <c r="L85" s="12" t="n">
-        <v>156000</v>
+        <v>36000</v>
       </c>
       <c r="M85" s="12" t="n">
         <v>1200</v>
@@ -18170,7 +18178,7 @@
       </c>
       <c r="O85" s="8" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Склад 2</t>
         </is>
       </c>
       <c r="P85" s="8" t="inlineStr">
@@ -18184,7 +18192,7 @@
         </is>
       </c>
       <c r="R85" s="12" t="n">
-        <v>10581</v>
+        <v>2442</v>
       </c>
     </row>
     <row r="86">
@@ -18208,17 +18216,17 @@
       </c>
       <c r="E86" s="8" t="inlineStr">
         <is>
-          <t>колонка указательная</t>
+          <t>клапан штуцерный</t>
         </is>
       </c>
       <c r="F86" s="8" t="inlineStr">
         <is>
-          <t>Ду10</t>
+          <t>Ду20</t>
         </is>
       </c>
       <c r="G86" s="10" t="inlineStr">
         <is>
-          <t>Клапан для колонки указательной Ду10 Ру16</t>
+          <t>Клапан муфтовый проходной запорный Ду20Ру16</t>
         </is>
       </c>
       <c r="H86" s="8" t="inlineStr">
@@ -18227,19 +18235,19 @@
         </is>
       </c>
       <c r="I86" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J86" s="12" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="K86" s="13" t="n">
-        <v>0.006</v>
+        <v>0.002</v>
       </c>
       <c r="L86" s="12" t="n">
-        <v>36000</v>
+        <v>1000</v>
       </c>
       <c r="M86" s="12" t="n">
-        <v>1200</v>
+        <v>667</v>
       </c>
       <c r="N86" s="10" t="inlineStr">
         <is>
@@ -18258,11 +18266,11 @@
       </c>
       <c r="Q86" s="8" t="inlineStr">
         <is>
-          <t>транспортной компанией</t>
+          <t>ждет следующего контейнера</t>
         </is>
       </c>
       <c r="R86" s="12" t="n">
-        <v>2442</v>
+        <v>122</v>
       </c>
     </row>
     <row r="87">
@@ -18291,12 +18299,12 @@
       </c>
       <c r="F87" s="8" t="inlineStr">
         <is>
-          <t>Ду20</t>
+          <t>Ду25</t>
         </is>
       </c>
       <c r="G87" s="10" t="inlineStr">
         <is>
-          <t>Клапан муфтовый проходной запорный Ду20Ру16</t>
+          <t>Клапан муфтовый проходной запорный Ду25Ру16</t>
         </is>
       </c>
       <c r="H87" s="8" t="inlineStr">
@@ -18305,19 +18313,19 @@
         </is>
       </c>
       <c r="I87" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J87" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K87" s="13" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="L87" s="12" t="n">
-        <v>1000</v>
+        <v>2500</v>
       </c>
       <c r="M87" s="12" t="n">
-        <v>667</v>
+        <v>500</v>
       </c>
       <c r="N87" s="10" t="inlineStr">
         <is>
@@ -18340,7 +18348,7 @@
         </is>
       </c>
       <c r="R87" s="12" t="n">
-        <v>122</v>
+        <v>407</v>
       </c>
     </row>
     <row r="88">
@@ -18369,12 +18377,12 @@
       </c>
       <c r="F88" s="8" t="inlineStr">
         <is>
-          <t>Ду25</t>
+          <t>Ду32</t>
         </is>
       </c>
       <c r="G88" s="10" t="inlineStr">
         <is>
-          <t>Клапан муфтовый проходной запорный Ду25Ру16</t>
+          <t>Клапан муфтовый проходной запорный Ду32Ру10</t>
         </is>
       </c>
       <c r="H88" s="8" t="inlineStr">
@@ -18383,19 +18391,19 @@
         </is>
       </c>
       <c r="I88" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J88" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K88" s="13" t="n">
-        <v>0.006</v>
+        <v>0.005</v>
       </c>
       <c r="L88" s="12" t="n">
-        <v>2500</v>
+        <v>1500</v>
       </c>
       <c r="M88" s="12" t="n">
-        <v>500</v>
+        <v>429</v>
       </c>
       <c r="N88" s="10" t="inlineStr">
         <is>
@@ -18418,7 +18426,7 @@
         </is>
       </c>
       <c r="R88" s="12" t="n">
-        <v>407</v>
+        <v>285</v>
       </c>
     </row>
     <row r="89">
@@ -18447,12 +18455,12 @@
       </c>
       <c r="F89" s="8" t="inlineStr">
         <is>
-          <t>Ду32</t>
+          <t>Ду15</t>
         </is>
       </c>
       <c r="G89" s="10" t="inlineStr">
         <is>
-          <t>Клапан муфтовый проходной запорный Ду32Ру10</t>
+          <t>Клапан штуцерный проходной бессальниковый Ду15/1</t>
         </is>
       </c>
       <c r="H89" s="8" t="inlineStr">
@@ -18461,20 +18469,16 @@
         </is>
       </c>
       <c r="I89" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J89" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K89" s="13" t="n">
         <v>0.005</v>
       </c>
-      <c r="L89" s="12" t="n">
-        <v>1500</v>
-      </c>
-      <c r="M89" s="12" t="n">
-        <v>429</v>
-      </c>
+      <c r="L89" s="12" t="n"/>
+      <c r="M89" s="12" t="n"/>
       <c r="N89" s="10" t="inlineStr">
         <is>
           <t>Ящик сплошной, с перегородками</t>
@@ -18492,11 +18496,11 @@
       </c>
       <c r="Q89" s="8" t="inlineStr">
         <is>
-          <t>ждет следующего контейнера</t>
+          <t>ждет контейнера, цены нет</t>
         </is>
       </c>
       <c r="R89" s="12" t="n">
-        <v>285</v>
+        <v>244</v>
       </c>
     </row>
     <row r="90">
@@ -18530,7 +18534,7 @@
       </c>
       <c r="G90" s="10" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной бессальниковый Ду15/1</t>
+          <t>(Кнопка)Клапан самозакрывающий проходной муфтовый Ду15Ру3</t>
         </is>
       </c>
       <c r="H90" s="8" t="inlineStr">
@@ -18539,13 +18543,13 @@
         </is>
       </c>
       <c r="I90" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J90" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K90" s="13" t="n">
-        <v>0.005</v>
+        <v>0.002</v>
       </c>
       <c r="L90" s="12" t="n"/>
       <c r="M90" s="12" t="n"/>
@@ -18570,7 +18574,7 @@
         </is>
       </c>
       <c r="R90" s="12" t="n">
-        <v>244</v>
+        <v>81</v>
       </c>
     </row>
     <row r="91">
@@ -18597,14 +18601,10 @@
           <t>клапан штуцерный</t>
         </is>
       </c>
-      <c r="F91" s="8" t="inlineStr">
-        <is>
-          <t>Ду15</t>
-        </is>
-      </c>
+      <c r="F91" s="8" t="inlineStr"/>
       <c r="G91" s="10" t="inlineStr">
         <is>
-          <t>(Кнопка)Клапан самозакрывающий проходной муфтовый Ду15Ру3</t>
+          <t>Клапан дроссельный угловой штуцерный</t>
         </is>
       </c>
       <c r="H91" s="8" t="inlineStr">
@@ -18616,10 +18616,10 @@
         <v>1</v>
       </c>
       <c r="J91" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K91" s="13" t="n">
-        <v>0.002</v>
+        <v>0.01</v>
       </c>
       <c r="L91" s="12" t="n"/>
       <c r="M91" s="12" t="n"/>
@@ -18644,7 +18644,7 @@
         </is>
       </c>
       <c r="R91" s="12" t="n">
-        <v>81</v>
+        <v>163</v>
       </c>
     </row>
     <row r="92">
@@ -18671,10 +18671,14 @@
           <t>клапан штуцерный</t>
         </is>
       </c>
-      <c r="F92" s="8" t="inlineStr"/>
+      <c r="F92" s="8" t="inlineStr">
+        <is>
+          <t>Ду10</t>
+        </is>
+      </c>
       <c r="G92" s="10" t="inlineStr">
         <is>
-          <t>Клапан дроссельный угловой штуцерный</t>
+          <t>Клапан штуцерный угловой Ду10 Ру100</t>
         </is>
       </c>
       <c r="H92" s="8" t="inlineStr">
@@ -18686,10 +18690,10 @@
         <v>1</v>
       </c>
       <c r="J92" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K92" s="13" t="n">
-        <v>0.01</v>
+        <v>0.001</v>
       </c>
       <c r="L92" s="12" t="n"/>
       <c r="M92" s="12" t="n"/>
@@ -18714,7 +18718,7 @@
         </is>
       </c>
       <c r="R92" s="12" t="n">
-        <v>163</v>
+        <v>49</v>
       </c>
     </row>
     <row r="93">
@@ -18741,29 +18745,25 @@
           <t>клапан штуцерный</t>
         </is>
       </c>
-      <c r="F93" s="8" t="inlineStr">
-        <is>
-          <t>Ду10</t>
-        </is>
-      </c>
+      <c r="F93" s="8" t="inlineStr"/>
       <c r="G93" s="10" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду10 Ру100</t>
+          <t>Клапан штуцерный угловой Ду НЕРЖ</t>
         </is>
       </c>
       <c r="H93" s="8" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>нержавейка</t>
         </is>
       </c>
       <c r="I93" s="8" t="n">
         <v>1</v>
       </c>
       <c r="J93" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K93" s="13" t="n">
-        <v>0.001</v>
+        <v>0.01</v>
       </c>
       <c r="L93" s="12" t="n"/>
       <c r="M93" s="12" t="n"/>
@@ -18788,7 +18788,7 @@
         </is>
       </c>
       <c r="R93" s="12" t="n">
-        <v>49</v>
+        <v>163</v>
       </c>
     </row>
     <row r="94">
@@ -18812,28 +18812,32 @@
       </c>
       <c r="E94" s="8" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
-        </is>
-      </c>
-      <c r="F94" s="8" t="inlineStr"/>
+          <t>клапан редукционный</t>
+        </is>
+      </c>
+      <c r="F94" s="8" t="inlineStr">
+        <is>
+          <t>Ду20</t>
+        </is>
+      </c>
       <c r="G94" s="10" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду НЕРЖ</t>
+          <t>Клапан редукционный штуц.проход.односедельный Ду20Ру400 у входа</t>
         </is>
       </c>
       <c r="H94" s="8" t="inlineStr">
         <is>
-          <t>нержавейка</t>
+          <t>сталь</t>
         </is>
       </c>
       <c r="I94" s="8" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J94" s="12" t="n">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="K94" s="13" t="n">
-        <v>0.01</v>
+        <v>0.018</v>
       </c>
       <c r="L94" s="12" t="n"/>
       <c r="M94" s="12" t="n"/>
@@ -18858,7 +18862,7 @@
         </is>
       </c>
       <c r="R94" s="12" t="n">
-        <v>163</v>
+        <v>3663</v>
       </c>
     </row>
     <row r="95">
@@ -18882,7 +18886,7 @@
       </c>
       <c r="E95" s="8" t="inlineStr">
         <is>
-          <t>клапан редукционный</t>
+          <t>клапан электромагнитный</t>
         </is>
       </c>
       <c r="F95" s="8" t="inlineStr">
@@ -18892,22 +18896,22 @@
       </c>
       <c r="G95" s="10" t="inlineStr">
         <is>
-          <t>Клапан редукционный штуц.проход.односедельный Ду20Ру400 у входа</t>
+          <t>Клапан с электромагнитным ручным управлением Ду20/10 перем. 220В</t>
         </is>
       </c>
       <c r="H95" s="8" t="inlineStr">
         <is>
-          <t>сталь</t>
+          <t>бронза/латунь</t>
         </is>
       </c>
       <c r="I95" s="8" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J95" s="12" t="n">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="K95" s="13" t="n">
-        <v>0.018</v>
+        <v>0.002</v>
       </c>
       <c r="L95" s="12" t="n"/>
       <c r="M95" s="12" t="n"/>
@@ -18932,7 +18936,7 @@
         </is>
       </c>
       <c r="R95" s="12" t="n">
-        <v>3663</v>
+        <v>407</v>
       </c>
     </row>
     <row r="96">
@@ -18956,7 +18960,7 @@
       </c>
       <c r="E96" s="8" t="inlineStr">
         <is>
-          <t>клапан электромагнитный</t>
+          <t>клапан пусковой</t>
         </is>
       </c>
       <c r="F96" s="8" t="inlineStr">
@@ -18966,7 +18970,7 @@
       </c>
       <c r="G96" s="10" t="inlineStr">
         <is>
-          <t>Клапан с электромагнитным ручным управлением Ду20/10 перем. 220В</t>
+          <t>Клапан пусковой Ду20Ру125</t>
         </is>
       </c>
       <c r="H96" s="8" t="inlineStr">
@@ -18975,13 +18979,13 @@
         </is>
       </c>
       <c r="I96" s="8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J96" s="12" t="n">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="K96" s="13" t="n">
-        <v>0.002</v>
+        <v>0.014</v>
       </c>
       <c r="L96" s="12" t="n"/>
       <c r="M96" s="12" t="n"/>
@@ -19006,7 +19010,7 @@
         </is>
       </c>
       <c r="R96" s="12" t="n">
-        <v>407</v>
+        <v>2849</v>
       </c>
     </row>
     <row r="97">
@@ -19035,12 +19039,12 @@
       </c>
       <c r="F97" s="8" t="inlineStr">
         <is>
-          <t>Ду20</t>
+          <t>Ду32</t>
         </is>
       </c>
       <c r="G97" s="10" t="inlineStr">
         <is>
-          <t>Клапан пусковой Ду20Ру125</t>
+          <t>Клапан пусковой Ду32Ру125</t>
         </is>
       </c>
       <c r="H97" s="8" t="inlineStr">
@@ -19049,13 +19053,13 @@
         </is>
       </c>
       <c r="I97" s="8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J97" s="12" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="K97" s="13" t="n">
-        <v>0.014</v>
+        <v>0.04</v>
       </c>
       <c r="L97" s="12" t="n"/>
       <c r="M97" s="12" t="n"/>
@@ -19080,7 +19084,7 @@
         </is>
       </c>
       <c r="R97" s="12" t="n">
-        <v>2849</v>
+        <v>3256</v>
       </c>
     </row>
     <row r="98">
@@ -19104,7 +19108,7 @@
       </c>
       <c r="E98" s="8" t="inlineStr">
         <is>
-          <t>клапан пусковой</t>
+          <t>клапан пожарный</t>
         </is>
       </c>
       <c r="F98" s="8" t="inlineStr">
@@ -19114,7 +19118,7 @@
       </c>
       <c r="G98" s="10" t="inlineStr">
         <is>
-          <t>Клапан пусковой Ду32Ру125</t>
+          <t>Клапан фланц. концевой пожарный угловой Ду32 Ру10</t>
         </is>
       </c>
       <c r="H98" s="8" t="inlineStr">
@@ -19123,13 +19127,13 @@
         </is>
       </c>
       <c r="I98" s="8" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J98" s="12" t="n">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="K98" s="13" t="n">
-        <v>0.04</v>
+        <v>0.005</v>
       </c>
       <c r="L98" s="12" t="n"/>
       <c r="M98" s="12" t="n"/>
@@ -19154,7 +19158,7 @@
         </is>
       </c>
       <c r="R98" s="12" t="n">
-        <v>3256</v>
+        <v>570</v>
       </c>
     </row>
     <row r="99">
@@ -19188,7 +19192,7 @@
       </c>
       <c r="G99" s="10" t="inlineStr">
         <is>
-          <t>Клапан фланц. концевой пожарный угловой Ду32 Ру10</t>
+          <t>Клапан фланц. концевой пожарный угловой Ду32 Ру16</t>
         </is>
       </c>
       <c r="H99" s="8" t="inlineStr">
@@ -19197,13 +19201,13 @@
         </is>
       </c>
       <c r="I99" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J99" s="12" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="K99" s="13" t="n">
-        <v>0.005</v>
+        <v>0.01</v>
       </c>
       <c r="L99" s="12" t="n"/>
       <c r="M99" s="12" t="n"/>
@@ -19228,7 +19232,7 @@
         </is>
       </c>
       <c r="R99" s="12" t="n">
-        <v>570</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="100">
@@ -19252,17 +19256,17 @@
       </c>
       <c r="E100" s="8" t="inlineStr">
         <is>
-          <t>клапан пожарный</t>
+          <t>клапан штуцерный</t>
         </is>
       </c>
       <c r="F100" s="8" t="inlineStr">
         <is>
-          <t>Ду32</t>
+          <t>Ду50</t>
         </is>
       </c>
       <c r="G100" s="10" t="inlineStr">
         <is>
-          <t>Клапан фланц. концевой пожарный угловой Ду32 Ру16</t>
+          <t>Клапан невозв-запорн.с присоед.под дюрит прох. Ду 50</t>
         </is>
       </c>
       <c r="H100" s="8" t="inlineStr">
@@ -19271,24 +19275,24 @@
         </is>
       </c>
       <c r="I100" s="8" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J100" s="12" t="n">
-        <v>14</v>
+        <v>70</v>
       </c>
       <c r="K100" s="13" t="n">
-        <v>0.01</v>
+        <v>0.12</v>
       </c>
       <c r="L100" s="12" t="n"/>
       <c r="M100" s="12" t="n"/>
       <c r="N100" s="10" t="inlineStr">
         <is>
-          <t>Ящик сплошной, с перегородками</t>
+          <t>Обрешетка на поддоне</t>
         </is>
       </c>
       <c r="O100" s="8" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 3</t>
         </is>
       </c>
       <c r="P100" s="8" t="inlineStr">
@@ -19302,7 +19306,7 @@
         </is>
       </c>
       <c r="R100" s="12" t="n">
-        <v>1140</v>
+        <v>5698</v>
       </c>
     </row>
     <row r="101">
@@ -19331,12 +19335,12 @@
       </c>
       <c r="F101" s="8" t="inlineStr">
         <is>
-          <t>Ду50</t>
+          <t>Ду65</t>
         </is>
       </c>
       <c r="G101" s="10" t="inlineStr">
         <is>
-          <t>Клапан невозв-запорн.с присоед.под дюрит прох. Ду 50</t>
+          <t>Клапан запорн.с присоед.под дюрит прох. Ду65</t>
         </is>
       </c>
       <c r="H101" s="8" t="inlineStr">
@@ -19345,13 +19349,13 @@
         </is>
       </c>
       <c r="I101" s="8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J101" s="12" t="n">
-        <v>70</v>
+        <v>200</v>
       </c>
       <c r="K101" s="13" t="n">
-        <v>0.12</v>
+        <v>0.4</v>
       </c>
       <c r="L101" s="12" t="n"/>
       <c r="M101" s="12" t="n"/>
@@ -19376,104 +19380,30 @@
         </is>
       </c>
       <c r="R101" s="12" t="n">
-        <v>5698</v>
+        <v>16279</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="8" t="n">
-        <v>99</v>
-      </c>
-      <c r="B102" s="16" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="C102" s="10" t="inlineStr">
-        <is>
-          <t>5. Мелочь — ей добиваем контейнер до 25 тонн</t>
-        </is>
-      </c>
-      <c r="D102" s="8" t="inlineStr">
-        <is>
-          <t>Ярус 3, ящики</t>
-        </is>
-      </c>
-      <c r="E102" s="8" t="inlineStr">
-        <is>
-          <t>клапан штуцерный</t>
-        </is>
-      </c>
-      <c r="F102" s="8" t="inlineStr">
-        <is>
-          <t>Ду65</t>
-        </is>
-      </c>
-      <c r="G102" s="10" t="inlineStr">
-        <is>
-          <t>Клапан запорн.с присоед.под дюрит прох. Ду65</t>
-        </is>
-      </c>
-      <c r="H102" s="8" t="inlineStr">
-        <is>
-          <t>бронза/латунь</t>
-        </is>
-      </c>
-      <c r="I102" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="J102" s="12" t="n">
-        <v>200</v>
-      </c>
-      <c r="K102" s="13" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L102" s="12" t="n"/>
-      <c r="M102" s="12" t="n"/>
-      <c r="N102" s="10" t="inlineStr">
-        <is>
-          <t>Обрешетка на поддоне</t>
-        </is>
-      </c>
-      <c r="O102" s="8" t="inlineStr">
-        <is>
-          <t>Склад 3</t>
-        </is>
-      </c>
-      <c r="P102" s="8" t="inlineStr">
-        <is>
-          <t>не влезло по весу</t>
-        </is>
-      </c>
-      <c r="Q102" s="8" t="inlineStr">
-        <is>
-          <t>ждет контейнера, цены нет</t>
-        </is>
-      </c>
-      <c r="R102" s="12" t="n">
-        <v>16279</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="G103" s="14" t="inlineStr">
+      <c r="G102" s="14" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="I103" s="15">
-        <f>SUM(I4:I102)</f>
+      <c r="I102" s="15">
+        <f>SUM(I4:I101)</f>
         <v/>
       </c>
-      <c r="J103" s="15">
-        <f>SUM(J4:J102)</f>
+      <c r="J102" s="15">
+        <f>SUM(J4:J101)</f>
         <v/>
       </c>
-      <c r="L103" s="15">
-        <f>SUM(L4:L102)</f>
+      <c r="L102" s="15">
+        <f>SUM(L4:L101)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:R102"/>
+  <autoFilter ref="A3:R101"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -19484,7 +19414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R30"/>
+  <dimension ref="A1:R31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -21289,7 +21219,7 @@
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>5. Мелочь — ей добиваем контейнер до 25 тонн</t>
+          <t>4. Прочее, по цене за килограмм</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
@@ -21299,17 +21229,13 @@
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>клапан штуцерный</t>
-        </is>
-      </c>
-      <c r="F26" s="8" t="inlineStr">
-        <is>
-          <t>Ду10</t>
-        </is>
-      </c>
+          <t>клинкет (задвижка)</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="inlineStr"/>
       <c r="G26" s="10" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 10 Ру25 СТАЛЬ</t>
+          <t>Задвижки (желтая) ок. крышек</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
@@ -21318,20 +21244,16 @@
         </is>
       </c>
       <c r="I26" s="8" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>1</v>
+        <v>520</v>
       </c>
       <c r="K26" s="13" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="L26" s="12" t="n">
-        <v>2000</v>
-      </c>
-      <c r="M26" s="12" t="n">
-        <v>3333</v>
-      </c>
+        <v>0.13</v>
+      </c>
+      <c r="L26" s="12" t="n"/>
+      <c r="M26" s="12" t="n"/>
       <c r="N26" s="10" t="inlineStr">
         <is>
           <t>Ящик сплошной, с перегородками</t>
@@ -21339,7 +21261,7 @@
       </c>
       <c r="O26" s="8" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 3</t>
         </is>
       </c>
       <c r="P26" s="8" t="inlineStr">
@@ -21349,11 +21271,11 @@
       </c>
       <c r="Q26" s="8" t="inlineStr">
         <is>
-          <t>транспортной компанией</t>
+          <t>ждет контейнера, цены нет</t>
         </is>
       </c>
       <c r="R26" s="12" t="n">
-        <v>49</v>
+        <v>42325</v>
       </c>
     </row>
     <row r="27">
@@ -21387,7 +21309,7 @@
       </c>
       <c r="G27" s="10" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 10 Ру63 СТАЛЬ</t>
+          <t>Клапан штуцерный проходной Ду 10 Ру25 СТАЛЬ</t>
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr">
@@ -21455,17 +21377,17 @@
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>клапан фланцевый</t>
+          <t>клапан штуцерный</t>
         </is>
       </c>
       <c r="F28" s="8" t="inlineStr">
         <is>
-          <t>Ду40</t>
+          <t>Ду10</t>
         </is>
       </c>
       <c r="G28" s="10" t="inlineStr">
         <is>
-          <t>Клапан фланцевый угловой Ду40 Ру25 сталь ок.входа</t>
+          <t>Клапан штуцерный проходной Ду 10 Ру63 СТАЛЬ</t>
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr">
@@ -21474,19 +21396,19 @@
         </is>
       </c>
       <c r="I28" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="K28" s="13" t="n">
-        <v>0.016</v>
+        <v>0.001</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>36000</v>
+        <v>2000</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>1800</v>
+        <v>3333</v>
       </c>
       <c r="N28" s="10" t="inlineStr">
         <is>
@@ -21509,7 +21431,7 @@
         </is>
       </c>
       <c r="R28" s="12" t="n">
-        <v>1628</v>
+        <v>49</v>
       </c>
     </row>
     <row r="29">
@@ -21538,79 +21460,157 @@
       </c>
       <c r="F29" s="8" t="inlineStr">
         <is>
+          <t>Ду40</t>
+        </is>
+      </c>
+      <c r="G29" s="10" t="inlineStr">
+        <is>
+          <t>Клапан фланцевый угловой Ду40 Ру25 сталь ок.входа</t>
+        </is>
+      </c>
+      <c r="H29" s="8" t="inlineStr">
+        <is>
+          <t>сталь</t>
+        </is>
+      </c>
+      <c r="I29" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J29" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="K29" s="13" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="L29" s="12" t="n">
+        <v>36000</v>
+      </c>
+      <c r="M29" s="12" t="n">
+        <v>1800</v>
+      </c>
+      <c r="N29" s="10" t="inlineStr">
+        <is>
+          <t>Ящик сплошной, с перегородками</t>
+        </is>
+      </c>
+      <c r="O29" s="8" t="inlineStr">
+        <is>
+          <t>Склад 2</t>
+        </is>
+      </c>
+      <c r="P29" s="8" t="inlineStr">
+        <is>
+          <t>сталь, в этот раз не грузим</t>
+        </is>
+      </c>
+      <c r="Q29" s="8" t="inlineStr">
+        <is>
+          <t>транспортной компанией</t>
+        </is>
+      </c>
+      <c r="R29" s="12" t="n">
+        <v>1628</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="n">
+        <v>27</v>
+      </c>
+      <c r="B30" s="16" t="inlineStr">
+        <is>
+          <t>позже</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>5. Мелочь — ей добиваем контейнер до 25 тонн</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>Ярус 3, ящики</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>клапан фланцевый</t>
+        </is>
+      </c>
+      <c r="F30" s="8" t="inlineStr">
+        <is>
           <t>Ду32</t>
         </is>
       </c>
-      <c r="G29" s="10" t="inlineStr">
+      <c r="G30" s="10" t="inlineStr">
         <is>
           <t>Клапан фланцевый проходной ДУ32 Ру25 (сталь)</t>
         </is>
       </c>
-      <c r="H29" s="8" t="inlineStr">
+      <c r="H30" s="8" t="inlineStr">
         <is>
           <t>сталь</t>
         </is>
       </c>
-      <c r="I29" s="8" t="n">
+      <c r="I30" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="J29" s="12" t="n">
+      <c r="J30" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="K29" s="13" t="n">
+      <c r="K30" s="13" t="n">
         <v>0.005</v>
       </c>
-      <c r="L29" s="12" t="n">
+      <c r="L30" s="12" t="n">
         <v>9600</v>
       </c>
-      <c r="M29" s="12" t="n">
+      <c r="M30" s="12" t="n">
         <v>1371</v>
       </c>
-      <c r="N29" s="10" t="inlineStr">
+      <c r="N30" s="10" t="inlineStr">
         <is>
           <t>Ящик сплошной, с перегородками</t>
         </is>
       </c>
-      <c r="O29" s="8" t="inlineStr">
+      <c r="O30" s="8" t="inlineStr">
         <is>
           <t>Склад 3</t>
         </is>
       </c>
-      <c r="P29" s="8" t="inlineStr">
+      <c r="P30" s="8" t="inlineStr">
         <is>
           <t>сталь, в этот раз не грузим</t>
         </is>
       </c>
-      <c r="Q29" s="8" t="inlineStr">
+      <c r="Q30" s="8" t="inlineStr">
         <is>
           <t>транспортной компанией</t>
         </is>
       </c>
-      <c r="R29" s="12" t="n">
+      <c r="R30" s="12" t="n">
         <v>570</v>
       </c>
     </row>
-    <row r="30">
-      <c r="G30" s="14" t="inlineStr">
+    <row r="31">
+      <c r="G31" s="14" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="I30" s="15">
-        <f>SUM(I4:I29)</f>
+      <c r="I31" s="15">
+        <f>SUM(I4:I30)</f>
         <v/>
       </c>
-      <c r="J30" s="15">
-        <f>SUM(J4:J29)</f>
+      <c r="J31" s="15">
+        <f>SUM(J4:J30)</f>
         <v/>
       </c>
-      <c r="L30" s="15">
-        <f>SUM(L4:L29)</f>
+      <c r="L31" s="15">
+        <f>SUM(L4:L30)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:R29"/>
+  <autoFilter ref="A3:R30"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
